--- a/AAII_Financials/Quarterly/SKHSY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/SKHSY_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="359" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="306" uniqueCount="92">
   <si>
     <t>SKHSY</t>
   </si>
@@ -656,53 +656,52 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:M102"/>
+  <dimension ref="A5:O102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="13" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="10" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="15" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45322</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45230</v>
+      </c>
+      <c r="F7" s="2">
         <v>45138</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45046</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>44957</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>44865</v>
       </c>
-      <c r="H7" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="I7" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="J7" s="2" t="s">
-        <v>3</v>
+      <c r="J7" s="2">
+        <v>44592</v>
       </c>
       <c r="K7" s="2" t="s">
         <v>3</v>
@@ -713,31 +712,37 @@
       <c r="M7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N7" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="O7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
-        <v>5007600</v>
+        <v>6185500</v>
       </c>
       <c r="E8" s="3">
-        <v>4703000</v>
+        <v>4900400</v>
       </c>
       <c r="F8" s="3">
-        <v>5303700</v>
+        <v>5083100</v>
       </c>
       <c r="G8" s="3">
-        <v>4690700</v>
-      </c>
-      <c r="H8" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I8" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J8" s="3" t="s">
-        <v>3</v>
+        <v>4773800</v>
+      </c>
+      <c r="H8" s="3">
+        <v>5383600</v>
+      </c>
+      <c r="I8" s="3">
+        <v>4761400</v>
+      </c>
+      <c r="J8" s="3">
+        <v>5019700</v>
       </c>
       <c r="K8" s="3" t="s">
         <v>3</v>
@@ -748,31 +753,37 @@
       <c r="M8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
-        <v>3976400</v>
+        <v>4964000</v>
       </c>
       <c r="E9" s="3">
-        <v>3786300</v>
+        <v>3895200</v>
       </c>
       <c r="F9" s="3">
-        <v>4333700</v>
+        <v>4036200</v>
       </c>
       <c r="G9" s="3">
-        <v>3784000</v>
-      </c>
-      <c r="H9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J9" s="3" t="s">
-        <v>3</v>
+        <v>3843300</v>
+      </c>
+      <c r="H9" s="3">
+        <v>4399000</v>
+      </c>
+      <c r="I9" s="3">
+        <v>3841000</v>
+      </c>
+      <c r="J9" s="3">
+        <v>4041200</v>
       </c>
       <c r="K9" s="3" t="s">
         <v>3</v>
@@ -783,31 +794,37 @@
       <c r="M9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
-        <v>1031300</v>
+        <v>1221500</v>
       </c>
       <c r="E10" s="3">
-        <v>916700</v>
+        <v>1005200</v>
       </c>
       <c r="F10" s="3">
-        <v>970100</v>
+        <v>1046800</v>
       </c>
       <c r="G10" s="3">
-        <v>906800</v>
-      </c>
-      <c r="H10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J10" s="3" t="s">
-        <v>3</v>
+        <v>930500</v>
+      </c>
+      <c r="H10" s="3">
+        <v>984700</v>
+      </c>
+      <c r="I10" s="3">
+        <v>920400</v>
+      </c>
+      <c r="J10" s="3">
+        <v>978500</v>
       </c>
       <c r="K10" s="3" t="s">
         <v>3</v>
@@ -818,8 +835,14 @@
       <c r="M10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -833,8 +856,10 @@
       <c r="K11" s="3"/>
       <c r="L11" s="3"/>
       <c r="M11" s="3"/>
-    </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N11" s="3"/>
+      <c r="O11" s="3"/>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -868,8 +893,14 @@
       <c r="M12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -903,31 +934,37 @@
       <c r="M13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N13" s="3">
+        <v>0</v>
+      </c>
+      <c r="O13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>700</v>
+        <v>-41400</v>
       </c>
       <c r="E14" s="3">
-        <v>900</v>
+        <v>-15500</v>
       </c>
       <c r="F14" s="3">
-        <v>18200</v>
+        <v>800</v>
       </c>
       <c r="G14" s="3">
-        <v>-56200</v>
-      </c>
-      <c r="H14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J14" s="3" t="s">
-        <v>3</v>
+        <v>-54500</v>
+      </c>
+      <c r="H14" s="3">
+        <v>18500</v>
+      </c>
+      <c r="I14" s="3">
+        <v>-57000</v>
+      </c>
+      <c r="J14" s="3">
+        <v>3000</v>
       </c>
       <c r="K14" s="3" t="s">
         <v>3</v>
@@ -938,8 +975,14 @@
       <c r="M14" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O14" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -973,8 +1016,14 @@
       <c r="M15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N15" s="3">
+        <v>0</v>
+      </c>
+      <c r="O15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -985,31 +1034,33 @@
       <c r="K16" s="3"/>
       <c r="L16" s="3"/>
       <c r="M16" s="3"/>
-    </row>
-    <row r="17" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N16" s="3"/>
+      <c r="O16" s="3"/>
+    </row>
+    <row r="17" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>4549000</v>
+        <v>5576200</v>
       </c>
       <c r="E17" s="3">
-        <v>4333800</v>
+        <v>4468600</v>
       </c>
       <c r="F17" s="3">
-        <v>4930300</v>
+        <v>4617500</v>
       </c>
       <c r="G17" s="3">
-        <v>4262300</v>
-      </c>
-      <c r="H17" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I17" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J17" s="3" t="s">
-        <v>3</v>
+        <v>4343600</v>
+      </c>
+      <c r="H17" s="3">
+        <v>5004500</v>
+      </c>
+      <c r="I17" s="3">
+        <v>4326400</v>
+      </c>
+      <c r="J17" s="3">
+        <v>4605300</v>
       </c>
       <c r="K17" s="3" t="s">
         <v>3</v>
@@ -1020,31 +1071,37 @@
       <c r="M17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>458600</v>
+        <v>609300</v>
       </c>
       <c r="E18" s="3">
-        <v>369100</v>
+        <v>431800</v>
       </c>
       <c r="F18" s="3">
-        <v>373500</v>
+        <v>465500</v>
       </c>
       <c r="G18" s="3">
-        <v>428500</v>
-      </c>
-      <c r="H18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J18" s="3" t="s">
-        <v>3</v>
+        <v>430200</v>
+      </c>
+      <c r="H18" s="3">
+        <v>379100</v>
+      </c>
+      <c r="I18" s="3">
+        <v>435000</v>
+      </c>
+      <c r="J18" s="3">
+        <v>414400</v>
       </c>
       <c r="K18" s="3" t="s">
         <v>3</v>
@@ -1055,8 +1112,14 @@
       <c r="M18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1070,31 +1133,33 @@
       <c r="K19" s="3"/>
       <c r="L19" s="3"/>
       <c r="M19" s="3"/>
-    </row>
-    <row r="20" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N19" s="3"/>
+      <c r="O19" s="3"/>
+    </row>
+    <row r="20" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>46800</v>
+        <v>16800</v>
       </c>
       <c r="E20" s="3">
-        <v>56700</v>
+        <v>27700</v>
       </c>
       <c r="F20" s="3">
-        <v>-19900</v>
+        <v>47500</v>
       </c>
       <c r="G20" s="3">
         <v>2100</v>
       </c>
-      <c r="H20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J20" s="3" t="s">
-        <v>3</v>
+      <c r="H20" s="3">
+        <v>-20200</v>
+      </c>
+      <c r="I20" s="3">
+        <v>2000</v>
+      </c>
+      <c r="J20" s="3">
+        <v>5800</v>
       </c>
       <c r="K20" s="3" t="s">
         <v>3</v>
@@ -1105,22 +1170,28 @@
       <c r="M20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>552300</v>
+        <v>654700</v>
       </c>
       <c r="E21" s="3">
-        <v>473300</v>
-      </c>
-      <c r="F21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G21" s="3" t="s">
-        <v>3</v>
+        <v>522200</v>
+      </c>
+      <c r="F21" s="3">
+        <v>560600</v>
+      </c>
+      <c r="G21" s="3">
+        <v>480500</v>
       </c>
       <c r="H21" s="3" t="s">
         <v>3</v>
@@ -1140,31 +1211,37 @@
       <c r="M21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>17400</v>
+        <v>24100</v>
       </c>
       <c r="E22" s="3">
-        <v>16800</v>
+        <v>24600</v>
       </c>
       <c r="F22" s="3">
-        <v>12700</v>
+        <v>17600</v>
       </c>
       <c r="G22" s="3">
-        <v>11000</v>
-      </c>
-      <c r="H22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J22" s="3" t="s">
-        <v>3</v>
+        <v>17000</v>
+      </c>
+      <c r="H22" s="3">
+        <v>12900</v>
+      </c>
+      <c r="I22" s="3">
+        <v>11200</v>
+      </c>
+      <c r="J22" s="3">
+        <v>10700</v>
       </c>
       <c r="K22" s="3" t="s">
         <v>3</v>
@@ -1175,31 +1252,37 @@
       <c r="M22" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>488100</v>
+        <v>602000</v>
       </c>
       <c r="E23" s="3">
-        <v>409100</v>
+        <v>434900</v>
       </c>
       <c r="F23" s="3">
-        <v>340800</v>
+        <v>495400</v>
       </c>
       <c r="G23" s="3">
-        <v>419500</v>
-      </c>
-      <c r="H23" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I23" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J23" s="3" t="s">
-        <v>3</v>
+        <v>415200</v>
+      </c>
+      <c r="H23" s="3">
+        <v>345900</v>
+      </c>
+      <c r="I23" s="3">
+        <v>425800</v>
+      </c>
+      <c r="J23" s="3">
+        <v>409500</v>
       </c>
       <c r="K23" s="3" t="s">
         <v>3</v>
@@ -1210,31 +1293,37 @@
       <c r="M23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>146300</v>
+        <v>177200</v>
       </c>
       <c r="E24" s="3">
-        <v>122500</v>
+        <v>98800</v>
       </c>
       <c r="F24" s="3">
-        <v>106200</v>
+        <v>148500</v>
       </c>
       <c r="G24" s="3">
-        <v>110700</v>
-      </c>
-      <c r="H24" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I24" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J24" s="3" t="s">
-        <v>3</v>
+        <v>124400</v>
+      </c>
+      <c r="H24" s="3">
+        <v>107800</v>
+      </c>
+      <c r="I24" s="3">
+        <v>112400</v>
+      </c>
+      <c r="J24" s="3">
+        <v>134300</v>
       </c>
       <c r="K24" s="3" t="s">
         <v>3</v>
@@ -1245,8 +1334,14 @@
       <c r="M24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1280,31 +1375,37 @@
       <c r="M25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N25" s="3">
+        <v>0</v>
+      </c>
+      <c r="O25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>341700</v>
+        <v>424800</v>
       </c>
       <c r="E26" s="3">
-        <v>286600</v>
+        <v>336100</v>
       </c>
       <c r="F26" s="3">
-        <v>234600</v>
+        <v>346900</v>
       </c>
       <c r="G26" s="3">
-        <v>308700</v>
-      </c>
-      <c r="H26" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I26" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J26" s="3" t="s">
-        <v>3</v>
+        <v>290900</v>
+      </c>
+      <c r="H26" s="3">
+        <v>238200</v>
+      </c>
+      <c r="I26" s="3">
+        <v>313400</v>
+      </c>
+      <c r="J26" s="3">
+        <v>275100</v>
       </c>
       <c r="K26" s="3" t="s">
         <v>3</v>
@@ -1315,31 +1416,37 @@
       <c r="M26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>335700</v>
+        <v>407300</v>
       </c>
       <c r="E27" s="3">
-        <v>278400</v>
+        <v>332900</v>
       </c>
       <c r="F27" s="3">
-        <v>230400</v>
+        <v>340800</v>
       </c>
       <c r="G27" s="3">
-        <v>303800</v>
-      </c>
-      <c r="H27" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I27" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J27" s="3" t="s">
-        <v>3</v>
+        <v>282600</v>
+      </c>
+      <c r="H27" s="3">
+        <v>233900</v>
+      </c>
+      <c r="I27" s="3">
+        <v>308300</v>
+      </c>
+      <c r="J27" s="3">
+        <v>256200</v>
       </c>
       <c r="K27" s="3" t="s">
         <v>3</v>
@@ -1350,8 +1457,14 @@
       <c r="M27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1385,8 +1498,14 @@
       <c r="M28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N28" s="3">
+        <v>0</v>
+      </c>
+      <c r="O28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1420,8 +1539,14 @@
       <c r="M29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N29" s="3">
+        <v>0</v>
+      </c>
+      <c r="O29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1455,8 +1580,14 @@
       <c r="M30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N30" s="3">
+        <v>0</v>
+      </c>
+      <c r="O30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1490,31 +1621,37 @@
       <c r="M31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N31" s="3">
+        <v>0</v>
+      </c>
+      <c r="O31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-46800</v>
+        <v>-16800</v>
       </c>
       <c r="E32" s="3">
-        <v>-56700</v>
+        <v>-27700</v>
       </c>
       <c r="F32" s="3">
-        <v>19900</v>
+        <v>-47500</v>
       </c>
       <c r="G32" s="3">
         <v>-2100</v>
       </c>
-      <c r="H32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J32" s="3" t="s">
-        <v>3</v>
+      <c r="H32" s="3">
+        <v>20200</v>
+      </c>
+      <c r="I32" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="J32" s="3">
+        <v>-5800</v>
       </c>
       <c r="K32" s="3" t="s">
         <v>3</v>
@@ -1525,31 +1662,37 @@
       <c r="M32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>335700</v>
+        <v>407300</v>
       </c>
       <c r="E33" s="3">
-        <v>278400</v>
+        <v>332900</v>
       </c>
       <c r="F33" s="3">
-        <v>230400</v>
+        <v>340800</v>
       </c>
       <c r="G33" s="3">
-        <v>303800</v>
-      </c>
-      <c r="H33" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I33" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J33" s="3" t="s">
-        <v>3</v>
+        <v>282600</v>
+      </c>
+      <c r="H33" s="3">
+        <v>233900</v>
+      </c>
+      <c r="I33" s="3">
+        <v>308300</v>
+      </c>
+      <c r="J33" s="3">
+        <v>256200</v>
       </c>
       <c r="K33" s="3" t="s">
         <v>3</v>
@@ -1560,8 +1703,14 @@
       <c r="M33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1595,31 +1744,37 @@
       <c r="M34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N34" s="3">
+        <v>0</v>
+      </c>
+      <c r="O34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>335700</v>
+        <v>407300</v>
       </c>
       <c r="E35" s="3">
-        <v>278400</v>
+        <v>332900</v>
       </c>
       <c r="F35" s="3">
-        <v>230400</v>
+        <v>340800</v>
       </c>
       <c r="G35" s="3">
-        <v>303800</v>
-      </c>
-      <c r="H35" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I35" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J35" s="3" t="s">
-        <v>3</v>
+        <v>282600</v>
+      </c>
+      <c r="H35" s="3">
+        <v>233900</v>
+      </c>
+      <c r="I35" s="3">
+        <v>308300</v>
+      </c>
+      <c r="J35" s="3">
+        <v>256200</v>
       </c>
       <c r="K35" s="3" t="s">
         <v>3</v>
@@ -1630,36 +1785,42 @@
       <c r="M35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45322</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45230</v>
+      </c>
+      <c r="F38" s="2">
         <v>45138</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45046</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>44957</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>44865</v>
       </c>
-      <c r="H38" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="I38" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="J38" s="2" t="s">
-        <v>3</v>
+      <c r="J38" s="2">
+        <v>44592</v>
       </c>
       <c r="K38" s="2" t="s">
         <v>3</v>
@@ -1670,8 +1831,14 @@
       <c r="M38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N38" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="O38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1685,8 +1852,10 @@
       <c r="K39" s="3"/>
       <c r="L39" s="3"/>
       <c r="M39" s="3"/>
-    </row>
-    <row r="40" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N39" s="3"/>
+      <c r="O39" s="3"/>
+    </row>
+    <row r="40" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1700,31 +1869,33 @@
       <c r="K40" s="3"/>
       <c r="L40" s="3"/>
       <c r="M40" s="3"/>
-    </row>
-    <row r="41" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N40" s="3"/>
+      <c r="O40" s="3"/>
+    </row>
+    <row r="41" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>2023300</v>
+        <v>1975800</v>
       </c>
       <c r="E41" s="3">
-        <v>2013700</v>
+        <v>2117400</v>
       </c>
       <c r="F41" s="3">
-        <v>2210500</v>
-      </c>
-      <c r="G41" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H41" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I41" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J41" s="3" t="s">
-        <v>3</v>
+        <v>2053800</v>
+      </c>
+      <c r="G41" s="3">
+        <v>2044000</v>
+      </c>
+      <c r="H41" s="3">
+        <v>2243800</v>
+      </c>
+      <c r="I41" s="3">
+        <v>2287500</v>
+      </c>
+      <c r="J41" s="3">
+        <v>3473000</v>
       </c>
       <c r="K41" s="3" t="s">
         <v>3</v>
@@ -1735,8 +1906,14 @@
       <c r="M41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -1770,31 +1947,37 @@
       <c r="M42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N42" s="3">
+        <v>0</v>
+      </c>
+      <c r="O42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>948100</v>
+        <v>1182500</v>
       </c>
       <c r="E43" s="3">
-        <v>1025500</v>
+        <v>1029700</v>
       </c>
       <c r="F43" s="3">
-        <v>1035800</v>
-      </c>
-      <c r="G43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J43" s="3" t="s">
-        <v>3</v>
+        <v>962400</v>
+      </c>
+      <c r="G43" s="3">
+        <v>1041000</v>
+      </c>
+      <c r="H43" s="3">
+        <v>1051400</v>
+      </c>
+      <c r="I43" s="3">
+        <v>1013600</v>
+      </c>
+      <c r="J43" s="3">
+        <v>884900</v>
       </c>
       <c r="K43" s="3" t="s">
         <v>3</v>
@@ -1805,31 +1988,37 @@
       <c r="M43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>11897300</v>
+        <v>12763700</v>
       </c>
       <c r="E44" s="3">
-        <v>10222900</v>
+        <v>13160400</v>
       </c>
       <c r="F44" s="3">
-        <v>9726200</v>
-      </c>
-      <c r="G44" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H44" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I44" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J44" s="3" t="s">
-        <v>3</v>
+        <v>12076500</v>
+      </c>
+      <c r="G44" s="3">
+        <v>10376900</v>
+      </c>
+      <c r="H44" s="3">
+        <v>9872700</v>
+      </c>
+      <c r="I44" s="3">
+        <v>10268700</v>
+      </c>
+      <c r="J44" s="3">
+        <v>8118200</v>
       </c>
       <c r="K44" s="3" t="s">
         <v>3</v>
@@ -1840,31 +2029,37 @@
       <c r="M44" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="45" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O44" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>883800</v>
+        <v>907400</v>
       </c>
       <c r="E45" s="3">
-        <v>902900</v>
+        <v>941100</v>
       </c>
       <c r="F45" s="3">
-        <v>931000</v>
-      </c>
-      <c r="G45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J45" s="3" t="s">
-        <v>3</v>
+        <v>897100</v>
+      </c>
+      <c r="G45" s="3">
+        <v>916500</v>
+      </c>
+      <c r="H45" s="3">
+        <v>945000</v>
+      </c>
+      <c r="I45" s="3">
+        <v>929600</v>
+      </c>
+      <c r="J45" s="3">
+        <v>685300</v>
       </c>
       <c r="K45" s="3" t="s">
         <v>3</v>
@@ -1875,31 +2070,37 @@
       <c r="M45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>15752600</v>
+        <v>16829400</v>
       </c>
       <c r="E46" s="3">
-        <v>14165100</v>
+        <v>17248600</v>
       </c>
       <c r="F46" s="3">
-        <v>13903400</v>
-      </c>
-      <c r="G46" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H46" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I46" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J46" s="3" t="s">
-        <v>3</v>
+        <v>15989800</v>
+      </c>
+      <c r="G46" s="3">
+        <v>14378400</v>
+      </c>
+      <c r="H46" s="3">
+        <v>14112800</v>
+      </c>
+      <c r="I46" s="3">
+        <v>14499500</v>
+      </c>
+      <c r="J46" s="3">
+        <v>13161400</v>
       </c>
       <c r="K46" s="3" t="s">
         <v>3</v>
@@ -1910,31 +2111,37 @@
       <c r="M46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>1413500</v>
+        <v>1351600</v>
       </c>
       <c r="E47" s="3">
-        <v>1319200</v>
+        <v>1375900</v>
       </c>
       <c r="F47" s="3">
-        <v>1294300</v>
-      </c>
-      <c r="G47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J47" s="3" t="s">
-        <v>3</v>
+        <v>1434800</v>
+      </c>
+      <c r="G47" s="3">
+        <v>1339100</v>
+      </c>
+      <c r="H47" s="3">
+        <v>1313800</v>
+      </c>
+      <c r="I47" s="3">
+        <v>1336600</v>
+      </c>
+      <c r="J47" s="3">
+        <v>1319900</v>
       </c>
       <c r="K47" s="3" t="s">
         <v>3</v>
@@ -1945,31 +2152,37 @@
       <c r="M47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>3561000</v>
+        <v>3344700</v>
       </c>
       <c r="E48" s="3">
-        <v>3730000</v>
+        <v>3418100</v>
       </c>
       <c r="F48" s="3">
-        <v>3682300</v>
-      </c>
-      <c r="G48" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H48" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I48" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J48" s="3" t="s">
-        <v>3</v>
+        <v>3614600</v>
+      </c>
+      <c r="G48" s="3">
+        <v>3786200</v>
+      </c>
+      <c r="H48" s="3">
+        <v>3737700</v>
+      </c>
+      <c r="I48" s="3">
+        <v>3892400</v>
+      </c>
+      <c r="J48" s="3">
+        <v>3644400</v>
       </c>
       <c r="K48" s="3" t="s">
         <v>3</v>
@@ -1980,31 +2193,37 @@
       <c r="M48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>282100</v>
+        <v>272200</v>
       </c>
       <c r="E49" s="3">
-        <v>278600</v>
+        <v>279500</v>
       </c>
       <c r="F49" s="3">
-        <v>339400</v>
-      </c>
-      <c r="G49" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H49" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I49" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J49" s="3" t="s">
-        <v>3</v>
+        <v>286300</v>
+      </c>
+      <c r="G49" s="3">
+        <v>282800</v>
+      </c>
+      <c r="H49" s="3">
+        <v>344500</v>
+      </c>
+      <c r="I49" s="3">
+        <v>371300</v>
+      </c>
+      <c r="J49" s="3">
+        <v>121200</v>
       </c>
       <c r="K49" s="3" t="s">
         <v>3</v>
@@ -2015,8 +2234,14 @@
       <c r="M49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2050,8 +2275,14 @@
       <c r="M50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N50" s="3">
+        <v>0</v>
+      </c>
+      <c r="O50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2085,31 +2316,37 @@
       <c r="M51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N51" s="3">
+        <v>0</v>
+      </c>
+      <c r="O51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>747500</v>
+        <v>799900</v>
       </c>
       <c r="E52" s="3">
-        <v>736600</v>
+        <v>793700</v>
       </c>
       <c r="F52" s="3">
-        <v>750600</v>
-      </c>
-      <c r="G52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J52" s="3" t="s">
-        <v>3</v>
+        <v>758800</v>
+      </c>
+      <c r="G52" s="3">
+        <v>747700</v>
+      </c>
+      <c r="H52" s="3">
+        <v>761900</v>
+      </c>
+      <c r="I52" s="3">
+        <v>651800</v>
+      </c>
+      <c r="J52" s="3">
+        <v>633100</v>
       </c>
       <c r="K52" s="3" t="s">
         <v>3</v>
@@ -2120,8 +2357,14 @@
       <c r="M52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2155,31 +2398,37 @@
       <c r="M53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N53" s="3">
+        <v>0</v>
+      </c>
+      <c r="O53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>21756700</v>
+        <v>22597900</v>
       </c>
       <c r="E54" s="3">
-        <v>20229500</v>
+        <v>23115700</v>
       </c>
       <c r="F54" s="3">
-        <v>19970000</v>
-      </c>
-      <c r="G54" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H54" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I54" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J54" s="3" t="s">
-        <v>3</v>
+        <v>22084300</v>
+      </c>
+      <c r="G54" s="3">
+        <v>20534200</v>
+      </c>
+      <c r="H54" s="3">
+        <v>20270800</v>
+      </c>
+      <c r="I54" s="3">
+        <v>20751700</v>
+      </c>
+      <c r="J54" s="3">
+        <v>18880000</v>
       </c>
       <c r="K54" s="3" t="s">
         <v>3</v>
@@ -2190,8 +2439,14 @@
       <c r="M54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2205,8 +2460,10 @@
       <c r="K55" s="3"/>
       <c r="L55" s="3"/>
       <c r="M55" s="3"/>
-    </row>
-    <row r="56" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N55" s="3"/>
+      <c r="O55" s="3"/>
+    </row>
+    <row r="56" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2220,31 +2477,33 @@
       <c r="K56" s="3"/>
       <c r="L56" s="3"/>
       <c r="M56" s="3"/>
-    </row>
-    <row r="57" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N56" s="3"/>
+      <c r="O56" s="3"/>
+    </row>
+    <row r="57" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>1500000</v>
+        <v>1599300</v>
       </c>
       <c r="E57" s="3">
-        <v>1418000</v>
+        <v>1499800</v>
       </c>
       <c r="F57" s="3">
-        <v>1506200</v>
-      </c>
-      <c r="G57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J57" s="3" t="s">
-        <v>3</v>
+        <v>1522600</v>
+      </c>
+      <c r="G57" s="3">
+        <v>1439400</v>
+      </c>
+      <c r="H57" s="3">
+        <v>1528900</v>
+      </c>
+      <c r="I57" s="3">
+        <v>1505600</v>
+      </c>
+      <c r="J57" s="3">
+        <v>1399600</v>
       </c>
       <c r="K57" s="3" t="s">
         <v>3</v>
@@ -2255,31 +2514,37 @@
       <c r="M57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>3067600</v>
+        <v>3111900</v>
       </c>
       <c r="E58" s="3">
-        <v>3218500</v>
+        <v>4016500</v>
       </c>
       <c r="F58" s="3">
-        <v>2718200</v>
-      </c>
-      <c r="G58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J58" s="3" t="s">
-        <v>3</v>
+        <v>3113800</v>
+      </c>
+      <c r="G58" s="3">
+        <v>3266900</v>
+      </c>
+      <c r="H58" s="3">
+        <v>2759100</v>
+      </c>
+      <c r="I58" s="3">
+        <v>3279200</v>
+      </c>
+      <c r="J58" s="3">
+        <v>1593600</v>
       </c>
       <c r="K58" s="3" t="s">
         <v>3</v>
@@ -2290,31 +2555,37 @@
       <c r="M58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>2729800</v>
+        <v>2959200</v>
       </c>
       <c r="E59" s="3">
-        <v>2527900</v>
+        <v>2912300</v>
       </c>
       <c r="F59" s="3">
-        <v>2712000</v>
-      </c>
-      <c r="G59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J59" s="3" t="s">
-        <v>3</v>
+        <v>2770900</v>
+      </c>
+      <c r="G59" s="3">
+        <v>2566000</v>
+      </c>
+      <c r="H59" s="3">
+        <v>2752900</v>
+      </c>
+      <c r="I59" s="3">
+        <v>2636900</v>
+      </c>
+      <c r="J59" s="3">
+        <v>2856500</v>
       </c>
       <c r="K59" s="3" t="s">
         <v>3</v>
@@ -2325,31 +2596,37 @@
       <c r="M59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>7297500</v>
+        <v>7670400</v>
       </c>
       <c r="E60" s="3">
-        <v>7164400</v>
+        <v>8428600</v>
       </c>
       <c r="F60" s="3">
-        <v>6936400</v>
-      </c>
-      <c r="G60" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H60" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I60" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J60" s="3" t="s">
-        <v>3</v>
+        <v>7407400</v>
+      </c>
+      <c r="G60" s="3">
+        <v>7272300</v>
+      </c>
+      <c r="H60" s="3">
+        <v>7040900</v>
+      </c>
+      <c r="I60" s="3">
+        <v>7421600</v>
+      </c>
+      <c r="J60" s="3">
+        <v>5849700</v>
       </c>
       <c r="K60" s="3" t="s">
         <v>3</v>
@@ -2360,31 +2637,37 @@
       <c r="M60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>1944600</v>
+        <v>1948500</v>
       </c>
       <c r="E61" s="3">
-        <v>1127000</v>
+        <v>1932700</v>
       </c>
       <c r="F61" s="3">
-        <v>1313600</v>
+        <v>1973900</v>
       </c>
       <c r="G61" s="3">
-        <v>0</v>
+        <v>1144000</v>
       </c>
       <c r="H61" s="3">
-        <v>0</v>
+        <v>1333400</v>
       </c>
       <c r="I61" s="3">
-        <v>0</v>
+        <v>1208300</v>
       </c>
       <c r="J61" s="3">
-        <v>0</v>
+        <v>2112500</v>
       </c>
       <c r="K61" s="3">
         <v>0</v>
@@ -2395,31 +2678,37 @@
       <c r="M61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N61" s="3">
+        <v>0</v>
+      </c>
+      <c r="O61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>825200</v>
+        <v>887100</v>
       </c>
       <c r="E62" s="3">
-        <v>802600</v>
+        <v>831300</v>
       </c>
       <c r="F62" s="3">
-        <v>647500</v>
-      </c>
-      <c r="G62" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H62" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I62" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J62" s="3" t="s">
-        <v>3</v>
+        <v>837600</v>
+      </c>
+      <c r="G62" s="3">
+        <v>814700</v>
+      </c>
+      <c r="H62" s="3">
+        <v>657300</v>
+      </c>
+      <c r="I62" s="3">
+        <v>789800</v>
+      </c>
+      <c r="J62" s="3">
+        <v>666600</v>
       </c>
       <c r="K62" s="3" t="s">
         <v>3</v>
@@ -2430,8 +2719,14 @@
       <c r="M62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2465,8 +2760,14 @@
       <c r="M63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N63" s="3">
+        <v>0</v>
+      </c>
+      <c r="O63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2500,8 +2801,14 @@
       <c r="M64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N64" s="3">
+        <v>0</v>
+      </c>
+      <c r="O64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2535,31 +2842,37 @@
       <c r="M65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N65" s="3">
+        <v>0</v>
+      </c>
+      <c r="O65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>10320800</v>
+        <v>10771300</v>
       </c>
       <c r="E66" s="3">
-        <v>9330700</v>
+        <v>11456800</v>
       </c>
       <c r="F66" s="3">
-        <v>9127200</v>
-      </c>
-      <c r="G66" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H66" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I66" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J66" s="3" t="s">
-        <v>3</v>
+        <v>10476300</v>
+      </c>
+      <c r="G66" s="3">
+        <v>9471200</v>
+      </c>
+      <c r="H66" s="3">
+        <v>9264600</v>
+      </c>
+      <c r="I66" s="3">
+        <v>9779300</v>
+      </c>
+      <c r="J66" s="3">
+        <v>8944400</v>
       </c>
       <c r="K66" s="3" t="s">
         <v>3</v>
@@ -2570,8 +2883,14 @@
       <c r="M66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2585,8 +2904,10 @@
       <c r="K67" s="3"/>
       <c r="L67" s="3"/>
       <c r="M67" s="3"/>
-    </row>
-    <row r="68" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N67" s="3"/>
+      <c r="O67" s="3"/>
+    </row>
+    <row r="68" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2620,8 +2941,14 @@
       <c r="M68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N68" s="3">
+        <v>0</v>
+      </c>
+      <c r="O68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2655,8 +2982,14 @@
       <c r="M69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N69" s="3">
+        <v>0</v>
+      </c>
+      <c r="O69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -2690,8 +3023,14 @@
       <c r="M70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N70" s="3">
+        <v>0</v>
+      </c>
+      <c r="O70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2725,31 +3064,37 @@
       <c r="M71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N71" s="3">
+        <v>0</v>
+      </c>
+      <c r="O71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>7045200</v>
+        <v>7632200</v>
       </c>
       <c r="E72" s="3">
-        <v>6709500</v>
+        <v>7225100</v>
       </c>
       <c r="F72" s="3">
-        <v>7015900</v>
-      </c>
-      <c r="G72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J72" s="3" t="s">
-        <v>3</v>
+        <v>7151300</v>
+      </c>
+      <c r="G72" s="3">
+        <v>6810500</v>
+      </c>
+      <c r="H72" s="3">
+        <v>7121500</v>
+      </c>
+      <c r="I72" s="3">
+        <v>6888000</v>
+      </c>
+      <c r="J72" s="3">
+        <v>6337800</v>
       </c>
       <c r="K72" s="3" t="s">
         <v>3</v>
@@ -2760,8 +3105,14 @@
       <c r="M72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -2795,8 +3146,14 @@
       <c r="M73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N73" s="3">
+        <v>0</v>
+      </c>
+      <c r="O73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -2830,8 +3187,14 @@
       <c r="M74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N74" s="3">
+        <v>0</v>
+      </c>
+      <c r="O74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -2865,31 +3228,37 @@
       <c r="M75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N75" s="3">
+        <v>0</v>
+      </c>
+      <c r="O75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>11435800</v>
+        <v>11826600</v>
       </c>
       <c r="E76" s="3">
-        <v>10898900</v>
+        <v>11659000</v>
       </c>
       <c r="F76" s="3">
-        <v>10842900</v>
-      </c>
-      <c r="G76" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H76" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I76" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J76" s="3" t="s">
-        <v>3</v>
+        <v>11608000</v>
+      </c>
+      <c r="G76" s="3">
+        <v>11063000</v>
+      </c>
+      <c r="H76" s="3">
+        <v>11006200</v>
+      </c>
+      <c r="I76" s="3">
+        <v>10972400</v>
+      </c>
+      <c r="J76" s="3">
+        <v>9935600</v>
       </c>
       <c r="K76" s="3" t="s">
         <v>3</v>
@@ -2900,8 +3269,14 @@
       <c r="M76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -2935,36 +3310,42 @@
       <c r="M77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N77" s="3">
+        <v>0</v>
+      </c>
+      <c r="O77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45322</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45230</v>
+      </c>
+      <c r="F80" s="2">
         <v>45138</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45046</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>44957</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>44865</v>
       </c>
-      <c r="H80" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="I80" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="J80" s="2" t="s">
-        <v>3</v>
+      <c r="J80" s="2">
+        <v>44592</v>
       </c>
       <c r="K80" s="2" t="s">
         <v>3</v>
@@ -2975,31 +3356,37 @@
       <c r="M80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N80" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="O80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>335700</v>
+        <v>407300</v>
       </c>
       <c r="E81" s="3">
-        <v>278400</v>
+        <v>332900</v>
       </c>
       <c r="F81" s="3">
-        <v>230400</v>
+        <v>340800</v>
       </c>
       <c r="G81" s="3">
-        <v>303800</v>
-      </c>
-      <c r="H81" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I81" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J81" s="3" t="s">
-        <v>3</v>
+        <v>282600</v>
+      </c>
+      <c r="H81" s="3">
+        <v>233900</v>
+      </c>
+      <c r="I81" s="3">
+        <v>308300</v>
+      </c>
+      <c r="J81" s="3">
+        <v>256200</v>
       </c>
       <c r="K81" s="3" t="s">
         <v>3</v>
@@ -3010,8 +3397,14 @@
       <c r="M81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3025,22 +3418,24 @@
       <c r="K82" s="3"/>
       <c r="L82" s="3"/>
       <c r="M82" s="3"/>
-    </row>
-    <row r="83" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N82" s="3"/>
+      <c r="O82" s="3"/>
+    </row>
+    <row r="83" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>46800</v>
+        <v>28600</v>
       </c>
       <c r="E83" s="3">
-        <v>47500</v>
-      </c>
-      <c r="F83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G83" s="3" t="s">
-        <v>3</v>
+        <v>62700</v>
+      </c>
+      <c r="F83" s="3">
+        <v>47600</v>
+      </c>
+      <c r="G83" s="3">
+        <v>48200</v>
       </c>
       <c r="H83" s="3" t="s">
         <v>3</v>
@@ -3054,14 +3449,20 @@
       <c r="K83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L83" s="3">
-        <v>0</v>
-      </c>
-      <c r="M83" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="84" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="L83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N83" s="3">
+        <v>0</v>
+      </c>
+      <c r="O83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3095,8 +3496,14 @@
       <c r="M84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N84" s="3">
+        <v>0</v>
+      </c>
+      <c r="O84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3130,8 +3537,14 @@
       <c r="M85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N85" s="3">
+        <v>0</v>
+      </c>
+      <c r="O85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3165,8 +3578,14 @@
       <c r="M86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N86" s="3">
+        <v>0</v>
+      </c>
+      <c r="O86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3200,8 +3619,14 @@
       <c r="M87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N87" s="3">
+        <v>0</v>
+      </c>
+      <c r="O87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3235,8 +3660,14 @@
       <c r="M88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N88" s="3">
+        <v>0</v>
+      </c>
+      <c r="O88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
@@ -3270,8 +3701,14 @@
       <c r="M89" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="90" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N89" s="3">
+        <v>0</v>
+      </c>
+      <c r="O89" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3285,17 +3722,19 @@
       <c r="K90" s="3"/>
       <c r="L90" s="3"/>
       <c r="M90" s="3"/>
-    </row>
-    <row r="91" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N90" s="3"/>
+      <c r="O90" s="3"/>
+    </row>
+    <row r="91" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-39333000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-37604000</v>
       </c>
-      <c r="E91" s="3">
-        <v>0</v>
-      </c>
       <c r="F91" s="3">
         <v>0</v>
       </c>
@@ -3320,8 +3759,14 @@
       <c r="M91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N91" s="3">
+        <v>0</v>
+      </c>
+      <c r="O91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3355,8 +3800,14 @@
       <c r="M92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N92" s="3">
+        <v>0</v>
+      </c>
+      <c r="O92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3390,8 +3841,14 @@
       <c r="M93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N93" s="3">
+        <v>0</v>
+      </c>
+      <c r="O93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -3425,8 +3882,14 @@
       <c r="M94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N94" s="3">
+        <v>0</v>
+      </c>
+      <c r="O94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3440,8 +3903,10 @@
       <c r="K95" s="3"/>
       <c r="L95" s="3"/>
       <c r="M95" s="3"/>
-    </row>
-    <row r="96" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N95" s="3"/>
+      <c r="O95" s="3"/>
+    </row>
+    <row r="96" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -3475,8 +3940,14 @@
       <c r="M96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N96" s="3">
+        <v>0</v>
+      </c>
+      <c r="O96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3510,8 +3981,14 @@
       <c r="M97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N97" s="3">
+        <v>0</v>
+      </c>
+      <c r="O97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -3545,8 +4022,14 @@
       <c r="M98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N98" s="3">
+        <v>0</v>
+      </c>
+      <c r="O98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -3580,8 +4063,14 @@
       <c r="M99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N99" s="3">
+        <v>0</v>
+      </c>
+      <c r="O99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -3615,8 +4104,14 @@
       <c r="M100" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="101" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N100" s="3">
+        <v>0</v>
+      </c>
+      <c r="O100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -3650,8 +4145,14 @@
       <c r="M101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N101" s="3">
+        <v>0</v>
+      </c>
+      <c r="O101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
@@ -3683,6 +4184,12 @@
         <v>0</v>
       </c>
       <c r="M102" s="3">
+        <v>0</v>
+      </c>
+      <c r="N102" s="3">
+        <v>0</v>
+      </c>
+      <c r="O102" s="3">
         <v>0</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/SKHSY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/SKHSY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="306" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="348" uniqueCount="92">
   <si>
     <t>SKHSY</t>
   </si>
@@ -656,56 +656,56 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:O102"/>
+  <dimension ref="A5:P102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="10" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="15" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="6" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="16" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45412</v>
+      </c>
+      <c r="E7" s="2">
         <v>45322</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45230</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45138</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45046</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44957</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44865</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44592</v>
       </c>
-      <c r="K7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="L7" s="2" t="s">
         <v>3</v>
       </c>
@@ -718,35 +718,38 @@
       <c r="O7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
-        <v>6185500</v>
+        <v>4957600</v>
       </c>
       <c r="E8" s="3">
-        <v>4900400</v>
+        <v>5855100</v>
       </c>
       <c r="F8" s="3">
-        <v>5083100</v>
+        <v>4638700</v>
       </c>
       <c r="G8" s="3">
-        <v>4773800</v>
+        <v>4811600</v>
       </c>
       <c r="H8" s="3">
-        <v>5383600</v>
+        <v>4518800</v>
       </c>
       <c r="I8" s="3">
-        <v>4761400</v>
+        <v>5096100</v>
       </c>
       <c r="J8" s="3">
+        <v>4507100</v>
+      </c>
+      <c r="K8" s="3">
         <v>5019700</v>
       </c>
-      <c r="K8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L8" s="3" t="s">
         <v>3</v>
       </c>
@@ -759,35 +762,38 @@
       <c r="O8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
-        <v>4964000</v>
+        <v>3930100</v>
       </c>
       <c r="E9" s="3">
-        <v>3895200</v>
+        <v>4698900</v>
       </c>
       <c r="F9" s="3">
-        <v>4036200</v>
+        <v>3687100</v>
       </c>
       <c r="G9" s="3">
-        <v>3843300</v>
+        <v>3820700</v>
       </c>
       <c r="H9" s="3">
-        <v>4399000</v>
+        <v>3638100</v>
       </c>
       <c r="I9" s="3">
-        <v>3841000</v>
+        <v>4164000</v>
       </c>
       <c r="J9" s="3">
+        <v>3635800</v>
+      </c>
+      <c r="K9" s="3">
         <v>4041200</v>
       </c>
-      <c r="K9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L9" s="3" t="s">
         <v>3</v>
       </c>
@@ -800,35 +806,38 @@
       <c r="O9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
-        <v>1221500</v>
+        <v>1027500</v>
       </c>
       <c r="E10" s="3">
-        <v>1005200</v>
+        <v>1156300</v>
       </c>
       <c r="F10" s="3">
-        <v>1046800</v>
+        <v>951500</v>
       </c>
       <c r="G10" s="3">
-        <v>930500</v>
+        <v>990900</v>
       </c>
       <c r="H10" s="3">
-        <v>984700</v>
+        <v>880800</v>
       </c>
       <c r="I10" s="3">
-        <v>920400</v>
+        <v>932100</v>
       </c>
       <c r="J10" s="3">
+        <v>871300</v>
+      </c>
+      <c r="K10" s="3">
         <v>978500</v>
       </c>
-      <c r="K10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L10" s="3" t="s">
         <v>3</v>
       </c>
@@ -841,8 +850,11 @@
       <c r="O10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -858,8 +870,9 @@
       <c r="M11" s="3"/>
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
-    </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P11" s="3"/>
+    </row>
+    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -899,8 +912,11 @@
       <c r="O12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -940,35 +956,38 @@
       <c r="O13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>-41400</v>
+        <v>100</v>
       </c>
       <c r="E14" s="3">
-        <v>-15500</v>
+        <v>-39200</v>
       </c>
       <c r="F14" s="3">
-        <v>800</v>
+        <v>-14700</v>
       </c>
       <c r="G14" s="3">
-        <v>-54500</v>
+        <v>700</v>
       </c>
       <c r="H14" s="3">
-        <v>18500</v>
+        <v>-51600</v>
       </c>
       <c r="I14" s="3">
-        <v>-57000</v>
+        <v>17500</v>
       </c>
       <c r="J14" s="3">
+        <v>-54000</v>
+      </c>
+      <c r="K14" s="3">
         <v>3000</v>
       </c>
-      <c r="K14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L14" s="3" t="s">
         <v>3</v>
       </c>
@@ -981,8 +1000,11 @@
       <c r="O14" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P14" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1022,8 +1044,11 @@
       <c r="O15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1036,35 +1061,36 @@
       <c r="M16" s="3"/>
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
-    </row>
-    <row r="17" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P16" s="3"/>
+    </row>
+    <row r="17" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>5576200</v>
+        <v>4500100</v>
       </c>
       <c r="E17" s="3">
-        <v>4468600</v>
+        <v>5278300</v>
       </c>
       <c r="F17" s="3">
-        <v>4617500</v>
+        <v>4229900</v>
       </c>
       <c r="G17" s="3">
-        <v>4343600</v>
+        <v>4370900</v>
       </c>
       <c r="H17" s="3">
-        <v>5004500</v>
+        <v>4111600</v>
       </c>
       <c r="I17" s="3">
-        <v>4326400</v>
+        <v>4737200</v>
       </c>
       <c r="J17" s="3">
+        <v>4095300</v>
+      </c>
+      <c r="K17" s="3">
         <v>4605300</v>
       </c>
-      <c r="K17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L17" s="3" t="s">
         <v>3</v>
       </c>
@@ -1077,35 +1103,38 @@
       <c r="O17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>609300</v>
+        <v>457500</v>
       </c>
       <c r="E18" s="3">
-        <v>431800</v>
+        <v>576800</v>
       </c>
       <c r="F18" s="3">
-        <v>465500</v>
+        <v>408700</v>
       </c>
       <c r="G18" s="3">
-        <v>430200</v>
+        <v>440700</v>
       </c>
       <c r="H18" s="3">
-        <v>379100</v>
+        <v>407200</v>
       </c>
       <c r="I18" s="3">
-        <v>435000</v>
+        <v>358800</v>
       </c>
       <c r="J18" s="3">
+        <v>411700</v>
+      </c>
+      <c r="K18" s="3">
         <v>414400</v>
       </c>
-      <c r="K18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1118,8 +1147,11 @@
       <c r="O18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1135,35 +1167,36 @@
       <c r="M19" s="3"/>
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
-    </row>
-    <row r="20" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P19" s="3"/>
+    </row>
+    <row r="20" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>16800</v>
+        <v>25000</v>
       </c>
       <c r="E20" s="3">
-        <v>27700</v>
+        <v>15900</v>
       </c>
       <c r="F20" s="3">
-        <v>47500</v>
+        <v>26200</v>
       </c>
       <c r="G20" s="3">
-        <v>2100</v>
+        <v>45000</v>
       </c>
       <c r="H20" s="3">
-        <v>-20200</v>
+        <v>2000</v>
       </c>
       <c r="I20" s="3">
-        <v>2000</v>
+        <v>-19200</v>
       </c>
       <c r="J20" s="3">
+        <v>1900</v>
+      </c>
+      <c r="K20" s="3">
         <v>5800</v>
       </c>
-      <c r="K20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L20" s="3" t="s">
         <v>3</v>
       </c>
@@ -1176,25 +1209,28 @@
       <c r="O20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>654700</v>
+        <v>531300</v>
       </c>
       <c r="E21" s="3">
-        <v>522200</v>
+        <v>619700</v>
       </c>
       <c r="F21" s="3">
-        <v>560600</v>
+        <v>494300</v>
       </c>
       <c r="G21" s="3">
-        <v>480500</v>
-      </c>
-      <c r="H21" s="3" t="s">
-        <v>3</v>
+        <v>530700</v>
+      </c>
+      <c r="H21" s="3">
+        <v>454800</v>
       </c>
       <c r="I21" s="3" t="s">
         <v>3</v>
@@ -1217,35 +1253,38 @@
       <c r="O21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>24100</v>
+        <v>30300</v>
       </c>
       <c r="E22" s="3">
-        <v>24600</v>
+        <v>22900</v>
       </c>
       <c r="F22" s="3">
-        <v>17600</v>
+        <v>23200</v>
       </c>
       <c r="G22" s="3">
-        <v>17000</v>
+        <v>16700</v>
       </c>
       <c r="H22" s="3">
-        <v>12900</v>
+        <v>16100</v>
       </c>
       <c r="I22" s="3">
-        <v>11200</v>
+        <v>12200</v>
       </c>
       <c r="J22" s="3">
+        <v>10600</v>
+      </c>
+      <c r="K22" s="3">
         <v>10700</v>
       </c>
-      <c r="K22" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L22" s="3" t="s">
         <v>3</v>
       </c>
@@ -1258,35 +1297,38 @@
       <c r="O22" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>602000</v>
+        <v>452100</v>
       </c>
       <c r="E23" s="3">
-        <v>434900</v>
+        <v>569900</v>
       </c>
       <c r="F23" s="3">
-        <v>495400</v>
+        <v>411700</v>
       </c>
       <c r="G23" s="3">
-        <v>415200</v>
+        <v>469000</v>
       </c>
       <c r="H23" s="3">
-        <v>345900</v>
+        <v>393100</v>
       </c>
       <c r="I23" s="3">
-        <v>425800</v>
+        <v>327500</v>
       </c>
       <c r="J23" s="3">
+        <v>403100</v>
+      </c>
+      <c r="K23" s="3">
         <v>409500</v>
       </c>
-      <c r="K23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L23" s="3" t="s">
         <v>3</v>
       </c>
@@ -1299,35 +1341,38 @@
       <c r="O23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>177200</v>
+        <v>124200</v>
       </c>
       <c r="E24" s="3">
-        <v>98800</v>
+        <v>167700</v>
       </c>
       <c r="F24" s="3">
-        <v>148500</v>
+        <v>93500</v>
       </c>
       <c r="G24" s="3">
-        <v>124400</v>
+        <v>140600</v>
       </c>
       <c r="H24" s="3">
-        <v>107800</v>
+        <v>117700</v>
       </c>
       <c r="I24" s="3">
-        <v>112400</v>
+        <v>102000</v>
       </c>
       <c r="J24" s="3">
+        <v>106400</v>
+      </c>
+      <c r="K24" s="3">
         <v>134300</v>
       </c>
-      <c r="K24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L24" s="3" t="s">
         <v>3</v>
       </c>
@@ -1340,8 +1385,11 @@
       <c r="O24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1381,35 +1429,38 @@
       <c r="O25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>424800</v>
+        <v>328000</v>
       </c>
       <c r="E26" s="3">
-        <v>336100</v>
+        <v>402100</v>
       </c>
       <c r="F26" s="3">
-        <v>346900</v>
+        <v>318200</v>
       </c>
       <c r="G26" s="3">
-        <v>290900</v>
+        <v>328400</v>
       </c>
       <c r="H26" s="3">
-        <v>238200</v>
+        <v>275300</v>
       </c>
       <c r="I26" s="3">
-        <v>313400</v>
+        <v>225500</v>
       </c>
       <c r="J26" s="3">
+        <v>296700</v>
+      </c>
+      <c r="K26" s="3">
         <v>275100</v>
       </c>
-      <c r="K26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L26" s="3" t="s">
         <v>3</v>
       </c>
@@ -1422,35 +1473,38 @@
       <c r="O26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>407300</v>
+        <v>321700</v>
       </c>
       <c r="E27" s="3">
-        <v>332900</v>
+        <v>385600</v>
       </c>
       <c r="F27" s="3">
-        <v>340800</v>
+        <v>315100</v>
       </c>
       <c r="G27" s="3">
-        <v>282600</v>
+        <v>322600</v>
       </c>
       <c r="H27" s="3">
-        <v>233900</v>
+        <v>267500</v>
       </c>
       <c r="I27" s="3">
-        <v>308300</v>
+        <v>221400</v>
       </c>
       <c r="J27" s="3">
+        <v>291900</v>
+      </c>
+      <c r="K27" s="3">
         <v>256200</v>
       </c>
-      <c r="K27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L27" s="3" t="s">
         <v>3</v>
       </c>
@@ -1463,8 +1517,11 @@
       <c r="O27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1504,8 +1561,11 @@
       <c r="O28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1545,8 +1605,11 @@
       <c r="O29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1586,8 +1649,11 @@
       <c r="O30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1627,35 +1693,38 @@
       <c r="O31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-16800</v>
+        <v>-25000</v>
       </c>
       <c r="E32" s="3">
-        <v>-27700</v>
+        <v>-15900</v>
       </c>
       <c r="F32" s="3">
-        <v>-47500</v>
+        <v>-26200</v>
       </c>
       <c r="G32" s="3">
-        <v>-2100</v>
+        <v>-45000</v>
       </c>
       <c r="H32" s="3">
-        <v>20200</v>
+        <v>-2000</v>
       </c>
       <c r="I32" s="3">
-        <v>-2000</v>
+        <v>19200</v>
       </c>
       <c r="J32" s="3">
+        <v>-1900</v>
+      </c>
+      <c r="K32" s="3">
         <v>-5800</v>
       </c>
-      <c r="K32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L32" s="3" t="s">
         <v>3</v>
       </c>
@@ -1668,35 +1737,38 @@
       <c r="O32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>407300</v>
+        <v>321700</v>
       </c>
       <c r="E33" s="3">
-        <v>332900</v>
+        <v>385600</v>
       </c>
       <c r="F33" s="3">
-        <v>340800</v>
+        <v>315100</v>
       </c>
       <c r="G33" s="3">
-        <v>282600</v>
+        <v>322600</v>
       </c>
       <c r="H33" s="3">
-        <v>233900</v>
+        <v>267500</v>
       </c>
       <c r="I33" s="3">
-        <v>308300</v>
+        <v>221400</v>
       </c>
       <c r="J33" s="3">
+        <v>291900</v>
+      </c>
+      <c r="K33" s="3">
         <v>256200</v>
       </c>
-      <c r="K33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L33" s="3" t="s">
         <v>3</v>
       </c>
@@ -1709,8 +1781,11 @@
       <c r="O33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1750,35 +1825,38 @@
       <c r="O34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>407300</v>
+        <v>321700</v>
       </c>
       <c r="E35" s="3">
-        <v>332900</v>
+        <v>385600</v>
       </c>
       <c r="F35" s="3">
-        <v>340800</v>
+        <v>315100</v>
       </c>
       <c r="G35" s="3">
-        <v>282600</v>
+        <v>322600</v>
       </c>
       <c r="H35" s="3">
-        <v>233900</v>
+        <v>267500</v>
       </c>
       <c r="I35" s="3">
-        <v>308300</v>
+        <v>221400</v>
       </c>
       <c r="J35" s="3">
+        <v>291900</v>
+      </c>
+      <c r="K35" s="3">
         <v>256200</v>
       </c>
-      <c r="K35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L35" s="3" t="s">
         <v>3</v>
       </c>
@@ -1791,40 +1869,43 @@
       <c r="O35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45412</v>
+      </c>
+      <c r="E38" s="2">
         <v>45322</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45230</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45138</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45046</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44957</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44865</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44592</v>
       </c>
-      <c r="K38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="L38" s="2" t="s">
         <v>3</v>
       </c>
@@ -1837,8 +1918,11 @@
       <c r="O38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1854,8 +1938,9 @@
       <c r="M39" s="3"/>
       <c r="N39" s="3"/>
       <c r="O39" s="3"/>
-    </row>
-    <row r="40" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P39" s="3"/>
+    </row>
+    <row r="40" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1871,35 +1956,36 @@
       <c r="M40" s="3"/>
       <c r="N40" s="3"/>
       <c r="O40" s="3"/>
-    </row>
-    <row r="41" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P40" s="3"/>
+    </row>
+    <row r="41" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>1975800</v>
+        <v>2475300</v>
       </c>
       <c r="E41" s="3">
-        <v>2117400</v>
+        <v>1870300</v>
       </c>
       <c r="F41" s="3">
-        <v>2053800</v>
+        <v>2004300</v>
       </c>
       <c r="G41" s="3">
-        <v>2044000</v>
+        <v>1944100</v>
       </c>
       <c r="H41" s="3">
-        <v>2243800</v>
+        <v>1934900</v>
       </c>
       <c r="I41" s="3">
-        <v>2287500</v>
+        <v>2123900</v>
       </c>
       <c r="J41" s="3">
+        <v>2165300</v>
+      </c>
+      <c r="K41" s="3">
         <v>3473000</v>
       </c>
-      <c r="K41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L41" s="3" t="s">
         <v>3</v>
       </c>
@@ -1912,31 +1998,34 @@
       <c r="O41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>0</v>
-      </c>
-      <c r="E42" s="3">
-        <v>0</v>
-      </c>
-      <c r="F42" s="3">
-        <v>0</v>
-      </c>
-      <c r="G42" s="3">
-        <v>0</v>
-      </c>
-      <c r="H42" s="3">
-        <v>0</v>
-      </c>
-      <c r="I42" s="3">
-        <v>0</v>
-      </c>
-      <c r="J42" s="3">
-        <v>0</v>
+        <v>78400</v>
+      </c>
+      <c r="E42" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F42" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G42" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H42" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I42" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J42" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K42" s="3">
         <v>0</v>
@@ -1953,35 +2042,38 @@
       <c r="O42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>1182500</v>
+        <v>1098000</v>
       </c>
       <c r="E43" s="3">
-        <v>1029700</v>
+        <v>1119300</v>
       </c>
       <c r="F43" s="3">
-        <v>962400</v>
+        <v>974700</v>
       </c>
       <c r="G43" s="3">
-        <v>1041000</v>
+        <v>911000</v>
       </c>
       <c r="H43" s="3">
-        <v>1051400</v>
+        <v>985400</v>
       </c>
       <c r="I43" s="3">
-        <v>1013600</v>
+        <v>995200</v>
       </c>
       <c r="J43" s="3">
+        <v>959500</v>
+      </c>
+      <c r="K43" s="3">
         <v>884900</v>
       </c>
-      <c r="K43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L43" s="3" t="s">
         <v>3</v>
       </c>
@@ -1994,35 +2086,38 @@
       <c r="O43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>12763700</v>
+        <v>16824000</v>
       </c>
       <c r="E44" s="3">
-        <v>13160400</v>
+        <v>12082000</v>
       </c>
       <c r="F44" s="3">
-        <v>12076500</v>
+        <v>12457400</v>
       </c>
       <c r="G44" s="3">
-        <v>10376900</v>
+        <v>11431500</v>
       </c>
       <c r="H44" s="3">
-        <v>9872700</v>
+        <v>9822600</v>
       </c>
       <c r="I44" s="3">
-        <v>10268700</v>
+        <v>9345400</v>
       </c>
       <c r="J44" s="3">
+        <v>9720300</v>
+      </c>
+      <c r="K44" s="3">
         <v>8118200</v>
       </c>
-      <c r="K44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L44" s="3" t="s">
         <v>3</v>
       </c>
@@ -2035,35 +2130,38 @@
       <c r="O44" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="45" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P44" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>907400</v>
+        <v>1173500</v>
       </c>
       <c r="E45" s="3">
-        <v>941100</v>
+        <v>859000</v>
       </c>
       <c r="F45" s="3">
-        <v>897100</v>
+        <v>890800</v>
       </c>
       <c r="G45" s="3">
-        <v>916500</v>
+        <v>849200</v>
       </c>
       <c r="H45" s="3">
-        <v>945000</v>
+        <v>867600</v>
       </c>
       <c r="I45" s="3">
-        <v>929600</v>
+        <v>894500</v>
       </c>
       <c r="J45" s="3">
+        <v>880000</v>
+      </c>
+      <c r="K45" s="3">
         <v>685300</v>
       </c>
-      <c r="K45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L45" s="3" t="s">
         <v>3</v>
       </c>
@@ -2076,35 +2174,38 @@
       <c r="O45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>16829400</v>
+        <v>21649100</v>
       </c>
       <c r="E46" s="3">
-        <v>17248600</v>
+        <v>15930500</v>
       </c>
       <c r="F46" s="3">
-        <v>15989800</v>
+        <v>16327300</v>
       </c>
       <c r="G46" s="3">
-        <v>14378400</v>
+        <v>15135700</v>
       </c>
       <c r="H46" s="3">
-        <v>14112800</v>
+        <v>13610400</v>
       </c>
       <c r="I46" s="3">
-        <v>14499500</v>
+        <v>13359000</v>
       </c>
       <c r="J46" s="3">
+        <v>13725100</v>
+      </c>
+      <c r="K46" s="3">
         <v>13161400</v>
       </c>
-      <c r="K46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L46" s="3" t="s">
         <v>3</v>
       </c>
@@ -2117,35 +2218,38 @@
       <c r="O46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>1351600</v>
+        <v>1347700</v>
       </c>
       <c r="E47" s="3">
-        <v>1375900</v>
+        <v>1279400</v>
       </c>
       <c r="F47" s="3">
-        <v>1434800</v>
+        <v>1302400</v>
       </c>
       <c r="G47" s="3">
-        <v>1339100</v>
+        <v>1358200</v>
       </c>
       <c r="H47" s="3">
-        <v>1313800</v>
+        <v>1267600</v>
       </c>
       <c r="I47" s="3">
-        <v>1336600</v>
+        <v>1243700</v>
       </c>
       <c r="J47" s="3">
+        <v>1265200</v>
+      </c>
+      <c r="K47" s="3">
         <v>1319900</v>
       </c>
-      <c r="K47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L47" s="3" t="s">
         <v>3</v>
       </c>
@@ -2158,35 +2262,38 @@
       <c r="O47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>3344700</v>
+        <v>3367300</v>
       </c>
       <c r="E48" s="3">
-        <v>3418100</v>
+        <v>3166100</v>
       </c>
       <c r="F48" s="3">
-        <v>3614600</v>
+        <v>3235500</v>
       </c>
       <c r="G48" s="3">
-        <v>3786200</v>
+        <v>3421500</v>
       </c>
       <c r="H48" s="3">
-        <v>3737700</v>
+        <v>3584000</v>
       </c>
       <c r="I48" s="3">
-        <v>3892400</v>
+        <v>3538100</v>
       </c>
       <c r="J48" s="3">
+        <v>3684500</v>
+      </c>
+      <c r="K48" s="3">
         <v>3644400</v>
       </c>
-      <c r="K48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L48" s="3" t="s">
         <v>3</v>
       </c>
@@ -2199,35 +2306,38 @@
       <c r="O48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>272200</v>
+        <v>1398800</v>
       </c>
       <c r="E49" s="3">
-        <v>279500</v>
+        <v>257700</v>
       </c>
       <c r="F49" s="3">
-        <v>286300</v>
+        <v>264500</v>
       </c>
       <c r="G49" s="3">
-        <v>282800</v>
+        <v>271000</v>
       </c>
       <c r="H49" s="3">
-        <v>344500</v>
+        <v>267700</v>
       </c>
       <c r="I49" s="3">
-        <v>371300</v>
+        <v>326100</v>
       </c>
       <c r="J49" s="3">
+        <v>351500</v>
+      </c>
+      <c r="K49" s="3">
         <v>121200</v>
       </c>
-      <c r="K49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L49" s="3" t="s">
         <v>3</v>
       </c>
@@ -2240,8 +2350,11 @@
       <c r="O49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2281,8 +2394,11 @@
       <c r="O50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2322,35 +2438,38 @@
       <c r="O51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>799900</v>
+        <v>713300</v>
       </c>
       <c r="E52" s="3">
-        <v>793700</v>
+        <v>757100</v>
       </c>
       <c r="F52" s="3">
-        <v>758800</v>
+        <v>751300</v>
       </c>
       <c r="G52" s="3">
-        <v>747700</v>
+        <v>718300</v>
       </c>
       <c r="H52" s="3">
-        <v>761900</v>
+        <v>707800</v>
       </c>
       <c r="I52" s="3">
-        <v>651800</v>
+        <v>721200</v>
       </c>
       <c r="J52" s="3">
+        <v>617000</v>
+      </c>
+      <c r="K52" s="3">
         <v>633100</v>
       </c>
-      <c r="K52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L52" s="3" t="s">
         <v>3</v>
       </c>
@@ -2363,8 +2482,11 @@
       <c r="O52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2404,35 +2526,38 @@
       <c r="O53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>22597900</v>
+        <v>28476300</v>
       </c>
       <c r="E54" s="3">
-        <v>23115700</v>
+        <v>21390900</v>
       </c>
       <c r="F54" s="3">
-        <v>22084300</v>
+        <v>21881100</v>
       </c>
       <c r="G54" s="3">
-        <v>20534200</v>
+        <v>20904700</v>
       </c>
       <c r="H54" s="3">
-        <v>20270800</v>
+        <v>19437400</v>
       </c>
       <c r="I54" s="3">
-        <v>20751700</v>
+        <v>19188100</v>
       </c>
       <c r="J54" s="3">
+        <v>19643300</v>
+      </c>
+      <c r="K54" s="3">
         <v>18880000</v>
       </c>
-      <c r="K54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L54" s="3" t="s">
         <v>3</v>
       </c>
@@ -2445,8 +2570,11 @@
       <c r="O54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2462,8 +2590,9 @@
       <c r="M55" s="3"/>
       <c r="N55" s="3"/>
       <c r="O55" s="3"/>
-    </row>
-    <row r="56" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P55" s="3"/>
+    </row>
+    <row r="56" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2479,35 +2608,36 @@
       <c r="M56" s="3"/>
       <c r="N56" s="3"/>
       <c r="O56" s="3"/>
-    </row>
-    <row r="57" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P56" s="3"/>
+    </row>
+    <row r="57" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>1599300</v>
+        <v>1445000</v>
       </c>
       <c r="E57" s="3">
-        <v>1499800</v>
+        <v>1513900</v>
       </c>
       <c r="F57" s="3">
-        <v>1522600</v>
+        <v>1419700</v>
       </c>
       <c r="G57" s="3">
-        <v>1439400</v>
+        <v>1441300</v>
       </c>
       <c r="H57" s="3">
-        <v>1528900</v>
+        <v>1362500</v>
       </c>
       <c r="I57" s="3">
-        <v>1505600</v>
+        <v>1447200</v>
       </c>
       <c r="J57" s="3">
+        <v>1425200</v>
+      </c>
+      <c r="K57" s="3">
         <v>1399600</v>
       </c>
-      <c r="K57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L57" s="3" t="s">
         <v>3</v>
       </c>
@@ -2520,35 +2650,38 @@
       <c r="O57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>3111900</v>
+        <v>8037500</v>
       </c>
       <c r="E58" s="3">
-        <v>4016500</v>
+        <v>2959600</v>
       </c>
       <c r="F58" s="3">
-        <v>3113800</v>
+        <v>3802000</v>
       </c>
       <c r="G58" s="3">
-        <v>3266900</v>
+        <v>2947500</v>
       </c>
       <c r="H58" s="3">
-        <v>2759100</v>
+        <v>3092400</v>
       </c>
       <c r="I58" s="3">
-        <v>3279200</v>
+        <v>2611800</v>
       </c>
       <c r="J58" s="3">
+        <v>3104000</v>
+      </c>
+      <c r="K58" s="3">
         <v>1593600</v>
       </c>
-      <c r="K58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L58" s="3" t="s">
         <v>3</v>
       </c>
@@ -2561,35 +2694,38 @@
       <c r="O58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>2959200</v>
+        <v>2994200</v>
       </c>
       <c r="E59" s="3">
-        <v>2912300</v>
+        <v>2787200</v>
       </c>
       <c r="F59" s="3">
-        <v>2770900</v>
+        <v>2756800</v>
       </c>
       <c r="G59" s="3">
-        <v>2566000</v>
+        <v>2622900</v>
       </c>
       <c r="H59" s="3">
-        <v>2752900</v>
+        <v>2428900</v>
       </c>
       <c r="I59" s="3">
-        <v>2636900</v>
+        <v>2605800</v>
       </c>
       <c r="J59" s="3">
+        <v>2496000</v>
+      </c>
+      <c r="K59" s="3">
         <v>2856500</v>
       </c>
-      <c r="K59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L59" s="3" t="s">
         <v>3</v>
       </c>
@@ -2602,35 +2738,38 @@
       <c r="O59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>7670400</v>
+        <v>12476700</v>
       </c>
       <c r="E60" s="3">
-        <v>8428600</v>
+        <v>7260700</v>
       </c>
       <c r="F60" s="3">
-        <v>7407400</v>
+        <v>7978500</v>
       </c>
       <c r="G60" s="3">
-        <v>7272300</v>
+        <v>7011700</v>
       </c>
       <c r="H60" s="3">
-        <v>7040900</v>
+        <v>6883800</v>
       </c>
       <c r="I60" s="3">
-        <v>7421600</v>
+        <v>6664800</v>
       </c>
       <c r="J60" s="3">
+        <v>7025200</v>
+      </c>
+      <c r="K60" s="3">
         <v>5849700</v>
       </c>
-      <c r="K60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L60" s="3" t="s">
         <v>3</v>
       </c>
@@ -2643,35 +2782,38 @@
       <c r="O60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>1948500</v>
+        <v>3146900</v>
       </c>
       <c r="E61" s="3">
-        <v>1932700</v>
+        <v>1984700</v>
       </c>
       <c r="F61" s="3">
-        <v>1973900</v>
+        <v>1829500</v>
       </c>
       <c r="G61" s="3">
-        <v>1144000</v>
+        <v>1868400</v>
       </c>
       <c r="H61" s="3">
-        <v>1333400</v>
+        <v>1082900</v>
       </c>
       <c r="I61" s="3">
-        <v>1208300</v>
+        <v>1262100</v>
       </c>
       <c r="J61" s="3">
+        <v>1143800</v>
+      </c>
+      <c r="K61" s="3">
         <v>2112500</v>
       </c>
-      <c r="K61" s="3">
-        <v>0</v>
-      </c>
       <c r="L61" s="3">
         <v>0</v>
       </c>
@@ -2684,35 +2826,38 @@
       <c r="O61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>887100</v>
+        <v>1093600</v>
       </c>
       <c r="E62" s="3">
-        <v>831300</v>
+        <v>699500</v>
       </c>
       <c r="F62" s="3">
-        <v>837600</v>
+        <v>786900</v>
       </c>
       <c r="G62" s="3">
-        <v>814700</v>
+        <v>792900</v>
       </c>
       <c r="H62" s="3">
-        <v>657300</v>
+        <v>771200</v>
       </c>
       <c r="I62" s="3">
-        <v>789800</v>
+        <v>622200</v>
       </c>
       <c r="J62" s="3">
+        <v>747600</v>
+      </c>
+      <c r="K62" s="3">
         <v>666600</v>
       </c>
-      <c r="K62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L62" s="3" t="s">
         <v>3</v>
       </c>
@@ -2725,8 +2870,11 @@
       <c r="O62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2766,8 +2914,11 @@
       <c r="O63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2807,8 +2958,11 @@
       <c r="O64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2848,35 +3002,38 @@
       <c r="O65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>10771300</v>
+        <v>16996100</v>
       </c>
       <c r="E66" s="3">
-        <v>11456800</v>
+        <v>10196000</v>
       </c>
       <c r="F66" s="3">
-        <v>10476300</v>
+        <v>10844800</v>
       </c>
       <c r="G66" s="3">
-        <v>9471200</v>
+        <v>9916700</v>
       </c>
       <c r="H66" s="3">
-        <v>9264600</v>
+        <v>8965300</v>
       </c>
       <c r="I66" s="3">
-        <v>9779300</v>
+        <v>8769800</v>
       </c>
       <c r="J66" s="3">
+        <v>9257000</v>
+      </c>
+      <c r="K66" s="3">
         <v>8944400</v>
       </c>
-      <c r="K66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L66" s="3" t="s">
         <v>3</v>
       </c>
@@ -2889,8 +3046,11 @@
       <c r="O66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2906,8 +3066,9 @@
       <c r="M67" s="3"/>
       <c r="N67" s="3"/>
       <c r="O67" s="3"/>
-    </row>
-    <row r="68" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P67" s="3"/>
+    </row>
+    <row r="68" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2947,8 +3108,11 @@
       <c r="O68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2988,8 +3152,11 @@
       <c r="O69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3029,8 +3196,11 @@
       <c r="O70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3070,35 +3240,38 @@
       <c r="O71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>7632200</v>
+        <v>7281600</v>
       </c>
       <c r="E72" s="3">
-        <v>7225100</v>
+        <v>7224600</v>
       </c>
       <c r="F72" s="3">
-        <v>7151300</v>
+        <v>6839200</v>
       </c>
       <c r="G72" s="3">
-        <v>6810500</v>
+        <v>6769300</v>
       </c>
       <c r="H72" s="3">
-        <v>7121500</v>
+        <v>6446800</v>
       </c>
       <c r="I72" s="3">
-        <v>6888000</v>
+        <v>6741200</v>
       </c>
       <c r="J72" s="3">
+        <v>6520100</v>
+      </c>
+      <c r="K72" s="3">
         <v>6337800</v>
       </c>
-      <c r="K72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L72" s="3" t="s">
         <v>3</v>
       </c>
@@ -3111,8 +3284,11 @@
       <c r="O72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3152,8 +3328,11 @@
       <c r="O73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3193,8 +3372,11 @@
       <c r="O74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3234,35 +3416,38 @@
       <c r="O75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>11826600</v>
+        <v>11480200</v>
       </c>
       <c r="E76" s="3">
-        <v>11659000</v>
+        <v>11194900</v>
       </c>
       <c r="F76" s="3">
-        <v>11608000</v>
+        <v>11036200</v>
       </c>
       <c r="G76" s="3">
-        <v>11063000</v>
+        <v>10988000</v>
       </c>
       <c r="H76" s="3">
-        <v>11006200</v>
+        <v>10472100</v>
       </c>
       <c r="I76" s="3">
-        <v>10972400</v>
+        <v>10418300</v>
       </c>
       <c r="J76" s="3">
+        <v>10386300</v>
+      </c>
+      <c r="K76" s="3">
         <v>9935600</v>
       </c>
-      <c r="K76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L76" s="3" t="s">
         <v>3</v>
       </c>
@@ -3275,8 +3460,11 @@
       <c r="O76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3316,40 +3504,43 @@
       <c r="O77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45412</v>
+      </c>
+      <c r="E80" s="2">
         <v>45322</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45230</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45138</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45046</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44957</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44865</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44592</v>
       </c>
-      <c r="K80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="L80" s="2" t="s">
         <v>3</v>
       </c>
@@ -3362,35 +3553,38 @@
       <c r="O80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>407300</v>
+        <v>321700</v>
       </c>
       <c r="E81" s="3">
-        <v>332900</v>
+        <v>385600</v>
       </c>
       <c r="F81" s="3">
-        <v>340800</v>
+        <v>315100</v>
       </c>
       <c r="G81" s="3">
-        <v>282600</v>
+        <v>322600</v>
       </c>
       <c r="H81" s="3">
-        <v>233900</v>
+        <v>267500</v>
       </c>
       <c r="I81" s="3">
-        <v>308300</v>
+        <v>221400</v>
       </c>
       <c r="J81" s="3">
+        <v>291900</v>
+      </c>
+      <c r="K81" s="3">
         <v>256200</v>
       </c>
-      <c r="K81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L81" s="3" t="s">
         <v>3</v>
       </c>
@@ -3403,8 +3597,11 @@
       <c r="O81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3420,25 +3617,26 @@
       <c r="M82" s="3"/>
       <c r="N82" s="3"/>
       <c r="O82" s="3"/>
-    </row>
-    <row r="83" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P82" s="3"/>
+    </row>
+    <row r="83" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>28600</v>
+        <v>48900</v>
       </c>
       <c r="E83" s="3">
-        <v>62700</v>
+        <v>27000</v>
       </c>
       <c r="F83" s="3">
-        <v>47600</v>
+        <v>59400</v>
       </c>
       <c r="G83" s="3">
-        <v>48200</v>
-      </c>
-      <c r="H83" s="3" t="s">
-        <v>3</v>
+        <v>45000</v>
+      </c>
+      <c r="H83" s="3">
+        <v>45600</v>
       </c>
       <c r="I83" s="3" t="s">
         <v>3</v>
@@ -3455,14 +3653,17 @@
       <c r="M83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N83" s="3">
-        <v>0</v>
+      <c r="N83" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="O83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3502,8 +3703,11 @@
       <c r="O84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3543,8 +3747,11 @@
       <c r="O85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3584,8 +3791,11 @@
       <c r="O86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3625,8 +3835,11 @@
       <c r="O87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3666,31 +3879,34 @@
       <c r="O88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="D89" s="3">
-        <v>0</v>
-      </c>
-      <c r="E89" s="3">
-        <v>0</v>
-      </c>
-      <c r="F89" s="3">
-        <v>0</v>
-      </c>
-      <c r="G89" s="3">
-        <v>0</v>
-      </c>
-      <c r="H89" s="3">
-        <v>0</v>
-      </c>
-      <c r="I89" s="3">
-        <v>0</v>
-      </c>
-      <c r="J89" s="3">
-        <v>0</v>
+      <c r="D89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J89" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K89" s="3">
         <v>0</v>
@@ -3707,8 +3923,11 @@
       <c r="O89" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="90" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P89" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3724,8 +3943,9 @@
       <c r="M90" s="3"/>
       <c r="N90" s="3"/>
       <c r="O90" s="3"/>
-    </row>
-    <row r="91" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P90" s="3"/>
+    </row>
+    <row r="91" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -3736,7 +3956,7 @@
         <v>-37604000</v>
       </c>
       <c r="F91" s="3">
-        <v>0</v>
+        <v>-92162000</v>
       </c>
       <c r="G91" s="3">
         <v>0</v>
@@ -3765,8 +3985,11 @@
       <c r="O91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3806,8 +4029,11 @@
       <c r="O92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3847,31 +4073,34 @@
       <c r="O93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="D94" s="3">
-        <v>0</v>
-      </c>
-      <c r="E94" s="3">
-        <v>0</v>
-      </c>
-      <c r="F94" s="3">
-        <v>0</v>
-      </c>
-      <c r="G94" s="3">
-        <v>0</v>
-      </c>
-      <c r="H94" s="3">
-        <v>0</v>
-      </c>
-      <c r="I94" s="3">
-        <v>0</v>
-      </c>
-      <c r="J94" s="3">
-        <v>0</v>
+      <c r="D94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J94" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K94" s="3">
         <v>0</v>
@@ -3888,8 +4117,11 @@
       <c r="O94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3905,8 +4137,9 @@
       <c r="M95" s="3"/>
       <c r="N95" s="3"/>
       <c r="O95" s="3"/>
-    </row>
-    <row r="96" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P95" s="3"/>
+    </row>
+    <row r="96" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -3946,8 +4179,11 @@
       <c r="O96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3987,8 +4223,11 @@
       <c r="O97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4028,8 +4267,11 @@
       <c r="O98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4069,31 +4311,34 @@
       <c r="O99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="D100" s="3">
-        <v>0</v>
-      </c>
-      <c r="E100" s="3">
-        <v>0</v>
-      </c>
-      <c r="F100" s="3">
-        <v>0</v>
-      </c>
-      <c r="G100" s="3">
-        <v>0</v>
-      </c>
-      <c r="H100" s="3">
-        <v>0</v>
-      </c>
-      <c r="I100" s="3">
-        <v>0</v>
-      </c>
-      <c r="J100" s="3">
-        <v>0</v>
+      <c r="D100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J100" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K100" s="3">
         <v>0</v>
@@ -4110,31 +4355,34 @@
       <c r="O100" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="101" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3">
-        <v>0</v>
-      </c>
-      <c r="E101" s="3">
-        <v>0</v>
-      </c>
-      <c r="F101" s="3">
-        <v>0</v>
-      </c>
-      <c r="G101" s="3">
-        <v>0</v>
-      </c>
-      <c r="H101" s="3">
-        <v>0</v>
-      </c>
-      <c r="I101" s="3">
-        <v>0</v>
-      </c>
-      <c r="J101" s="3">
-        <v>0</v>
+      <c r="D101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K101" s="3">
         <v>0</v>
@@ -4151,31 +4399,34 @@
       <c r="O101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="D102" s="3">
-        <v>0</v>
-      </c>
-      <c r="E102" s="3">
-        <v>0</v>
-      </c>
-      <c r="F102" s="3">
-        <v>0</v>
-      </c>
-      <c r="G102" s="3">
-        <v>0</v>
-      </c>
-      <c r="H102" s="3">
-        <v>0</v>
-      </c>
-      <c r="I102" s="3">
-        <v>0</v>
-      </c>
-      <c r="J102" s="3">
-        <v>0</v>
+      <c r="D102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J102" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K102" s="3">
         <v>0</v>
@@ -4190,6 +4441,9 @@
         <v>0</v>
       </c>
       <c r="O102" s="3">
+        <v>0</v>
+      </c>
+      <c r="P102" s="3">
         <v>0</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/SKHSY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/SKHSY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="348" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="319" uniqueCount="92">
   <si>
     <t>SKHSY</t>
   </si>
@@ -656,59 +656,59 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:P102"/>
+  <dimension ref="A5:Q102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="6" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="16" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="7" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="17" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45504</v>
+      </c>
+      <c r="E7" s="2">
         <v>45412</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45322</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45230</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45138</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45046</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44957</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44865</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44592</v>
       </c>
-      <c r="L7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="M7" s="2" t="s">
         <v>3</v>
       </c>
@@ -721,38 +721,41 @@
       <c r="P7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
-        <v>4957600</v>
+        <v>7682700</v>
       </c>
       <c r="E8" s="3">
-        <v>5855100</v>
+        <v>5517100</v>
       </c>
       <c r="F8" s="3">
-        <v>4638700</v>
+        <v>6515900</v>
       </c>
       <c r="G8" s="3">
-        <v>4811600</v>
+        <v>5162200</v>
       </c>
       <c r="H8" s="3">
-        <v>4518800</v>
+        <v>5354600</v>
       </c>
       <c r="I8" s="3">
-        <v>5096100</v>
+        <v>5028800</v>
       </c>
       <c r="J8" s="3">
+        <v>5671200</v>
+      </c>
+      <c r="K8" s="3">
         <v>4507100</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>5019700</v>
       </c>
-      <c r="L8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M8" s="3" t="s">
         <v>3</v>
       </c>
@@ -765,38 +768,41 @@
       <c r="P8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
-        <v>3930100</v>
+        <v>6259000</v>
       </c>
       <c r="E9" s="3">
-        <v>4698900</v>
+        <v>4373600</v>
       </c>
       <c r="F9" s="3">
-        <v>3687100</v>
+        <v>5229100</v>
       </c>
       <c r="G9" s="3">
-        <v>3820700</v>
+        <v>4103200</v>
       </c>
       <c r="H9" s="3">
-        <v>3638100</v>
+        <v>4251800</v>
       </c>
       <c r="I9" s="3">
-        <v>4164000</v>
+        <v>4048600</v>
       </c>
       <c r="J9" s="3">
+        <v>4633900</v>
+      </c>
+      <c r="K9" s="3">
         <v>3635800</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>4041200</v>
       </c>
-      <c r="L9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M9" s="3" t="s">
         <v>3</v>
       </c>
@@ -809,38 +815,41 @@
       <c r="P9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
-        <v>1027500</v>
+        <v>1423800</v>
       </c>
       <c r="E10" s="3">
-        <v>1156300</v>
+        <v>1143400</v>
       </c>
       <c r="F10" s="3">
-        <v>951500</v>
+        <v>1286800</v>
       </c>
       <c r="G10" s="3">
-        <v>990900</v>
+        <v>1058900</v>
       </c>
       <c r="H10" s="3">
-        <v>880800</v>
+        <v>1102700</v>
       </c>
       <c r="I10" s="3">
-        <v>932100</v>
+        <v>980200</v>
       </c>
       <c r="J10" s="3">
+        <v>1037300</v>
+      </c>
+      <c r="K10" s="3">
         <v>871300</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>978500</v>
       </c>
-      <c r="L10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M10" s="3" t="s">
         <v>3</v>
       </c>
@@ -853,8 +862,11 @@
       <c r="P10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -871,8 +883,9 @@
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q11" s="3"/>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -915,8 +928,11 @@
       <c r="P12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -959,38 +975,41 @@
       <c r="P13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>24000</v>
+      </c>
+      <c r="E14" s="3">
         <v>100</v>
       </c>
-      <c r="E14" s="3">
-        <v>-39200</v>
-      </c>
       <c r="F14" s="3">
-        <v>-14700</v>
+        <v>-43600</v>
       </c>
       <c r="G14" s="3">
-        <v>700</v>
+        <v>-16300</v>
       </c>
       <c r="H14" s="3">
-        <v>-51600</v>
+        <v>800</v>
       </c>
       <c r="I14" s="3">
-        <v>17500</v>
+        <v>-57400</v>
       </c>
       <c r="J14" s="3">
+        <v>19500</v>
+      </c>
+      <c r="K14" s="3">
         <v>-54000</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>3000</v>
       </c>
-      <c r="L14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1003,8 +1022,11 @@
       <c r="P14" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q14" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1047,8 +1069,11 @@
       <c r="P15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1062,38 +1087,39 @@
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
-    </row>
-    <row r="17" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q16" s="3"/>
+    </row>
+    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>4500100</v>
+        <v>7100200</v>
       </c>
       <c r="E17" s="3">
-        <v>5278300</v>
+        <v>5008000</v>
       </c>
       <c r="F17" s="3">
-        <v>4229900</v>
+        <v>5874000</v>
       </c>
       <c r="G17" s="3">
-        <v>4370900</v>
+        <v>4707300</v>
       </c>
       <c r="H17" s="3">
-        <v>4111600</v>
+        <v>4864200</v>
       </c>
       <c r="I17" s="3">
-        <v>4737200</v>
+        <v>4575600</v>
       </c>
       <c r="J17" s="3">
+        <v>5271800</v>
+      </c>
+      <c r="K17" s="3">
         <v>4095300</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>4605300</v>
       </c>
-      <c r="L17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M17" s="3" t="s">
         <v>3</v>
       </c>
@@ -1106,38 +1132,41 @@
       <c r="P17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>457500</v>
+        <v>582500</v>
       </c>
       <c r="E18" s="3">
-        <v>576800</v>
+        <v>509100</v>
       </c>
       <c r="F18" s="3">
-        <v>408700</v>
+        <v>641900</v>
       </c>
       <c r="G18" s="3">
-        <v>440700</v>
+        <v>454900</v>
       </c>
       <c r="H18" s="3">
-        <v>407200</v>
+        <v>490400</v>
       </c>
       <c r="I18" s="3">
-        <v>358800</v>
+        <v>453200</v>
       </c>
       <c r="J18" s="3">
+        <v>399300</v>
+      </c>
+      <c r="K18" s="3">
         <v>411700</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>414400</v>
       </c>
-      <c r="L18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1150,8 +1179,11 @@
       <c r="P18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1168,38 +1200,39 @@
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
-    </row>
-    <row r="20" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q19" s="3"/>
+    </row>
+    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>25000</v>
+        <v>127200</v>
       </c>
       <c r="E20" s="3">
-        <v>15900</v>
+        <v>27800</v>
       </c>
       <c r="F20" s="3">
-        <v>26200</v>
+        <v>17700</v>
       </c>
       <c r="G20" s="3">
-        <v>45000</v>
+        <v>29100</v>
       </c>
       <c r="H20" s="3">
-        <v>2000</v>
+        <v>50100</v>
       </c>
       <c r="I20" s="3">
-        <v>-19200</v>
+        <v>2200</v>
       </c>
       <c r="J20" s="3">
+        <v>-21300</v>
+      </c>
+      <c r="K20" s="3">
         <v>1900</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>5800</v>
       </c>
-      <c r="L20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M20" s="3" t="s">
         <v>3</v>
       </c>
@@ -1212,28 +1245,31 @@
       <c r="P20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>531300</v>
+        <v>766700</v>
       </c>
       <c r="E21" s="3">
-        <v>619700</v>
+        <v>591300</v>
       </c>
       <c r="F21" s="3">
-        <v>494300</v>
+        <v>689700</v>
       </c>
       <c r="G21" s="3">
-        <v>530700</v>
+        <v>550100</v>
       </c>
       <c r="H21" s="3">
-        <v>454800</v>
-      </c>
-      <c r="I21" s="3" t="s">
-        <v>3</v>
+        <v>590600</v>
+      </c>
+      <c r="I21" s="3">
+        <v>506100</v>
       </c>
       <c r="J21" s="3" t="s">
         <v>3</v>
@@ -1256,38 +1292,41 @@
       <c r="P21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>30300</v>
+        <v>64500</v>
       </c>
       <c r="E22" s="3">
-        <v>22900</v>
+        <v>33800</v>
       </c>
       <c r="F22" s="3">
-        <v>23200</v>
+        <v>25400</v>
       </c>
       <c r="G22" s="3">
-        <v>16700</v>
+        <v>25900</v>
       </c>
       <c r="H22" s="3">
-        <v>16100</v>
+        <v>18600</v>
       </c>
       <c r="I22" s="3">
-        <v>12200</v>
+        <v>17900</v>
       </c>
       <c r="J22" s="3">
+        <v>13600</v>
+      </c>
+      <c r="K22" s="3">
         <v>10600</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>10700</v>
       </c>
-      <c r="L22" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M22" s="3" t="s">
         <v>3</v>
       </c>
@@ -1300,38 +1339,41 @@
       <c r="P22" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>452100</v>
+        <v>645300</v>
       </c>
       <c r="E23" s="3">
-        <v>569900</v>
+        <v>503100</v>
       </c>
       <c r="F23" s="3">
-        <v>411700</v>
+        <v>634200</v>
       </c>
       <c r="G23" s="3">
-        <v>469000</v>
+        <v>458100</v>
       </c>
       <c r="H23" s="3">
-        <v>393100</v>
+        <v>521900</v>
       </c>
       <c r="I23" s="3">
-        <v>327500</v>
+        <v>437400</v>
       </c>
       <c r="J23" s="3">
+        <v>364400</v>
+      </c>
+      <c r="K23" s="3">
         <v>403100</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>409500</v>
       </c>
-      <c r="L23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M23" s="3" t="s">
         <v>3</v>
       </c>
@@ -1344,38 +1386,41 @@
       <c r="P23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>124200</v>
+        <v>123900</v>
       </c>
       <c r="E24" s="3">
-        <v>167700</v>
+        <v>138200</v>
       </c>
       <c r="F24" s="3">
-        <v>93500</v>
+        <v>186700</v>
       </c>
       <c r="G24" s="3">
-        <v>140600</v>
+        <v>104000</v>
       </c>
       <c r="H24" s="3">
-        <v>117700</v>
+        <v>156500</v>
       </c>
       <c r="I24" s="3">
-        <v>102000</v>
+        <v>131000</v>
       </c>
       <c r="J24" s="3">
+        <v>113500</v>
+      </c>
+      <c r="K24" s="3">
         <v>106400</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>134300</v>
       </c>
-      <c r="L24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M24" s="3" t="s">
         <v>3</v>
       </c>
@@ -1388,8 +1433,11 @@
       <c r="P24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1432,38 +1480,41 @@
       <c r="P25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>328000</v>
+        <v>521500</v>
       </c>
       <c r="E26" s="3">
-        <v>402100</v>
+        <v>365000</v>
       </c>
       <c r="F26" s="3">
-        <v>318200</v>
+        <v>447500</v>
       </c>
       <c r="G26" s="3">
-        <v>328400</v>
+        <v>354100</v>
       </c>
       <c r="H26" s="3">
-        <v>275300</v>
+        <v>365400</v>
       </c>
       <c r="I26" s="3">
-        <v>225500</v>
+        <v>306400</v>
       </c>
       <c r="J26" s="3">
+        <v>250900</v>
+      </c>
+      <c r="K26" s="3">
         <v>296700</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>275100</v>
       </c>
-      <c r="L26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M26" s="3" t="s">
         <v>3</v>
       </c>
@@ -1476,38 +1527,41 @@
       <c r="P26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>321700</v>
+        <v>515100</v>
       </c>
       <c r="E27" s="3">
-        <v>385600</v>
+        <v>358000</v>
       </c>
       <c r="F27" s="3">
-        <v>315100</v>
+        <v>429100</v>
       </c>
       <c r="G27" s="3">
-        <v>322600</v>
+        <v>350700</v>
       </c>
       <c r="H27" s="3">
-        <v>267500</v>
+        <v>359000</v>
       </c>
       <c r="I27" s="3">
-        <v>221400</v>
+        <v>297700</v>
       </c>
       <c r="J27" s="3">
+        <v>246400</v>
+      </c>
+      <c r="K27" s="3">
         <v>291900</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>256200</v>
       </c>
-      <c r="L27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M27" s="3" t="s">
         <v>3</v>
       </c>
@@ -1520,8 +1574,11 @@
       <c r="P27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1564,8 +1621,11 @@
       <c r="P28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1608,8 +1668,11 @@
       <c r="P29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1652,8 +1715,11 @@
       <c r="P30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1696,38 +1762,41 @@
       <c r="P31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-25000</v>
+        <v>-127200</v>
       </c>
       <c r="E32" s="3">
-        <v>-15900</v>
+        <v>-27800</v>
       </c>
       <c r="F32" s="3">
-        <v>-26200</v>
+        <v>-17700</v>
       </c>
       <c r="G32" s="3">
-        <v>-45000</v>
+        <v>-29100</v>
       </c>
       <c r="H32" s="3">
-        <v>-2000</v>
+        <v>-50100</v>
       </c>
       <c r="I32" s="3">
-        <v>19200</v>
+        <v>-2200</v>
       </c>
       <c r="J32" s="3">
+        <v>21300</v>
+      </c>
+      <c r="K32" s="3">
         <v>-1900</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-5800</v>
       </c>
-      <c r="L32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M32" s="3" t="s">
         <v>3</v>
       </c>
@@ -1740,38 +1809,41 @@
       <c r="P32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>321700</v>
+        <v>515100</v>
       </c>
       <c r="E33" s="3">
-        <v>385600</v>
+        <v>358000</v>
       </c>
       <c r="F33" s="3">
-        <v>315100</v>
+        <v>429100</v>
       </c>
       <c r="G33" s="3">
-        <v>322600</v>
+        <v>350700</v>
       </c>
       <c r="H33" s="3">
-        <v>267500</v>
+        <v>359000</v>
       </c>
       <c r="I33" s="3">
-        <v>221400</v>
+        <v>297700</v>
       </c>
       <c r="J33" s="3">
+        <v>246400</v>
+      </c>
+      <c r="K33" s="3">
         <v>291900</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>256200</v>
       </c>
-      <c r="L33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M33" s="3" t="s">
         <v>3</v>
       </c>
@@ -1784,8 +1856,11 @@
       <c r="P33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1828,38 +1903,41 @@
       <c r="P34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>321700</v>
+        <v>515100</v>
       </c>
       <c r="E35" s="3">
-        <v>385600</v>
+        <v>358000</v>
       </c>
       <c r="F35" s="3">
-        <v>315100</v>
+        <v>429100</v>
       </c>
       <c r="G35" s="3">
-        <v>322600</v>
+        <v>350700</v>
       </c>
       <c r="H35" s="3">
-        <v>267500</v>
+        <v>359000</v>
       </c>
       <c r="I35" s="3">
-        <v>221400</v>
+        <v>297700</v>
       </c>
       <c r="J35" s="3">
+        <v>246400</v>
+      </c>
+      <c r="K35" s="3">
         <v>291900</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>256200</v>
       </c>
-      <c r="L35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M35" s="3" t="s">
         <v>3</v>
       </c>
@@ -1872,43 +1950,46 @@
       <c r="P35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45504</v>
+      </c>
+      <c r="E38" s="2">
         <v>45412</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45322</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45230</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45138</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45046</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44957</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44865</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44592</v>
       </c>
-      <c r="L38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="M38" s="2" t="s">
         <v>3</v>
       </c>
@@ -1921,8 +2002,11 @@
       <c r="P38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1939,8 +2023,9 @@
       <c r="N39" s="3"/>
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
-    </row>
-    <row r="40" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q39" s="3"/>
+    </row>
+    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1957,38 +2042,39 @@
       <c r="N40" s="3"/>
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
-    </row>
-    <row r="41" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q40" s="3"/>
+    </row>
+    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>2475300</v>
+        <v>3066100</v>
       </c>
       <c r="E41" s="3">
-        <v>1870300</v>
+        <v>2754600</v>
       </c>
       <c r="F41" s="3">
-        <v>2004300</v>
+        <v>2081400</v>
       </c>
       <c r="G41" s="3">
-        <v>1944100</v>
+        <v>2230500</v>
       </c>
       <c r="H41" s="3">
-        <v>1934900</v>
+        <v>2163500</v>
       </c>
       <c r="I41" s="3">
-        <v>2123900</v>
+        <v>2153200</v>
       </c>
       <c r="J41" s="3">
+        <v>2363600</v>
+      </c>
+      <c r="K41" s="3">
         <v>2165300</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>3473000</v>
       </c>
-      <c r="L41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2001,16 +2087,19 @@
       <c r="P41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>78400</v>
-      </c>
-      <c r="E42" s="3" t="s">
-        <v>3</v>
+        <v>203300</v>
+      </c>
+      <c r="E42" s="3">
+        <v>87300</v>
       </c>
       <c r="F42" s="3" t="s">
         <v>3</v>
@@ -2027,8 +2116,8 @@
       <c r="J42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K42" s="3">
-        <v>0</v>
+      <c r="K42" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L42" s="3">
         <v>0</v>
@@ -2045,38 +2134,41 @@
       <c r="P42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>1098000</v>
+        <v>1252500</v>
       </c>
       <c r="E43" s="3">
-        <v>1119300</v>
+        <v>1221900</v>
       </c>
       <c r="F43" s="3">
-        <v>974700</v>
+        <v>1245600</v>
       </c>
       <c r="G43" s="3">
-        <v>911000</v>
+        <v>1084700</v>
       </c>
       <c r="H43" s="3">
-        <v>985400</v>
+        <v>1013800</v>
       </c>
       <c r="I43" s="3">
-        <v>995200</v>
+        <v>1096600</v>
       </c>
       <c r="J43" s="3">
+        <v>1107500</v>
+      </c>
+      <c r="K43" s="3">
         <v>959500</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>884900</v>
       </c>
-      <c r="L43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M43" s="3" t="s">
         <v>3</v>
       </c>
@@ -2089,38 +2181,41 @@
       <c r="P43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>16824000</v>
+        <v>19408100</v>
       </c>
       <c r="E44" s="3">
-        <v>12082000</v>
+        <v>18722600</v>
       </c>
       <c r="F44" s="3">
-        <v>12457400</v>
+        <v>13445400</v>
       </c>
       <c r="G44" s="3">
-        <v>11431500</v>
+        <v>13863300</v>
       </c>
       <c r="H44" s="3">
-        <v>9822600</v>
+        <v>12721600</v>
       </c>
       <c r="I44" s="3">
-        <v>9345400</v>
+        <v>10931100</v>
       </c>
       <c r="J44" s="3">
+        <v>10400000</v>
+      </c>
+      <c r="K44" s="3">
         <v>9720300</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>8118200</v>
       </c>
-      <c r="L44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M44" s="3" t="s">
         <v>3</v>
       </c>
@@ -2133,38 +2228,41 @@
       <c r="P44" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="45" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q44" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>1173500</v>
+        <v>1621000</v>
       </c>
       <c r="E45" s="3">
-        <v>859000</v>
+        <v>1305900</v>
       </c>
       <c r="F45" s="3">
-        <v>890800</v>
+        <v>955900</v>
       </c>
       <c r="G45" s="3">
-        <v>849200</v>
+        <v>991300</v>
       </c>
       <c r="H45" s="3">
-        <v>867600</v>
+        <v>945000</v>
       </c>
       <c r="I45" s="3">
-        <v>894500</v>
+        <v>965500</v>
       </c>
       <c r="J45" s="3">
+        <v>995400</v>
+      </c>
+      <c r="K45" s="3">
         <v>880000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>685300</v>
       </c>
-      <c r="L45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M45" s="3" t="s">
         <v>3</v>
       </c>
@@ -2177,38 +2275,41 @@
       <c r="P45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>21649100</v>
+        <v>25551000</v>
       </c>
       <c r="E46" s="3">
-        <v>15930500</v>
+        <v>24092300</v>
       </c>
       <c r="F46" s="3">
-        <v>16327300</v>
+        <v>17728300</v>
       </c>
       <c r="G46" s="3">
-        <v>15135700</v>
+        <v>18169900</v>
       </c>
       <c r="H46" s="3">
-        <v>13610400</v>
+        <v>16843800</v>
       </c>
       <c r="I46" s="3">
-        <v>13359000</v>
+        <v>15146400</v>
       </c>
       <c r="J46" s="3">
+        <v>14866600</v>
+      </c>
+      <c r="K46" s="3">
         <v>13725100</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>13161400</v>
       </c>
-      <c r="L46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M46" s="3" t="s">
         <v>3</v>
       </c>
@@ -2221,38 +2322,41 @@
       <c r="P46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>1347700</v>
+        <v>1613700</v>
       </c>
       <c r="E47" s="3">
-        <v>1279400</v>
+        <v>1499800</v>
       </c>
       <c r="F47" s="3">
-        <v>1302400</v>
+        <v>1423800</v>
       </c>
       <c r="G47" s="3">
-        <v>1358200</v>
+        <v>1449400</v>
       </c>
       <c r="H47" s="3">
-        <v>1267600</v>
+        <v>1511400</v>
       </c>
       <c r="I47" s="3">
-        <v>1243700</v>
+        <v>1410600</v>
       </c>
       <c r="J47" s="3">
+        <v>1384000</v>
+      </c>
+      <c r="K47" s="3">
         <v>1265200</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>1319900</v>
       </c>
-      <c r="L47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M47" s="3" t="s">
         <v>3</v>
       </c>
@@ -2265,38 +2369,41 @@
       <c r="P47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>3367300</v>
+        <v>3779900</v>
       </c>
       <c r="E48" s="3">
-        <v>3166100</v>
+        <v>3747400</v>
       </c>
       <c r="F48" s="3">
-        <v>3235500</v>
+        <v>3523400</v>
       </c>
       <c r="G48" s="3">
-        <v>3421500</v>
+        <v>3600700</v>
       </c>
       <c r="H48" s="3">
-        <v>3584000</v>
+        <v>3807700</v>
       </c>
       <c r="I48" s="3">
-        <v>3538100</v>
+        <v>3988400</v>
       </c>
       <c r="J48" s="3">
+        <v>3937400</v>
+      </c>
+      <c r="K48" s="3">
         <v>3684500</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>3644400</v>
       </c>
-      <c r="L48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M48" s="3" t="s">
         <v>3</v>
       </c>
@@ -2309,38 +2416,41 @@
       <c r="P48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>1398800</v>
+        <v>1743700</v>
       </c>
       <c r="E49" s="3">
-        <v>257700</v>
+        <v>1556700</v>
       </c>
       <c r="F49" s="3">
-        <v>264500</v>
+        <v>286800</v>
       </c>
       <c r="G49" s="3">
-        <v>271000</v>
+        <v>294400</v>
       </c>
       <c r="H49" s="3">
-        <v>267700</v>
+        <v>301600</v>
       </c>
       <c r="I49" s="3">
-        <v>326100</v>
+        <v>297900</v>
       </c>
       <c r="J49" s="3">
+        <v>362900</v>
+      </c>
+      <c r="K49" s="3">
         <v>351500</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>121200</v>
       </c>
-      <c r="L49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M49" s="3" t="s">
         <v>3</v>
       </c>
@@ -2353,8 +2463,11 @@
       <c r="P49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2397,8 +2510,11 @@
       <c r="P50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2441,38 +2557,41 @@
       <c r="P51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>713300</v>
+        <v>825700</v>
       </c>
       <c r="E52" s="3">
-        <v>757100</v>
+        <v>793800</v>
       </c>
       <c r="F52" s="3">
-        <v>751300</v>
+        <v>842600</v>
       </c>
       <c r="G52" s="3">
-        <v>718300</v>
+        <v>836100</v>
       </c>
       <c r="H52" s="3">
-        <v>707800</v>
+        <v>799300</v>
       </c>
       <c r="I52" s="3">
-        <v>721200</v>
+        <v>787600</v>
       </c>
       <c r="J52" s="3">
+        <v>802600</v>
+      </c>
+      <c r="K52" s="3">
         <v>617000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>633100</v>
       </c>
-      <c r="L52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M52" s="3" t="s">
         <v>3</v>
       </c>
@@ -2485,8 +2604,11 @@
       <c r="P52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2529,38 +2651,41 @@
       <c r="P53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>28476300</v>
+        <v>33514200</v>
       </c>
       <c r="E54" s="3">
-        <v>21390900</v>
+        <v>31690000</v>
       </c>
       <c r="F54" s="3">
-        <v>21881100</v>
+        <v>23804900</v>
       </c>
       <c r="G54" s="3">
-        <v>20904700</v>
+        <v>24350400</v>
       </c>
       <c r="H54" s="3">
-        <v>19437400</v>
+        <v>23263900</v>
       </c>
       <c r="I54" s="3">
-        <v>19188100</v>
+        <v>21631000</v>
       </c>
       <c r="J54" s="3">
+        <v>21353500</v>
+      </c>
+      <c r="K54" s="3">
         <v>19643300</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>18880000</v>
       </c>
-      <c r="L54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M54" s="3" t="s">
         <v>3</v>
       </c>
@@ -2573,8 +2698,11 @@
       <c r="P54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2591,8 +2719,9 @@
       <c r="N55" s="3"/>
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
-    </row>
-    <row r="56" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q55" s="3"/>
+    </row>
+    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2609,38 +2738,39 @@
       <c r="N56" s="3"/>
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
-    </row>
-    <row r="57" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q56" s="3"/>
+    </row>
+    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>1445000</v>
+        <v>1582400</v>
       </c>
       <c r="E57" s="3">
-        <v>1513900</v>
+        <v>1608000</v>
       </c>
       <c r="F57" s="3">
-        <v>1419700</v>
+        <v>1684800</v>
       </c>
       <c r="G57" s="3">
-        <v>1441300</v>
+        <v>1579900</v>
       </c>
       <c r="H57" s="3">
-        <v>1362500</v>
+        <v>1604000</v>
       </c>
       <c r="I57" s="3">
-        <v>1447200</v>
+        <v>1516200</v>
       </c>
       <c r="J57" s="3">
+        <v>1610500</v>
+      </c>
+      <c r="K57" s="3">
         <v>1425200</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>1399600</v>
       </c>
-      <c r="L57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M57" s="3" t="s">
         <v>3</v>
       </c>
@@ -2653,38 +2783,41 @@
       <c r="P57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>8037500</v>
+        <v>7637600</v>
       </c>
       <c r="E58" s="3">
-        <v>2959600</v>
+        <v>8944600</v>
       </c>
       <c r="F58" s="3">
-        <v>3802000</v>
+        <v>3293600</v>
       </c>
       <c r="G58" s="3">
-        <v>2947500</v>
+        <v>4231000</v>
       </c>
       <c r="H58" s="3">
-        <v>3092400</v>
+        <v>3280100</v>
       </c>
       <c r="I58" s="3">
-        <v>2611800</v>
+        <v>3441400</v>
       </c>
       <c r="J58" s="3">
+        <v>2906500</v>
+      </c>
+      <c r="K58" s="3">
         <v>3104000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>1593600</v>
       </c>
-      <c r="L58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M58" s="3" t="s">
         <v>3</v>
       </c>
@@ -2697,38 +2830,41 @@
       <c r="P58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>2994200</v>
+        <v>4020500</v>
       </c>
       <c r="E59" s="3">
-        <v>2787200</v>
+        <v>3332100</v>
       </c>
       <c r="F59" s="3">
-        <v>2756800</v>
+        <v>3101700</v>
       </c>
       <c r="G59" s="3">
-        <v>2622900</v>
+        <v>3067900</v>
       </c>
       <c r="H59" s="3">
-        <v>2428900</v>
+        <v>2918900</v>
       </c>
       <c r="I59" s="3">
-        <v>2605800</v>
+        <v>2703000</v>
       </c>
       <c r="J59" s="3">
+        <v>2899900</v>
+      </c>
+      <c r="K59" s="3">
         <v>2496000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>2856500</v>
       </c>
-      <c r="L59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M59" s="3" t="s">
         <v>3</v>
       </c>
@@ -2741,38 +2877,41 @@
       <c r="P59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>12476700</v>
+        <v>13240500</v>
       </c>
       <c r="E60" s="3">
-        <v>7260700</v>
+        <v>13884700</v>
       </c>
       <c r="F60" s="3">
-        <v>7978500</v>
+        <v>8080100</v>
       </c>
       <c r="G60" s="3">
-        <v>7011700</v>
+        <v>8878800</v>
       </c>
       <c r="H60" s="3">
-        <v>6883800</v>
+        <v>7803000</v>
       </c>
       <c r="I60" s="3">
-        <v>6664800</v>
+        <v>7660700</v>
       </c>
       <c r="J60" s="3">
+        <v>7417000</v>
+      </c>
+      <c r="K60" s="3">
         <v>7025200</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>5849700</v>
       </c>
-      <c r="L60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M60" s="3" t="s">
         <v>3</v>
       </c>
@@ -2785,38 +2924,41 @@
       <c r="P60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>3146900</v>
+        <v>5045300</v>
       </c>
       <c r="E61" s="3">
-        <v>1984700</v>
+        <v>3502000</v>
       </c>
       <c r="F61" s="3">
-        <v>1829500</v>
+        <v>2208600</v>
       </c>
       <c r="G61" s="3">
-        <v>1868400</v>
+        <v>2035900</v>
       </c>
       <c r="H61" s="3">
-        <v>1082900</v>
+        <v>2079300</v>
       </c>
       <c r="I61" s="3">
-        <v>1262100</v>
+        <v>1205100</v>
       </c>
       <c r="J61" s="3">
+        <v>1404600</v>
+      </c>
+      <c r="K61" s="3">
         <v>1143800</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>2112500</v>
       </c>
-      <c r="L61" s="3">
-        <v>0</v>
-      </c>
       <c r="M61" s="3">
         <v>0</v>
       </c>
@@ -2829,38 +2971,41 @@
       <c r="P61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>1093600</v>
+        <v>1045400</v>
       </c>
       <c r="E62" s="3">
-        <v>699500</v>
+        <v>1217000</v>
       </c>
       <c r="F62" s="3">
-        <v>786900</v>
+        <v>778400</v>
       </c>
       <c r="G62" s="3">
-        <v>792900</v>
+        <v>875700</v>
       </c>
       <c r="H62" s="3">
-        <v>771200</v>
+        <v>882400</v>
       </c>
       <c r="I62" s="3">
-        <v>622200</v>
+        <v>858300</v>
       </c>
       <c r="J62" s="3">
+        <v>692400</v>
+      </c>
+      <c r="K62" s="3">
         <v>747600</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>666600</v>
       </c>
-      <c r="L62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M62" s="3" t="s">
         <v>3</v>
       </c>
@@ -2873,8 +3018,11 @@
       <c r="P62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2917,8 +3065,11 @@
       <c r="P63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2961,8 +3112,11 @@
       <c r="P64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3005,38 +3159,41 @@
       <c r="P65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>16996100</v>
+        <v>19658400</v>
       </c>
       <c r="E66" s="3">
-        <v>10196000</v>
+        <v>18914200</v>
       </c>
       <c r="F66" s="3">
-        <v>10844800</v>
+        <v>11346600</v>
       </c>
       <c r="G66" s="3">
-        <v>9916700</v>
+        <v>12068700</v>
       </c>
       <c r="H66" s="3">
-        <v>8965300</v>
+        <v>11035800</v>
       </c>
       <c r="I66" s="3">
-        <v>8769800</v>
+        <v>9977100</v>
       </c>
       <c r="J66" s="3">
+        <v>9759500</v>
+      </c>
+      <c r="K66" s="3">
         <v>9257000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>8944400</v>
       </c>
-      <c r="L66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M66" s="3" t="s">
         <v>3</v>
       </c>
@@ -3049,8 +3206,11 @@
       <c r="P66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3067,8 +3227,9 @@
       <c r="N67" s="3"/>
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
-    </row>
-    <row r="68" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q67" s="3"/>
+    </row>
+    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3111,8 +3272,11 @@
       <c r="P68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3155,8 +3319,11 @@
       <c r="P69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3199,8 +3366,11 @@
       <c r="P70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3243,38 +3413,41 @@
       <c r="P71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>7281600</v>
+        <v>8618400</v>
       </c>
       <c r="E72" s="3">
-        <v>7224600</v>
+        <v>8103300</v>
       </c>
       <c r="F72" s="3">
-        <v>6839200</v>
+        <v>8039900</v>
       </c>
       <c r="G72" s="3">
-        <v>6769300</v>
+        <v>7611000</v>
       </c>
       <c r="H72" s="3">
-        <v>6446800</v>
+        <v>7533300</v>
       </c>
       <c r="I72" s="3">
-        <v>6741200</v>
+        <v>7174300</v>
       </c>
       <c r="J72" s="3">
+        <v>7501900</v>
+      </c>
+      <c r="K72" s="3">
         <v>6520100</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>6337800</v>
       </c>
-      <c r="L72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M72" s="3" t="s">
         <v>3</v>
       </c>
@@ -3287,8 +3460,11 @@
       <c r="P72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3331,8 +3507,11 @@
       <c r="P73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3375,8 +3554,11 @@
       <c r="P74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3419,38 +3601,41 @@
       <c r="P75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>11480200</v>
+        <v>13855800</v>
       </c>
       <c r="E76" s="3">
-        <v>11194900</v>
+        <v>12775800</v>
       </c>
       <c r="F76" s="3">
-        <v>11036200</v>
+        <v>12458300</v>
       </c>
       <c r="G76" s="3">
-        <v>10988000</v>
+        <v>12281700</v>
       </c>
       <c r="H76" s="3">
-        <v>10472100</v>
+        <v>12228100</v>
       </c>
       <c r="I76" s="3">
-        <v>10418300</v>
+        <v>11653900</v>
       </c>
       <c r="J76" s="3">
+        <v>11594100</v>
+      </c>
+      <c r="K76" s="3">
         <v>10386300</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>9935600</v>
       </c>
-      <c r="L76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M76" s="3" t="s">
         <v>3</v>
       </c>
@@ -3463,8 +3648,11 @@
       <c r="P76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3507,43 +3695,46 @@
       <c r="P77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45504</v>
+      </c>
+      <c r="E80" s="2">
         <v>45412</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45322</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45230</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45138</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45046</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44957</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44865</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44592</v>
       </c>
-      <c r="L80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="M80" s="2" t="s">
         <v>3</v>
       </c>
@@ -3556,38 +3747,41 @@
       <c r="P80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>321700</v>
+        <v>515100</v>
       </c>
       <c r="E81" s="3">
-        <v>385600</v>
+        <v>358000</v>
       </c>
       <c r="F81" s="3">
-        <v>315100</v>
+        <v>429100</v>
       </c>
       <c r="G81" s="3">
-        <v>322600</v>
+        <v>350700</v>
       </c>
       <c r="H81" s="3">
-        <v>267500</v>
+        <v>359000</v>
       </c>
       <c r="I81" s="3">
-        <v>221400</v>
+        <v>297700</v>
       </c>
       <c r="J81" s="3">
+        <v>246400</v>
+      </c>
+      <c r="K81" s="3">
         <v>291900</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>256200</v>
       </c>
-      <c r="L81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M81" s="3" t="s">
         <v>3</v>
       </c>
@@ -3600,8 +3794,11 @@
       <c r="P81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3618,28 +3815,29 @@
       <c r="N82" s="3"/>
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
-    </row>
-    <row r="83" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q82" s="3"/>
+    </row>
+    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>48900</v>
+        <v>56900</v>
       </c>
       <c r="E83" s="3">
-        <v>27000</v>
+        <v>54400</v>
       </c>
       <c r="F83" s="3">
-        <v>59400</v>
+        <v>30100</v>
       </c>
       <c r="G83" s="3">
-        <v>45000</v>
+        <v>66100</v>
       </c>
       <c r="H83" s="3">
-        <v>45600</v>
-      </c>
-      <c r="I83" s="3" t="s">
-        <v>3</v>
+        <v>50100</v>
+      </c>
+      <c r="I83" s="3">
+        <v>50800</v>
       </c>
       <c r="J83" s="3" t="s">
         <v>3</v>
@@ -3656,14 +3854,17 @@
       <c r="N83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O83" s="3">
-        <v>0</v>
+      <c r="O83" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3706,8 +3907,11 @@
       <c r="P84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3750,8 +3954,11 @@
       <c r="P85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3794,8 +4001,11 @@
       <c r="P86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3838,8 +4048,11 @@
       <c r="P87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3882,34 +4095,37 @@
       <c r="P88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="D89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K89" s="3">
-        <v>0</v>
+      <c r="D89" s="3">
+        <v>0</v>
+      </c>
+      <c r="E89" s="3">
+        <v>0</v>
+      </c>
+      <c r="F89" s="3">
+        <v>0</v>
+      </c>
+      <c r="G89" s="3">
+        <v>0</v>
+      </c>
+      <c r="H89" s="3">
+        <v>0</v>
+      </c>
+      <c r="I89" s="3">
+        <v>0</v>
+      </c>
+      <c r="J89" s="3">
+        <v>0</v>
+      </c>
+      <c r="K89" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L89" s="3">
         <v>0</v>
@@ -3926,8 +4142,11 @@
       <c r="P89" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="90" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q89" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3944,23 +4163,24 @@
       <c r="N90" s="3"/>
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
-    </row>
-    <row r="91" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q90" s="3"/>
+    </row>
+    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-41227000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-39333000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-37604000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-92162000</v>
       </c>
-      <c r="G91" s="3">
-        <v>0</v>
-      </c>
       <c r="H91" s="3">
         <v>0</v>
       </c>
@@ -3988,8 +4208,11 @@
       <c r="P91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4032,8 +4255,11 @@
       <c r="P92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4076,34 +4302,37 @@
       <c r="P93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="D94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K94" s="3">
-        <v>0</v>
+      <c r="D94" s="3">
+        <v>0</v>
+      </c>
+      <c r="E94" s="3">
+        <v>0</v>
+      </c>
+      <c r="F94" s="3">
+        <v>0</v>
+      </c>
+      <c r="G94" s="3">
+        <v>0</v>
+      </c>
+      <c r="H94" s="3">
+        <v>0</v>
+      </c>
+      <c r="I94" s="3">
+        <v>0</v>
+      </c>
+      <c r="J94" s="3">
+        <v>0</v>
+      </c>
+      <c r="K94" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L94" s="3">
         <v>0</v>
@@ -4120,8 +4349,11 @@
       <c r="P94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4138,8 +4370,9 @@
       <c r="N95" s="3"/>
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
-    </row>
-    <row r="96" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q95" s="3"/>
+    </row>
+    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -4182,8 +4415,11 @@
       <c r="P96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4226,8 +4462,11 @@
       <c r="P97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4270,8 +4509,11 @@
       <c r="P98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4314,34 +4556,37 @@
       <c r="P99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="D100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K100" s="3">
-        <v>0</v>
+      <c r="D100" s="3">
+        <v>0</v>
+      </c>
+      <c r="E100" s="3">
+        <v>0</v>
+      </c>
+      <c r="F100" s="3">
+        <v>0</v>
+      </c>
+      <c r="G100" s="3">
+        <v>0</v>
+      </c>
+      <c r="H100" s="3">
+        <v>0</v>
+      </c>
+      <c r="I100" s="3">
+        <v>0</v>
+      </c>
+      <c r="J100" s="3">
+        <v>0</v>
+      </c>
+      <c r="K100" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L100" s="3">
         <v>0</v>
@@ -4358,34 +4603,37 @@
       <c r="P100" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="101" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K101" s="3">
-        <v>0</v>
+      <c r="D101" s="3">
+        <v>0</v>
+      </c>
+      <c r="E101" s="3">
+        <v>0</v>
+      </c>
+      <c r="F101" s="3">
+        <v>0</v>
+      </c>
+      <c r="G101" s="3">
+        <v>0</v>
+      </c>
+      <c r="H101" s="3">
+        <v>0</v>
+      </c>
+      <c r="I101" s="3">
+        <v>0</v>
+      </c>
+      <c r="J101" s="3">
+        <v>0</v>
+      </c>
+      <c r="K101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L101" s="3">
         <v>0</v>
@@ -4402,34 +4650,37 @@
       <c r="P101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="D102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K102" s="3">
-        <v>0</v>
+      <c r="D102" s="3">
+        <v>0</v>
+      </c>
+      <c r="E102" s="3">
+        <v>0</v>
+      </c>
+      <c r="F102" s="3">
+        <v>0</v>
+      </c>
+      <c r="G102" s="3">
+        <v>0</v>
+      </c>
+      <c r="H102" s="3">
+        <v>0</v>
+      </c>
+      <c r="I102" s="3">
+        <v>0</v>
+      </c>
+      <c r="J102" s="3">
+        <v>0</v>
+      </c>
+      <c r="K102" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L102" s="3">
         <v>0</v>
@@ -4444,6 +4695,9 @@
         <v>0</v>
       </c>
       <c r="P102" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q102" s="3">
         <v>0</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/SKHSY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/SKHSY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="319" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="505" uniqueCount="92">
   <si>
     <t>SKHSY</t>
   </si>
@@ -656,62 +656,61 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Q102"/>
+  <dimension ref="A5:R102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="7" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="17" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="13" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="18" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45596</v>
+      </c>
+      <c r="E7" s="2">
         <v>45504</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45412</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45322</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45230</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45138</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45046</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44957</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44865</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44592</v>
       </c>
-      <c r="M7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="N7" s="2" t="s">
         <v>3</v>
       </c>
@@ -724,41 +723,44 @@
       <c r="Q7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D8" s="3">
-        <v>7682700</v>
-      </c>
-      <c r="E8" s="3">
-        <v>5517100</v>
-      </c>
-      <c r="F8" s="3">
-        <v>6515900</v>
-      </c>
-      <c r="G8" s="3">
-        <v>5162200</v>
-      </c>
-      <c r="H8" s="3">
-        <v>5354600</v>
-      </c>
-      <c r="I8" s="3">
-        <v>5028800</v>
-      </c>
-      <c r="J8" s="3">
+      <c r="D8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K8" s="3">
         <v>5671200</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>4507100</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>5019700</v>
       </c>
-      <c r="M8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N8" s="3" t="s">
         <v>3</v>
       </c>
@@ -771,41 +773,44 @@
       <c r="Q8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D9" s="3">
-        <v>6259000</v>
-      </c>
-      <c r="E9" s="3">
-        <v>4373600</v>
-      </c>
-      <c r="F9" s="3">
-        <v>5229100</v>
-      </c>
-      <c r="G9" s="3">
-        <v>4103200</v>
-      </c>
-      <c r="H9" s="3">
-        <v>4251800</v>
-      </c>
-      <c r="I9" s="3">
-        <v>4048600</v>
-      </c>
-      <c r="J9" s="3">
+      <c r="D9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K9" s="3">
         <v>4633900</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>3635800</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>4041200</v>
       </c>
-      <c r="M9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N9" s="3" t="s">
         <v>3</v>
       </c>
@@ -818,41 +823,44 @@
       <c r="Q9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D10" s="3">
-        <v>1423800</v>
-      </c>
-      <c r="E10" s="3">
-        <v>1143400</v>
-      </c>
-      <c r="F10" s="3">
-        <v>1286800</v>
-      </c>
-      <c r="G10" s="3">
-        <v>1058900</v>
-      </c>
-      <c r="H10" s="3">
-        <v>1102700</v>
-      </c>
-      <c r="I10" s="3">
-        <v>980200</v>
-      </c>
-      <c r="J10" s="3">
+      <c r="D10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K10" s="3">
         <v>1037300</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>871300</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>978500</v>
       </c>
-      <c r="M10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N10" s="3" t="s">
         <v>3</v>
       </c>
@@ -865,8 +873,11 @@
       <c r="Q10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -884,8 +895,9 @@
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R11" s="3"/>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -931,8 +943,11 @@
       <c r="Q12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -978,41 +993,44 @@
       <c r="Q13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
-        <v>24000</v>
-      </c>
-      <c r="E14" s="3">
-        <v>100</v>
-      </c>
-      <c r="F14" s="3">
-        <v>-43600</v>
-      </c>
-      <c r="G14" s="3">
-        <v>-16300</v>
-      </c>
-      <c r="H14" s="3">
-        <v>800</v>
-      </c>
-      <c r="I14" s="3">
-        <v>-57400</v>
-      </c>
-      <c r="J14" s="3">
+      <c r="D14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K14" s="3">
         <v>19500</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>-54000</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>3000</v>
       </c>
-      <c r="M14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1025,31 +1043,34 @@
       <c r="Q14" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R14" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D15" s="3">
-        <v>0</v>
-      </c>
-      <c r="E15" s="3">
-        <v>0</v>
-      </c>
-      <c r="F15" s="3">
-        <v>0</v>
-      </c>
-      <c r="G15" s="3">
-        <v>0</v>
-      </c>
-      <c r="H15" s="3">
-        <v>0</v>
-      </c>
-      <c r="I15" s="3">
-        <v>0</v>
-      </c>
-      <c r="J15" s="3">
-        <v>0</v>
+      <c r="D15" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F15" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G15" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H15" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I15" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J15" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K15" s="3">
         <v>0</v>
@@ -1072,8 +1093,11 @@
       <c r="Q15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1088,41 +1112,42 @@
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
-    </row>
-    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R16" s="3"/>
+    </row>
+    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D17" s="3">
-        <v>7100200</v>
-      </c>
-      <c r="E17" s="3">
-        <v>5008000</v>
-      </c>
-      <c r="F17" s="3">
-        <v>5874000</v>
-      </c>
-      <c r="G17" s="3">
-        <v>4707300</v>
-      </c>
-      <c r="H17" s="3">
-        <v>4864200</v>
-      </c>
-      <c r="I17" s="3">
-        <v>4575600</v>
-      </c>
-      <c r="J17" s="3">
+      <c r="D17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K17" s="3">
         <v>5271800</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>4095300</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>4605300</v>
       </c>
-      <c r="M17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N17" s="3" t="s">
         <v>3</v>
       </c>
@@ -1135,41 +1160,44 @@
       <c r="Q17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D18" s="3">
-        <v>582500</v>
-      </c>
-      <c r="E18" s="3">
-        <v>509100</v>
-      </c>
-      <c r="F18" s="3">
-        <v>641900</v>
-      </c>
-      <c r="G18" s="3">
-        <v>454900</v>
-      </c>
-      <c r="H18" s="3">
-        <v>490400</v>
-      </c>
-      <c r="I18" s="3">
-        <v>453200</v>
-      </c>
-      <c r="J18" s="3">
+      <c r="D18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K18" s="3">
         <v>399300</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>411700</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>414400</v>
       </c>
-      <c r="M18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1182,8 +1210,11 @@
       <c r="Q18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1201,41 +1232,42 @@
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
-    </row>
-    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R19" s="3"/>
+    </row>
+    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3">
-        <v>127200</v>
-      </c>
-      <c r="E20" s="3">
-        <v>27800</v>
-      </c>
-      <c r="F20" s="3">
-        <v>17700</v>
-      </c>
-      <c r="G20" s="3">
-        <v>29100</v>
-      </c>
-      <c r="H20" s="3">
-        <v>50100</v>
-      </c>
-      <c r="I20" s="3">
-        <v>2200</v>
-      </c>
-      <c r="J20" s="3">
+      <c r="D20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K20" s="3">
         <v>-21300</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>1900</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>5800</v>
       </c>
-      <c r="M20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N20" s="3" t="s">
         <v>3</v>
       </c>
@@ -1248,28 +1280,31 @@
       <c r="Q20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D21" s="3">
-        <v>766700</v>
-      </c>
-      <c r="E21" s="3">
-        <v>591300</v>
-      </c>
-      <c r="F21" s="3">
-        <v>689700</v>
-      </c>
-      <c r="G21" s="3">
-        <v>550100</v>
-      </c>
-      <c r="H21" s="3">
-        <v>590600</v>
-      </c>
-      <c r="I21" s="3">
-        <v>506100</v>
+      <c r="D21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I21" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="J21" s="3" t="s">
         <v>3</v>
@@ -1295,41 +1330,44 @@
       <c r="Q21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="3">
-        <v>64500</v>
-      </c>
-      <c r="E22" s="3">
-        <v>33800</v>
-      </c>
-      <c r="F22" s="3">
-        <v>25400</v>
-      </c>
-      <c r="G22" s="3">
-        <v>25900</v>
-      </c>
-      <c r="H22" s="3">
-        <v>18600</v>
-      </c>
-      <c r="I22" s="3">
-        <v>17900</v>
-      </c>
-      <c r="J22" s="3">
+      <c r="D22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K22" s="3">
         <v>13600</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>10600</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>10700</v>
       </c>
-      <c r="M22" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N22" s="3" t="s">
         <v>3</v>
       </c>
@@ -1342,41 +1380,44 @@
       <c r="Q22" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D23" s="3">
-        <v>645300</v>
-      </c>
-      <c r="E23" s="3">
-        <v>503100</v>
-      </c>
-      <c r="F23" s="3">
-        <v>634200</v>
-      </c>
-      <c r="G23" s="3">
-        <v>458100</v>
-      </c>
-      <c r="H23" s="3">
-        <v>521900</v>
-      </c>
-      <c r="I23" s="3">
-        <v>437400</v>
-      </c>
-      <c r="J23" s="3">
+      <c r="D23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K23" s="3">
         <v>364400</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>403100</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>409500</v>
       </c>
-      <c r="M23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N23" s="3" t="s">
         <v>3</v>
       </c>
@@ -1389,41 +1430,44 @@
       <c r="Q23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D24" s="3">
-        <v>123900</v>
-      </c>
-      <c r="E24" s="3">
-        <v>138200</v>
-      </c>
-      <c r="F24" s="3">
-        <v>186700</v>
-      </c>
-      <c r="G24" s="3">
-        <v>104000</v>
-      </c>
-      <c r="H24" s="3">
-        <v>156500</v>
-      </c>
-      <c r="I24" s="3">
-        <v>131000</v>
-      </c>
-      <c r="J24" s="3">
+      <c r="D24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K24" s="3">
         <v>113500</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>106400</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>134300</v>
       </c>
-      <c r="M24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N24" s="3" t="s">
         <v>3</v>
       </c>
@@ -1436,8 +1480,11 @@
       <c r="Q24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1483,41 +1530,44 @@
       <c r="Q25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="D26" s="3">
-        <v>521500</v>
-      </c>
-      <c r="E26" s="3">
-        <v>365000</v>
-      </c>
-      <c r="F26" s="3">
-        <v>447500</v>
-      </c>
-      <c r="G26" s="3">
-        <v>354100</v>
-      </c>
-      <c r="H26" s="3">
-        <v>365400</v>
-      </c>
-      <c r="I26" s="3">
-        <v>306400</v>
-      </c>
-      <c r="J26" s="3">
+      <c r="D26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K26" s="3">
         <v>250900</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>296700</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>275100</v>
       </c>
-      <c r="M26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N26" s="3" t="s">
         <v>3</v>
       </c>
@@ -1530,41 +1580,44 @@
       <c r="Q26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="D27" s="3">
-        <v>515100</v>
-      </c>
-      <c r="E27" s="3">
-        <v>358000</v>
-      </c>
-      <c r="F27" s="3">
-        <v>429100</v>
-      </c>
-      <c r="G27" s="3">
-        <v>350700</v>
-      </c>
-      <c r="H27" s="3">
-        <v>359000</v>
-      </c>
-      <c r="I27" s="3">
-        <v>297700</v>
-      </c>
-      <c r="J27" s="3">
+      <c r="D27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K27" s="3">
         <v>246400</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>291900</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>256200</v>
       </c>
-      <c r="M27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N27" s="3" t="s">
         <v>3</v>
       </c>
@@ -1577,8 +1630,11 @@
       <c r="Q27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1624,31 +1680,34 @@
       <c r="Q28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="D29" s="3">
-        <v>0</v>
-      </c>
-      <c r="E29" s="3">
-        <v>0</v>
-      </c>
-      <c r="F29" s="3">
-        <v>0</v>
-      </c>
-      <c r="G29" s="3">
-        <v>0</v>
-      </c>
-      <c r="H29" s="3">
-        <v>0</v>
-      </c>
-      <c r="I29" s="3">
-        <v>0</v>
-      </c>
-      <c r="J29" s="3">
-        <v>0</v>
+      <c r="D29" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E29" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F29" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G29" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H29" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I29" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J29" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K29" s="3">
         <v>0</v>
@@ -1671,8 +1730,11 @@
       <c r="Q29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1718,8 +1780,11 @@
       <c r="Q30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1765,41 +1830,44 @@
       <c r="Q31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3">
-        <v>-127200</v>
-      </c>
-      <c r="E32" s="3">
-        <v>-27800</v>
-      </c>
-      <c r="F32" s="3">
-        <v>-17700</v>
-      </c>
-      <c r="G32" s="3">
-        <v>-29100</v>
-      </c>
-      <c r="H32" s="3">
-        <v>-50100</v>
-      </c>
-      <c r="I32" s="3">
-        <v>-2200</v>
-      </c>
-      <c r="J32" s="3">
+      <c r="D32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K32" s="3">
         <v>21300</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-1900</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-5800</v>
       </c>
-      <c r="M32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N32" s="3" t="s">
         <v>3</v>
       </c>
@@ -1812,41 +1880,44 @@
       <c r="Q32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D33" s="3">
-        <v>515100</v>
-      </c>
-      <c r="E33" s="3">
-        <v>358000</v>
-      </c>
-      <c r="F33" s="3">
-        <v>429100</v>
-      </c>
-      <c r="G33" s="3">
-        <v>350700</v>
-      </c>
-      <c r="H33" s="3">
-        <v>359000</v>
-      </c>
-      <c r="I33" s="3">
-        <v>297700</v>
-      </c>
-      <c r="J33" s="3">
+      <c r="D33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K33" s="3">
         <v>246400</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>291900</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>256200</v>
       </c>
-      <c r="M33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N33" s="3" t="s">
         <v>3</v>
       </c>
@@ -1859,8 +1930,11 @@
       <c r="Q33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1906,41 +1980,44 @@
       <c r="Q34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D35" s="3">
-        <v>515100</v>
-      </c>
-      <c r="E35" s="3">
-        <v>358000</v>
-      </c>
-      <c r="F35" s="3">
-        <v>429100</v>
-      </c>
-      <c r="G35" s="3">
-        <v>350700</v>
-      </c>
-      <c r="H35" s="3">
-        <v>359000</v>
-      </c>
-      <c r="I35" s="3">
-        <v>297700</v>
-      </c>
-      <c r="J35" s="3">
+      <c r="D35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K35" s="3">
         <v>246400</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>291900</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>256200</v>
       </c>
-      <c r="M35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N35" s="3" t="s">
         <v>3</v>
       </c>
@@ -1953,46 +2030,49 @@
       <c r="Q35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45596</v>
+      </c>
+      <c r="E38" s="2">
         <v>45504</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45412</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45322</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45230</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45138</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45046</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44957</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44865</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44592</v>
       </c>
-      <c r="M38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="N38" s="2" t="s">
         <v>3</v>
       </c>
@@ -2005,8 +2085,11 @@
       <c r="Q38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2024,8 +2107,9 @@
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
-    </row>
-    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R39" s="3"/>
+    </row>
+    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2043,41 +2127,42 @@
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
-    </row>
-    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R40" s="3"/>
+    </row>
+    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>3066100</v>
+        <v>2305500</v>
       </c>
       <c r="E41" s="3">
-        <v>2754600</v>
+        <v>2869900</v>
       </c>
       <c r="F41" s="3">
-        <v>2081400</v>
+        <v>2464100</v>
       </c>
       <c r="G41" s="3">
-        <v>2230500</v>
+        <v>2003800</v>
       </c>
       <c r="H41" s="3">
-        <v>2163500</v>
+        <v>2073100</v>
       </c>
       <c r="I41" s="3">
-        <v>2153200</v>
+        <v>2143900</v>
       </c>
       <c r="J41" s="3">
+        <v>2227900</v>
+      </c>
+      <c r="K41" s="3">
         <v>2363600</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>2165300</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>3473000</v>
       </c>
-      <c r="M41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2090,37 +2175,40 @@
       <c r="Q41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>203300</v>
+        <v>83900</v>
       </c>
       <c r="E42" s="3">
-        <v>87300</v>
-      </c>
-      <c r="F42" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G42" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H42" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I42" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J42" s="3" t="s">
-        <v>3</v>
+        <v>190300</v>
+      </c>
+      <c r="F42" s="3">
+        <v>78100</v>
+      </c>
+      <c r="G42" s="3">
+        <v>0</v>
+      </c>
+      <c r="H42" s="3">
+        <v>0</v>
+      </c>
+      <c r="I42" s="3">
+        <v>0</v>
+      </c>
+      <c r="J42" s="3">
+        <v>0</v>
       </c>
       <c r="K42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L42" s="3">
-        <v>0</v>
+      <c r="L42" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M42" s="3">
         <v>0</v>
@@ -2137,41 +2225,44 @@
       <c r="Q42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>1252500</v>
+        <v>1270300</v>
       </c>
       <c r="E43" s="3">
-        <v>1221900</v>
+        <v>1172400</v>
       </c>
       <c r="F43" s="3">
-        <v>1245600</v>
+        <v>1093000</v>
       </c>
       <c r="G43" s="3">
-        <v>1084700</v>
+        <v>1199200</v>
       </c>
       <c r="H43" s="3">
-        <v>1013800</v>
+        <v>1008200</v>
       </c>
       <c r="I43" s="3">
-        <v>1096600</v>
+        <v>1004600</v>
       </c>
       <c r="J43" s="3">
+        <v>1134600</v>
+      </c>
+      <c r="K43" s="3">
         <v>1107500</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>959500</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>884900</v>
       </c>
-      <c r="M43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N43" s="3" t="s">
         <v>3</v>
       </c>
@@ -2184,41 +2275,44 @@
       <c r="Q43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>19408100</v>
+        <v>17004400</v>
       </c>
       <c r="E44" s="3">
-        <v>18722600</v>
+        <v>18166300</v>
       </c>
       <c r="F44" s="3">
-        <v>13445400</v>
+        <v>16747900</v>
       </c>
       <c r="G44" s="3">
-        <v>13863300</v>
+        <v>12944000</v>
       </c>
       <c r="H44" s="3">
-        <v>12721600</v>
+        <v>12885100</v>
       </c>
       <c r="I44" s="3">
-        <v>10931100</v>
+        <v>12606200</v>
       </c>
       <c r="J44" s="3">
+        <v>11310400</v>
+      </c>
+      <c r="K44" s="3">
         <v>10400000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>9720300</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>8118200</v>
       </c>
-      <c r="M44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N44" s="3" t="s">
         <v>3</v>
       </c>
@@ -2231,41 +2325,44 @@
       <c r="Q44" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R44" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>1621000</v>
+        <v>1468000</v>
       </c>
       <c r="E45" s="3">
-        <v>1305900</v>
+        <v>1517300</v>
       </c>
       <c r="F45" s="3">
-        <v>955900</v>
+        <v>1168100</v>
       </c>
       <c r="G45" s="3">
-        <v>991300</v>
+        <v>920200</v>
       </c>
       <c r="H45" s="3">
-        <v>945000</v>
+        <v>921400</v>
       </c>
       <c r="I45" s="3">
-        <v>965500</v>
+        <v>936400</v>
       </c>
       <c r="J45" s="3">
+        <v>999000</v>
+      </c>
+      <c r="K45" s="3">
         <v>995400</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>880000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>685300</v>
       </c>
-      <c r="M45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N45" s="3" t="s">
         <v>3</v>
       </c>
@@ -2278,41 +2375,44 @@
       <c r="Q45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>25551000</v>
+        <v>22132200</v>
       </c>
       <c r="E46" s="3">
-        <v>24092300</v>
+        <v>23916200</v>
       </c>
       <c r="F46" s="3">
-        <v>17728300</v>
+        <v>21551200</v>
       </c>
       <c r="G46" s="3">
-        <v>18169900</v>
+        <v>17067200</v>
       </c>
       <c r="H46" s="3">
-        <v>16843800</v>
+        <v>16887700</v>
       </c>
       <c r="I46" s="3">
-        <v>15146400</v>
+        <v>16691100</v>
       </c>
       <c r="J46" s="3">
+        <v>15671900</v>
+      </c>
+      <c r="K46" s="3">
         <v>14866600</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>13725100</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>13161400</v>
       </c>
-      <c r="M46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N46" s="3" t="s">
         <v>3</v>
       </c>
@@ -2325,41 +2425,44 @@
       <c r="Q46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>1613700</v>
+        <v>1390000</v>
       </c>
       <c r="E47" s="3">
-        <v>1499800</v>
+        <v>2145600</v>
       </c>
       <c r="F47" s="3">
-        <v>1423800</v>
+        <v>1968900</v>
       </c>
       <c r="G47" s="3">
-        <v>1449400</v>
+        <v>2016400</v>
       </c>
       <c r="H47" s="3">
-        <v>1511400</v>
+        <v>1965700</v>
       </c>
       <c r="I47" s="3">
-        <v>1410600</v>
+        <v>2132000</v>
       </c>
       <c r="J47" s="3">
+        <v>2117000</v>
+      </c>
+      <c r="K47" s="3">
         <v>1384000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>1265200</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>1319900</v>
       </c>
-      <c r="M47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N47" s="3" t="s">
         <v>3</v>
       </c>
@@ -2372,41 +2475,44 @@
       <c r="Q47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>3779900</v>
+        <v>3439800</v>
       </c>
       <c r="E48" s="3">
-        <v>3747400</v>
+        <v>3538100</v>
       </c>
       <c r="F48" s="3">
-        <v>3523400</v>
+        <v>3352100</v>
       </c>
       <c r="G48" s="3">
-        <v>3600700</v>
+        <v>3392000</v>
       </c>
       <c r="H48" s="3">
-        <v>3807700</v>
+        <v>3346600</v>
       </c>
       <c r="I48" s="3">
-        <v>3988400</v>
+        <v>3773100</v>
       </c>
       <c r="J48" s="3">
+        <v>4126800</v>
+      </c>
+      <c r="K48" s="3">
         <v>3937400</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>3684500</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>3644400</v>
       </c>
-      <c r="M48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N48" s="3" t="s">
         <v>3</v>
       </c>
@@ -2419,41 +2525,44 @@
       <c r="Q48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>1743700</v>
+        <v>1434100</v>
       </c>
       <c r="E49" s="3">
-        <v>1556700</v>
+        <v>1632200</v>
       </c>
       <c r="F49" s="3">
-        <v>286800</v>
+        <v>1392500</v>
       </c>
       <c r="G49" s="3">
-        <v>294400</v>
+        <v>276100</v>
       </c>
       <c r="H49" s="3">
-        <v>301600</v>
+        <v>273600</v>
       </c>
       <c r="I49" s="3">
-        <v>297900</v>
+        <v>298900</v>
       </c>
       <c r="J49" s="3">
+        <v>308200</v>
+      </c>
+      <c r="K49" s="3">
         <v>362900</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>351500</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>121200</v>
       </c>
-      <c r="M49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N49" s="3" t="s">
         <v>3</v>
       </c>
@@ -2466,8 +2575,11 @@
       <c r="Q49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2513,8 +2625,11 @@
       <c r="Q50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2560,41 +2675,44 @@
       <c r="Q51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>825700</v>
+        <v>655400</v>
       </c>
       <c r="E52" s="3">
-        <v>793800</v>
+        <v>0</v>
       </c>
       <c r="F52" s="3">
-        <v>842600</v>
+        <v>0</v>
       </c>
       <c r="G52" s="3">
-        <v>836100</v>
+        <v>0</v>
       </c>
       <c r="H52" s="3">
-        <v>799300</v>
+        <v>0</v>
       </c>
       <c r="I52" s="3">
-        <v>787600</v>
+        <v>0</v>
       </c>
       <c r="J52" s="3">
+        <v>0</v>
+      </c>
+      <c r="K52" s="3">
         <v>802600</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>617000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>633100</v>
       </c>
-      <c r="M52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N52" s="3" t="s">
         <v>3</v>
       </c>
@@ -2607,8 +2725,11 @@
       <c r="Q52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2654,41 +2775,44 @@
       <c r="Q53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>33514200</v>
+        <v>29223600</v>
       </c>
       <c r="E54" s="3">
-        <v>31690000</v>
+        <v>31369800</v>
       </c>
       <c r="F54" s="3">
-        <v>23804900</v>
+        <v>28347500</v>
       </c>
       <c r="G54" s="3">
-        <v>24350400</v>
+        <v>22917100</v>
       </c>
       <c r="H54" s="3">
-        <v>23263900</v>
+        <v>22632200</v>
       </c>
       <c r="I54" s="3">
-        <v>21631000</v>
+        <v>23052900</v>
       </c>
       <c r="J54" s="3">
+        <v>22381500</v>
+      </c>
+      <c r="K54" s="3">
         <v>21353500</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>19643300</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>18880000</v>
       </c>
-      <c r="M54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N54" s="3" t="s">
         <v>3</v>
       </c>
@@ -2701,8 +2825,11 @@
       <c r="Q54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2720,8 +2847,9 @@
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
-    </row>
-    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R55" s="3"/>
+    </row>
+    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2739,41 +2867,42 @@
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
-    </row>
-    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R56" s="3"/>
+    </row>
+    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>1582400</v>
+        <v>985700</v>
       </c>
       <c r="E57" s="3">
-        <v>1608000</v>
+        <v>1481200</v>
       </c>
       <c r="F57" s="3">
-        <v>1684800</v>
+        <v>1438400</v>
       </c>
       <c r="G57" s="3">
-        <v>1579900</v>
+        <v>1621900</v>
       </c>
       <c r="H57" s="3">
-        <v>1604000</v>
+        <v>1468400</v>
       </c>
       <c r="I57" s="3">
-        <v>1516200</v>
+        <v>1589400</v>
       </c>
       <c r="J57" s="3">
+        <v>1568900</v>
+      </c>
+      <c r="K57" s="3">
         <v>1610500</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>1425200</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>1399600</v>
       </c>
-      <c r="M57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N57" s="3" t="s">
         <v>3</v>
       </c>
@@ -2786,41 +2915,44 @@
       <c r="Q57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>7637600</v>
+        <v>5930100</v>
       </c>
       <c r="E58" s="3">
-        <v>8944600</v>
+        <v>7148900</v>
       </c>
       <c r="F58" s="3">
-        <v>3293600</v>
+        <v>8001100</v>
       </c>
       <c r="G58" s="3">
-        <v>4231000</v>
+        <v>3155800</v>
       </c>
       <c r="H58" s="3">
-        <v>3280100</v>
+        <v>3932500</v>
       </c>
       <c r="I58" s="3">
-        <v>3441400</v>
+        <v>3250400</v>
       </c>
       <c r="J58" s="3">
+        <v>3560800</v>
+      </c>
+      <c r="K58" s="3">
         <v>2906500</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>3104000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>1593600</v>
       </c>
-      <c r="M58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N58" s="3" t="s">
         <v>3</v>
       </c>
@@ -2833,41 +2965,44 @@
       <c r="Q58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>4020500</v>
+        <v>3514300</v>
       </c>
       <c r="E59" s="3">
-        <v>3332100</v>
+        <v>3554900</v>
       </c>
       <c r="F59" s="3">
-        <v>3101700</v>
+        <v>2799700</v>
       </c>
       <c r="G59" s="3">
-        <v>3067900</v>
+        <v>2732700</v>
       </c>
       <c r="H59" s="3">
-        <v>2918900</v>
+        <v>2558700</v>
       </c>
       <c r="I59" s="3">
-        <v>2703000</v>
+        <v>2693400</v>
       </c>
       <c r="J59" s="3">
+        <v>2599600</v>
+      </c>
+      <c r="K59" s="3">
         <v>2899900</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>2496000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>2856500</v>
       </c>
-      <c r="M59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N59" s="3" t="s">
         <v>3</v>
       </c>
@@ -2880,41 +3015,44 @@
       <c r="Q59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>13240500</v>
+        <v>10752000</v>
       </c>
       <c r="E60" s="3">
-        <v>13884700</v>
+        <v>12393300</v>
       </c>
       <c r="F60" s="3">
-        <v>8080100</v>
+        <v>12420200</v>
       </c>
       <c r="G60" s="3">
-        <v>8878800</v>
+        <v>7778700</v>
       </c>
       <c r="H60" s="3">
-        <v>7803000</v>
+        <v>8252300</v>
       </c>
       <c r="I60" s="3">
-        <v>7660700</v>
+        <v>7732200</v>
       </c>
       <c r="J60" s="3">
+        <v>7926500</v>
+      </c>
+      <c r="K60" s="3">
         <v>7417000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>7025200</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>5849700</v>
       </c>
-      <c r="M60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N60" s="3" t="s">
         <v>3</v>
       </c>
@@ -2927,41 +3065,44 @@
       <c r="Q60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>5045300</v>
+        <v>5493200</v>
       </c>
       <c r="E61" s="3">
-        <v>3502000</v>
+        <v>4722500</v>
       </c>
       <c r="F61" s="3">
-        <v>2208600</v>
+        <v>3132700</v>
       </c>
       <c r="G61" s="3">
-        <v>2035900</v>
+        <v>1976000</v>
       </c>
       <c r="H61" s="3">
-        <v>2079300</v>
+        <v>1892300</v>
       </c>
       <c r="I61" s="3">
-        <v>1205100</v>
+        <v>2060400</v>
       </c>
       <c r="J61" s="3">
+        <v>1246900</v>
+      </c>
+      <c r="K61" s="3">
         <v>1404600</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>1143800</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>2112500</v>
       </c>
-      <c r="M61" s="3">
-        <v>0</v>
-      </c>
       <c r="N61" s="3">
         <v>0</v>
       </c>
@@ -2974,41 +3115,44 @@
       <c r="Q61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>1045400</v>
+        <v>708500</v>
       </c>
       <c r="E62" s="3">
-        <v>1217000</v>
+        <v>618100</v>
       </c>
       <c r="F62" s="3">
-        <v>778400</v>
+        <v>733100</v>
       </c>
       <c r="G62" s="3">
-        <v>875700</v>
+        <v>643000</v>
       </c>
       <c r="H62" s="3">
-        <v>882400</v>
+        <v>591300</v>
       </c>
       <c r="I62" s="3">
-        <v>858300</v>
+        <v>616700</v>
       </c>
       <c r="J62" s="3">
+        <v>637900</v>
+      </c>
+      <c r="K62" s="3">
         <v>692400</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>747600</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>666600</v>
       </c>
-      <c r="M62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N62" s="3" t="s">
         <v>3</v>
       </c>
@@ -3021,8 +3165,11 @@
       <c r="Q62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3068,8 +3215,11 @@
       <c r="Q63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3115,8 +3265,11 @@
       <c r="Q64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3162,41 +3315,44 @@
       <c r="Q65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>19658400</v>
+        <v>17290100</v>
       </c>
       <c r="E66" s="3">
-        <v>18914200</v>
+        <v>18094400</v>
       </c>
       <c r="F66" s="3">
-        <v>11346600</v>
+        <v>16641600</v>
       </c>
       <c r="G66" s="3">
-        <v>12068700</v>
+        <v>10654400</v>
       </c>
       <c r="H66" s="3">
-        <v>11035800</v>
+        <v>10958600</v>
       </c>
       <c r="I66" s="3">
-        <v>9977100</v>
+        <v>10667000</v>
       </c>
       <c r="J66" s="3">
+        <v>10061400</v>
+      </c>
+      <c r="K66" s="3">
         <v>9759500</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>9257000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>8944400</v>
       </c>
-      <c r="M66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N66" s="3" t="s">
         <v>3</v>
       </c>
@@ -3209,8 +3365,11 @@
       <c r="Q66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3228,8 +3387,9 @@
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
-    </row>
-    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R67" s="3"/>
+    </row>
+    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3275,8 +3435,11 @@
       <c r="Q68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3322,8 +3485,11 @@
       <c r="Q69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3369,8 +3535,11 @@
       <c r="Q70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3416,41 +3585,44 @@
       <c r="Q71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>8618400</v>
+        <v>7966000</v>
       </c>
       <c r="E72" s="3">
-        <v>8103300</v>
+        <v>8066400</v>
       </c>
       <c r="F72" s="3">
-        <v>8039900</v>
+        <v>7248000</v>
       </c>
       <c r="G72" s="3">
-        <v>7611000</v>
+        <v>7739400</v>
       </c>
       <c r="H72" s="3">
-        <v>7533300</v>
+        <v>7073200</v>
       </c>
       <c r="I72" s="3">
-        <v>7174300</v>
+        <v>7464200</v>
       </c>
       <c r="J72" s="3">
+        <v>7422400</v>
+      </c>
+      <c r="K72" s="3">
         <v>7501900</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>6520100</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>6337800</v>
       </c>
-      <c r="M72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N72" s="3" t="s">
         <v>3</v>
       </c>
@@ -3463,8 +3635,11 @@
       <c r="Q72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3510,8 +3685,11 @@
       <c r="Q73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3557,8 +3735,11 @@
       <c r="Q74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3604,41 +3785,44 @@
       <c r="Q75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>13855800</v>
+        <v>11642700</v>
       </c>
       <c r="E76" s="3">
-        <v>12775800</v>
+        <v>12969200</v>
       </c>
       <c r="F76" s="3">
-        <v>12458300</v>
+        <v>11428300</v>
       </c>
       <c r="G76" s="3">
-        <v>12281700</v>
+        <v>11993700</v>
       </c>
       <c r="H76" s="3">
-        <v>12228100</v>
+        <v>11415000</v>
       </c>
       <c r="I76" s="3">
-        <v>11653900</v>
+        <v>12117200</v>
       </c>
       <c r="J76" s="3">
+        <v>12058200</v>
+      </c>
+      <c r="K76" s="3">
         <v>11594100</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>10386300</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>9935600</v>
       </c>
-      <c r="M76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N76" s="3" t="s">
         <v>3</v>
       </c>
@@ -3651,8 +3835,11 @@
       <c r="Q76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3698,46 +3885,49 @@
       <c r="Q77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45596</v>
+      </c>
+      <c r="E80" s="2">
         <v>45504</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45412</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45322</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45230</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45138</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45046</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44957</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44865</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44592</v>
       </c>
-      <c r="M80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="N80" s="2" t="s">
         <v>3</v>
       </c>
@@ -3750,41 +3940,44 @@
       <c r="Q80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D81" s="3">
-        <v>515100</v>
-      </c>
-      <c r="E81" s="3">
-        <v>358000</v>
-      </c>
-      <c r="F81" s="3">
-        <v>429100</v>
-      </c>
-      <c r="G81" s="3">
-        <v>350700</v>
-      </c>
-      <c r="H81" s="3">
-        <v>359000</v>
-      </c>
-      <c r="I81" s="3">
-        <v>297700</v>
-      </c>
-      <c r="J81" s="3">
+      <c r="D81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K81" s="3">
         <v>246400</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>291900</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>256200</v>
       </c>
-      <c r="M81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N81" s="3" t="s">
         <v>3</v>
       </c>
@@ -3797,8 +3990,11 @@
       <c r="Q81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3816,28 +4012,29 @@
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
-    </row>
-    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R82" s="3"/>
+    </row>
+    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="D83" s="3">
-        <v>56900</v>
-      </c>
-      <c r="E83" s="3">
-        <v>54400</v>
-      </c>
-      <c r="F83" s="3">
-        <v>30100</v>
-      </c>
-      <c r="G83" s="3">
-        <v>66100</v>
-      </c>
-      <c r="H83" s="3">
-        <v>50100</v>
-      </c>
-      <c r="I83" s="3">
-        <v>50800</v>
+      <c r="D83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I83" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="J83" s="3" t="s">
         <v>3</v>
@@ -3857,14 +4054,17 @@
       <c r="O83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P83" s="3">
-        <v>0</v>
+      <c r="P83" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3910,8 +4110,11 @@
       <c r="Q84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3957,8 +4160,11 @@
       <c r="Q85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4004,8 +4210,11 @@
       <c r="Q86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4051,8 +4260,11 @@
       <c r="Q87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4098,37 +4310,40 @@
       <c r="Q88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="D89" s="3">
-        <v>0</v>
-      </c>
-      <c r="E89" s="3">
-        <v>0</v>
-      </c>
-      <c r="F89" s="3">
-        <v>0</v>
-      </c>
-      <c r="G89" s="3">
-        <v>0</v>
-      </c>
-      <c r="H89" s="3">
-        <v>0</v>
-      </c>
-      <c r="I89" s="3">
-        <v>0</v>
-      </c>
-      <c r="J89" s="3">
-        <v>0</v>
-      </c>
-      <c r="K89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L89" s="3">
-        <v>0</v>
+      <c r="D89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K89" s="3">
+        <v>0</v>
+      </c>
+      <c r="L89" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M89" s="3">
         <v>0</v>
@@ -4145,8 +4360,11 @@
       <c r="Q89" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R89" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4164,31 +4382,32 @@
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
-    </row>
-    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R90" s="3"/>
+    </row>
+    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D91" s="3">
-        <v>-41227000</v>
-      </c>
-      <c r="E91" s="3">
-        <v>-39333000</v>
-      </c>
-      <c r="F91" s="3">
-        <v>-37604000</v>
-      </c>
-      <c r="G91" s="3">
-        <v>-92162000</v>
-      </c>
-      <c r="H91" s="3">
-        <v>0</v>
-      </c>
-      <c r="I91" s="3">
-        <v>0</v>
-      </c>
-      <c r="J91" s="3">
-        <v>0</v>
+      <c r="D91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K91" s="3">
         <v>0</v>
@@ -4211,8 +4430,11 @@
       <c r="Q91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4258,8 +4480,11 @@
       <c r="Q92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4305,37 +4530,40 @@
       <c r="Q93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="D94" s="3">
-        <v>0</v>
-      </c>
-      <c r="E94" s="3">
-        <v>0</v>
-      </c>
-      <c r="F94" s="3">
-        <v>0</v>
-      </c>
-      <c r="G94" s="3">
-        <v>0</v>
-      </c>
-      <c r="H94" s="3">
-        <v>0</v>
-      </c>
-      <c r="I94" s="3">
-        <v>0</v>
-      </c>
-      <c r="J94" s="3">
-        <v>0</v>
-      </c>
-      <c r="K94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L94" s="3">
-        <v>0</v>
+      <c r="D94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K94" s="3">
+        <v>0</v>
+      </c>
+      <c r="L94" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M94" s="3">
         <v>0</v>
@@ -4352,8 +4580,11 @@
       <c r="Q94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4371,31 +4602,32 @@
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
-    </row>
-    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R95" s="3"/>
+    </row>
+    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3">
-        <v>0</v>
-      </c>
-      <c r="E96" s="3">
-        <v>0</v>
-      </c>
-      <c r="F96" s="3">
-        <v>0</v>
-      </c>
-      <c r="G96" s="3">
-        <v>0</v>
-      </c>
-      <c r="H96" s="3">
-        <v>0</v>
-      </c>
-      <c r="I96" s="3">
-        <v>0</v>
-      </c>
-      <c r="J96" s="3">
-        <v>0</v>
+      <c r="D96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K96" s="3">
         <v>0</v>
@@ -4418,8 +4650,11 @@
       <c r="Q96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4465,8 +4700,11 @@
       <c r="Q97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4512,8 +4750,11 @@
       <c r="Q98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4559,37 +4800,40 @@
       <c r="Q99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="D100" s="3">
-        <v>0</v>
-      </c>
-      <c r="E100" s="3">
-        <v>0</v>
-      </c>
-      <c r="F100" s="3">
-        <v>0</v>
-      </c>
-      <c r="G100" s="3">
-        <v>0</v>
-      </c>
-      <c r="H100" s="3">
-        <v>0</v>
-      </c>
-      <c r="I100" s="3">
-        <v>0</v>
-      </c>
-      <c r="J100" s="3">
-        <v>0</v>
-      </c>
-      <c r="K100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L100" s="3">
-        <v>0</v>
+      <c r="D100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K100" s="3">
+        <v>0</v>
+      </c>
+      <c r="L100" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M100" s="3">
         <v>0</v>
@@ -4606,37 +4850,40 @@
       <c r="Q100" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3">
-        <v>0</v>
-      </c>
-      <c r="E101" s="3">
-        <v>0</v>
-      </c>
-      <c r="F101" s="3">
-        <v>0</v>
-      </c>
-      <c r="G101" s="3">
-        <v>0</v>
-      </c>
-      <c r="H101" s="3">
-        <v>0</v>
-      </c>
-      <c r="I101" s="3">
-        <v>0</v>
-      </c>
-      <c r="J101" s="3">
-        <v>0</v>
-      </c>
-      <c r="K101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L101" s="3">
-        <v>0</v>
+      <c r="D101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K101" s="3">
+        <v>0</v>
+      </c>
+      <c r="L101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M101" s="3">
         <v>0</v>
@@ -4653,37 +4900,40 @@
       <c r="Q101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="D102" s="3">
-        <v>0</v>
-      </c>
-      <c r="E102" s="3">
-        <v>0</v>
-      </c>
-      <c r="F102" s="3">
-        <v>0</v>
-      </c>
-      <c r="G102" s="3">
-        <v>0</v>
-      </c>
-      <c r="H102" s="3">
-        <v>0</v>
-      </c>
-      <c r="I102" s="3">
-        <v>0</v>
-      </c>
-      <c r="J102" s="3">
-        <v>0</v>
-      </c>
-      <c r="K102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L102" s="3">
-        <v>0</v>
+      <c r="D102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K102" s="3">
+        <v>0</v>
+      </c>
+      <c r="L102" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M102" s="3">
         <v>0</v>
@@ -4698,6 +4948,9 @@
         <v>0</v>
       </c>
       <c r="Q102" s="3">
+        <v>0</v>
+      </c>
+      <c r="R102" s="3">
         <v>0</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/SKHSY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/SKHSY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="505" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="533" uniqueCount="92">
   <si>
     <t>SKHSY</t>
   </si>
@@ -656,64 +656,64 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:R102"/>
+  <dimension ref="A5:S102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="13" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="18" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="14" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="19" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45688</v>
+      </c>
+      <c r="E7" s="2">
         <v>45596</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45504</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45412</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45322</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45230</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45138</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45046</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44957</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44865</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44592</v>
       </c>
-      <c r="N7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="O7" s="2" t="s">
         <v>3</v>
       </c>
@@ -726,8 +726,11 @@
       <c r="R7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
@@ -752,18 +755,18 @@
       <c r="J8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K8" s="3">
+      <c r="K8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L8" s="3">
         <v>5671200</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>4507100</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>5019700</v>
       </c>
-      <c r="N8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O8" s="3" t="s">
         <v>3</v>
       </c>
@@ -776,8 +779,11 @@
       <c r="R8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -802,18 +808,18 @@
       <c r="J9" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K9" s="3">
+      <c r="K9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L9" s="3">
         <v>4633900</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>3635800</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>4041200</v>
       </c>
-      <c r="N9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O9" s="3" t="s">
         <v>3</v>
       </c>
@@ -826,8 +832,11 @@
       <c r="R9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -852,18 +861,18 @@
       <c r="J10" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K10" s="3">
+      <c r="K10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L10" s="3">
         <v>1037300</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>871300</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>978500</v>
       </c>
-      <c r="N10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O10" s="3" t="s">
         <v>3</v>
       </c>
@@ -876,8 +885,11 @@
       <c r="R10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -896,8 +908,9 @@
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
       <c r="R11" s="3"/>
-    </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S11" s="3"/>
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -946,8 +959,11 @@
       <c r="R12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -996,8 +1012,11 @@
       <c r="R13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1022,18 +1041,18 @@
       <c r="J14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K14" s="3">
+      <c r="K14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L14" s="3">
         <v>19500</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>-54000</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>3000</v>
       </c>
-      <c r="N14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1046,8 +1065,11 @@
       <c r="R14" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S14" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1072,8 +1094,8 @@
       <c r="J15" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K15" s="3">
-        <v>0</v>
+      <c r="K15" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L15" s="3">
         <v>0</v>
@@ -1096,8 +1118,11 @@
       <c r="R15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1113,8 +1138,9 @@
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
       <c r="R16" s="3"/>
-    </row>
-    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S16" s="3"/>
+    </row>
+    <row r="17" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -1139,18 +1165,18 @@
       <c r="J17" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K17" s="3">
+      <c r="K17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L17" s="3">
         <v>5271800</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>4095300</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>4605300</v>
       </c>
-      <c r="N17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O17" s="3" t="s">
         <v>3</v>
       </c>
@@ -1163,8 +1189,11 @@
       <c r="R17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1189,18 +1218,18 @@
       <c r="J18" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K18" s="3">
+      <c r="K18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L18" s="3">
         <v>399300</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>411700</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>414400</v>
       </c>
-      <c r="N18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1213,8 +1242,11 @@
       <c r="R18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1233,8 +1265,9 @@
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
       <c r="R19" s="3"/>
-    </row>
-    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S19" s="3"/>
+    </row>
+    <row r="20" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1259,18 +1292,18 @@
       <c r="J20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K20" s="3">
+      <c r="K20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L20" s="3">
         <v>-21300</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>1900</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>5800</v>
       </c>
-      <c r="N20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O20" s="3" t="s">
         <v>3</v>
       </c>
@@ -1283,8 +1316,11 @@
       <c r="R20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1333,8 +1369,11 @@
       <c r="R21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1359,18 +1398,18 @@
       <c r="J22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K22" s="3">
+      <c r="K22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L22" s="3">
         <v>13600</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>10600</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>10700</v>
       </c>
-      <c r="N22" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O22" s="3" t="s">
         <v>3</v>
       </c>
@@ -1383,8 +1422,11 @@
       <c r="R22" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
@@ -1409,18 +1451,18 @@
       <c r="J23" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K23" s="3">
+      <c r="K23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L23" s="3">
         <v>364400</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>403100</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>409500</v>
       </c>
-      <c r="N23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O23" s="3" t="s">
         <v>3</v>
       </c>
@@ -1433,8 +1475,11 @@
       <c r="R23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1459,18 +1504,18 @@
       <c r="J24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K24" s="3">
+      <c r="K24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L24" s="3">
         <v>113500</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>106400</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>134300</v>
       </c>
-      <c r="N24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O24" s="3" t="s">
         <v>3</v>
       </c>
@@ -1483,8 +1528,11 @@
       <c r="R24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1533,8 +1581,11 @@
       <c r="R25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -1559,18 +1610,18 @@
       <c r="J26" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K26" s="3">
+      <c r="K26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L26" s="3">
         <v>250900</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>296700</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>275100</v>
       </c>
-      <c r="N26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O26" s="3" t="s">
         <v>3</v>
       </c>
@@ -1583,8 +1634,11 @@
       <c r="R26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -1609,18 +1663,18 @@
       <c r="J27" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K27" s="3">
+      <c r="K27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L27" s="3">
         <v>246400</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>291900</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>256200</v>
       </c>
-      <c r="N27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O27" s="3" t="s">
         <v>3</v>
       </c>
@@ -1633,8 +1687,11 @@
       <c r="R27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1683,8 +1740,11 @@
       <c r="R28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1709,8 +1769,8 @@
       <c r="J29" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K29" s="3">
-        <v>0</v>
+      <c r="K29" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L29" s="3">
         <v>0</v>
@@ -1733,8 +1793,11 @@
       <c r="R29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1783,8 +1846,11 @@
       <c r="R30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1833,8 +1899,11 @@
       <c r="R31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -1859,18 +1928,18 @@
       <c r="J32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K32" s="3">
+      <c r="K32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L32" s="3">
         <v>21300</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-1900</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-5800</v>
       </c>
-      <c r="N32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O32" s="3" t="s">
         <v>3</v>
       </c>
@@ -1883,8 +1952,11 @@
       <c r="R32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -1909,18 +1981,18 @@
       <c r="J33" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K33" s="3">
+      <c r="K33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L33" s="3">
         <v>246400</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>291900</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>256200</v>
       </c>
-      <c r="N33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O33" s="3" t="s">
         <v>3</v>
       </c>
@@ -1933,8 +2005,11 @@
       <c r="R33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1983,8 +2058,11 @@
       <c r="R34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -2009,18 +2087,18 @@
       <c r="J35" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K35" s="3">
+      <c r="K35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L35" s="3">
         <v>246400</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>291900</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>256200</v>
       </c>
-      <c r="N35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O35" s="3" t="s">
         <v>3</v>
       </c>
@@ -2033,49 +2111,52 @@
       <c r="R35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45688</v>
+      </c>
+      <c r="E38" s="2">
         <v>45596</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45504</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45412</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45322</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45230</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45138</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45046</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44957</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44865</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44592</v>
       </c>
-      <c r="N38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="O38" s="2" t="s">
         <v>3</v>
       </c>
@@ -2088,8 +2169,11 @@
       <c r="R38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2108,8 +2192,9 @@
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
       <c r="R39" s="3"/>
-    </row>
-    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S39" s="3"/>
+    </row>
+    <row r="40" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2128,44 +2213,45 @@
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
       <c r="R40" s="3"/>
-    </row>
-    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S40" s="3"/>
+    </row>
+    <row r="41" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>2519500</v>
+      </c>
+      <c r="E41" s="3">
         <v>2305500</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>2869900</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>2464100</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>2003800</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>2073100</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>2143900</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>2227900</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>2363600</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>2165300</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>3473000</v>
       </c>
-      <c r="N41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2178,23 +2264,26 @@
       <c r="R41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>1600</v>
+      </c>
+      <c r="E42" s="3">
         <v>83900</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>190300</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>78100</v>
       </c>
-      <c r="G42" s="3">
-        <v>0</v>
-      </c>
       <c r="H42" s="3">
         <v>0</v>
       </c>
@@ -2204,14 +2293,14 @@
       <c r="J42" s="3">
         <v>0</v>
       </c>
-      <c r="K42" s="3" t="s">
-        <v>3</v>
+      <c r="K42" s="3">
+        <v>0</v>
       </c>
       <c r="L42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M42" s="3">
-        <v>0</v>
+      <c r="M42" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N42" s="3">
         <v>0</v>
@@ -2228,44 +2317,47 @@
       <c r="R42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>1356200</v>
+      </c>
+      <c r="E43" s="3">
         <v>1270300</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>1172400</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>1093000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>1199200</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>1008200</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>1004600</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>1134600</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>1107500</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>959500</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>884900</v>
       </c>
-      <c r="N43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O43" s="3" t="s">
         <v>3</v>
       </c>
@@ -2278,44 +2370,47 @@
       <c r="R43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>18497600</v>
+      </c>
+      <c r="E44" s="3">
         <v>17004400</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>18166300</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>16747900</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>12944000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>12885100</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>12606200</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>11310400</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>10400000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>9720300</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>8118200</v>
       </c>
-      <c r="N44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O44" s="3" t="s">
         <v>3</v>
       </c>
@@ -2328,44 +2423,47 @@
       <c r="R44" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S44" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>1587100</v>
+      </c>
+      <c r="E45" s="3">
         <v>1468000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>1517300</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>1168100</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>920200</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>921400</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>936400</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>999000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>995400</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>880000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>685300</v>
       </c>
-      <c r="N45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O45" s="3" t="s">
         <v>3</v>
       </c>
@@ -2378,44 +2476,47 @@
       <c r="R45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>23962100</v>
+      </c>
+      <c r="E46" s="3">
         <v>22132200</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>23916200</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>21551200</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>17067200</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>16887700</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>16691100</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>15671900</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>14866600</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>13725100</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>13161400</v>
       </c>
-      <c r="N46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O46" s="3" t="s">
         <v>3</v>
       </c>
@@ -2428,44 +2529,47 @@
       <c r="R46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>1327400</v>
+      </c>
+      <c r="E47" s="3">
         <v>1390000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>2145600</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>1968900</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>2016400</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>1965700</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>2132000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>2117000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>1384000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>1265200</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>1319900</v>
       </c>
-      <c r="N47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O47" s="3" t="s">
         <v>3</v>
       </c>
@@ -2478,44 +2582,47 @@
       <c r="R47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>3448600</v>
+      </c>
+      <c r="E48" s="3">
         <v>3439800</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>3538100</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>3352100</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>3392000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>3346600</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>3773100</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>4126800</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>3937400</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>3684500</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>3644400</v>
       </c>
-      <c r="N48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O48" s="3" t="s">
         <v>3</v>
       </c>
@@ -2528,44 +2635,47 @@
       <c r="R48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>1432200</v>
+      </c>
+      <c r="E49" s="3">
         <v>1434100</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>1632200</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>1392500</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>276100</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>273600</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>298900</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>308200</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>362900</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>351500</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>121200</v>
       </c>
-      <c r="N49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O49" s="3" t="s">
         <v>3</v>
       </c>
@@ -2578,8 +2688,11 @@
       <c r="R49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2628,8 +2741,11 @@
       <c r="R50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2678,17 +2794,20 @@
       <c r="R51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>714600</v>
+      </c>
+      <c r="E52" s="3">
         <v>655400</v>
       </c>
-      <c r="E52" s="3">
-        <v>0</v>
-      </c>
       <c r="F52" s="3">
         <v>0</v>
       </c>
@@ -2705,17 +2824,17 @@
         <v>0</v>
       </c>
       <c r="K52" s="3">
+        <v>0</v>
+      </c>
+      <c r="L52" s="3">
         <v>802600</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>617000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>633100</v>
       </c>
-      <c r="N52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O52" s="3" t="s">
         <v>3</v>
       </c>
@@ -2728,8 +2847,11 @@
       <c r="R52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2778,44 +2900,47 @@
       <c r="R53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>31041600</v>
+      </c>
+      <c r="E54" s="3">
         <v>29223600</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>31369800</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>28347500</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>22917100</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>22632200</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>23052900</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>22381500</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>21353500</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>19643300</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>18880000</v>
       </c>
-      <c r="N54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O54" s="3" t="s">
         <v>3</v>
       </c>
@@ -2828,8 +2953,11 @@
       <c r="R54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2848,8 +2976,9 @@
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
       <c r="R55" s="3"/>
-    </row>
-    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S55" s="3"/>
+    </row>
+    <row r="56" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2868,44 +2997,45 @@
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
       <c r="R56" s="3"/>
-    </row>
-    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S56" s="3"/>
+    </row>
+    <row r="57" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>1258900</v>
+      </c>
+      <c r="E57" s="3">
         <v>985700</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>1481200</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>1438400</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>1621900</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>1468400</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>1589400</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>1568900</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>1610500</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>1425200</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>1399600</v>
       </c>
-      <c r="N57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O57" s="3" t="s">
         <v>3</v>
       </c>
@@ -2918,44 +3048,47 @@
       <c r="R57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>4974600</v>
+      </c>
+      <c r="E58" s="3">
         <v>5930100</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>7148900</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>8001100</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>3155800</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>3932500</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>3250400</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>3560800</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>2906500</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>3104000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>1593600</v>
       </c>
-      <c r="N58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O58" s="3" t="s">
         <v>3</v>
       </c>
@@ -2968,44 +3101,47 @@
       <c r="R58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>3509000</v>
+      </c>
+      <c r="E59" s="3">
         <v>3514300</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>3554900</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>2799700</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>2732700</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>2558700</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>2693400</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>2599600</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>2899900</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>2496000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>2856500</v>
       </c>
-      <c r="N59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O59" s="3" t="s">
         <v>3</v>
       </c>
@@ -3018,44 +3154,47 @@
       <c r="R59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>10041900</v>
+      </c>
+      <c r="E60" s="3">
         <v>10752000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>12393300</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>12420200</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>7778700</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>8252300</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>7732200</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>7926500</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>7417000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>7025200</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>5849700</v>
       </c>
-      <c r="N60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O60" s="3" t="s">
         <v>3</v>
       </c>
@@ -3068,44 +3207,47 @@
       <c r="R60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>6948600</v>
+      </c>
+      <c r="E61" s="3">
         <v>5493200</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>4722500</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>3132700</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>1976000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>1892300</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>2060400</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>1246900</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>1404600</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>1143800</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>2112500</v>
       </c>
-      <c r="N61" s="3">
-        <v>0</v>
-      </c>
       <c r="O61" s="3">
         <v>0</v>
       </c>
@@ -3118,44 +3260,47 @@
       <c r="R61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>724400</v>
+      </c>
+      <c r="E62" s="3">
         <v>708500</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>618100</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>733100</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>643000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>591300</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>616700</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>637900</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>692400</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>747600</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>666600</v>
       </c>
-      <c r="N62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O62" s="3" t="s">
         <v>3</v>
       </c>
@@ -3168,8 +3313,11 @@
       <c r="R62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3218,8 +3366,11 @@
       <c r="R63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3268,8 +3419,11 @@
       <c r="R64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3318,44 +3472,47 @@
       <c r="R65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>18011400</v>
+      </c>
+      <c r="E66" s="3">
         <v>17290100</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>18094400</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>16641600</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>10654400</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>10958600</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>10667000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>10061400</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>9759500</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>9257000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>8944400</v>
       </c>
-      <c r="N66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O66" s="3" t="s">
         <v>3</v>
       </c>
@@ -3368,8 +3525,11 @@
       <c r="R66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3388,8 +3548,9 @@
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
       <c r="R67" s="3"/>
-    </row>
-    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S67" s="3"/>
+    </row>
+    <row r="68" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3438,8 +3599,11 @@
       <c r="R68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3488,8 +3652,11 @@
       <c r="R69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3538,8 +3705,11 @@
       <c r="R70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3588,44 +3758,47 @@
       <c r="R71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>8178500</v>
+      </c>
+      <c r="E72" s="3">
         <v>7966000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>8066400</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>7248000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>7739400</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>7073200</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>7464200</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>7422400</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>7501900</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>6520100</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>6337800</v>
       </c>
-      <c r="N72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O72" s="3" t="s">
         <v>3</v>
       </c>
@@ -3638,8 +3811,11 @@
       <c r="R72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3688,8 +3864,11 @@
       <c r="R73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3738,8 +3917,11 @@
       <c r="R74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3788,44 +3970,47 @@
       <c r="R75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>12666800</v>
+      </c>
+      <c r="E76" s="3">
         <v>11642700</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>12969200</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>11428300</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>11993700</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>11415000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>12117200</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>12058200</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>11594100</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>10386300</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>9935600</v>
       </c>
-      <c r="N76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O76" s="3" t="s">
         <v>3</v>
       </c>
@@ -3838,8 +4023,11 @@
       <c r="R76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3888,49 +4076,52 @@
       <c r="R77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45688</v>
+      </c>
+      <c r="E80" s="2">
         <v>45596</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45504</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45412</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45322</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45230</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45138</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45046</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44957</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44865</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44592</v>
       </c>
-      <c r="N80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="O80" s="2" t="s">
         <v>3</v>
       </c>
@@ -3943,8 +4134,11 @@
       <c r="R80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -3969,18 +4163,18 @@
       <c r="J81" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K81" s="3">
+      <c r="K81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L81" s="3">
         <v>246400</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>291900</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>256200</v>
       </c>
-      <c r="N81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O81" s="3" t="s">
         <v>3</v>
       </c>
@@ -3993,8 +4187,11 @@
       <c r="R81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4013,8 +4210,9 @@
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
       <c r="R82" s="3"/>
-    </row>
-    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S82" s="3"/>
+    </row>
+    <row r="83" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -4057,14 +4255,17 @@
       <c r="P83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q83" s="3">
-        <v>0</v>
+      <c r="Q83" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4113,8 +4314,11 @@
       <c r="R84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4163,8 +4367,11 @@
       <c r="R85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4213,8 +4420,11 @@
       <c r="R86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4263,8 +4473,11 @@
       <c r="R87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4313,8 +4526,11 @@
       <c r="R88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
@@ -4339,14 +4555,14 @@
       <c r="J89" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K89" s="3">
-        <v>0</v>
-      </c>
-      <c r="L89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M89" s="3">
-        <v>0</v>
+      <c r="K89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L89" s="3">
+        <v>0</v>
+      </c>
+      <c r="M89" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N89" s="3">
         <v>0</v>
@@ -4363,8 +4579,11 @@
       <c r="R89" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S89" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4383,8 +4602,9 @@
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
       <c r="R90" s="3"/>
-    </row>
-    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S90" s="3"/>
+    </row>
+    <row r="91" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -4409,8 +4629,8 @@
       <c r="J91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K91" s="3">
-        <v>0</v>
+      <c r="K91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L91" s="3">
         <v>0</v>
@@ -4433,8 +4653,11 @@
       <c r="R91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4483,8 +4706,11 @@
       <c r="R92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4533,8 +4759,11 @@
       <c r="R93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -4559,14 +4788,14 @@
       <c r="J94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K94" s="3">
-        <v>0</v>
-      </c>
-      <c r="L94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M94" s="3">
-        <v>0</v>
+      <c r="K94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L94" s="3">
+        <v>0</v>
+      </c>
+      <c r="M94" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N94" s="3">
         <v>0</v>
@@ -4583,8 +4812,11 @@
       <c r="R94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4603,8 +4835,9 @@
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
       <c r="R95" s="3"/>
-    </row>
-    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S95" s="3"/>
+    </row>
+    <row r="96" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -4629,8 +4862,8 @@
       <c r="J96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K96" s="3">
-        <v>0</v>
+      <c r="K96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L96" s="3">
         <v>0</v>
@@ -4653,8 +4886,11 @@
       <c r="R96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4703,8 +4939,11 @@
       <c r="R97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4753,8 +4992,11 @@
       <c r="R98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4803,8 +5045,11 @@
       <c r="R99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -4829,14 +5074,14 @@
       <c r="J100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K100" s="3">
-        <v>0</v>
-      </c>
-      <c r="L100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M100" s="3">
-        <v>0</v>
+      <c r="K100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L100" s="3">
+        <v>0</v>
+      </c>
+      <c r="M100" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N100" s="3">
         <v>0</v>
@@ -4853,8 +5098,11 @@
       <c r="R100" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -4879,14 +5127,14 @@
       <c r="J101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K101" s="3">
-        <v>0</v>
-      </c>
-      <c r="L101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M101" s="3">
-        <v>0</v>
+      <c r="K101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L101" s="3">
+        <v>0</v>
+      </c>
+      <c r="M101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N101" s="3">
         <v>0</v>
@@ -4903,8 +5151,11 @@
       <c r="R101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
@@ -4929,14 +5180,14 @@
       <c r="J102" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K102" s="3">
-        <v>0</v>
-      </c>
-      <c r="L102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M102" s="3">
-        <v>0</v>
+      <c r="K102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L102" s="3">
+        <v>0</v>
+      </c>
+      <c r="M102" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N102" s="3">
         <v>0</v>
@@ -4951,6 +5202,9 @@
         <v>0</v>
       </c>
       <c r="R102" s="3">
+        <v>0</v>
+      </c>
+      <c r="S102" s="3">
         <v>0</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/SKHSY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/SKHSY_QTR_FIN.xlsx
@@ -2220,7 +2220,7 @@
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>2519500</v>
+        <v>2521100</v>
       </c>
       <c r="E41" s="3">
         <v>2305500</v>
@@ -2273,7 +2273,7 @@
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>1600</v>
+        <v>0</v>
       </c>
       <c r="E42" s="3">
         <v>83900</v>
@@ -2538,7 +2538,7 @@
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>1327400</v>
+        <v>2041900</v>
       </c>
       <c r="E47" s="3">
         <v>1390000</v>
@@ -2803,7 +2803,7 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>714600</v>
+        <v>0</v>
       </c>
       <c r="E52" s="3">
         <v>655400</v>
@@ -3004,7 +3004,7 @@
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>1258900</v>
+        <v>1771200</v>
       </c>
       <c r="E57" s="3">
         <v>985700</v>
@@ -3110,7 +3110,7 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>3509000</v>
+        <v>2996700</v>
       </c>
       <c r="E59" s="3">
         <v>3514300</v>

--- a/AAII_Financials/Quarterly/SKHSY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/SKHSY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="533" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="597" uniqueCount="92">
   <si>
     <t>SKHSY</t>
   </si>
@@ -656,67 +656,70 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:S102"/>
+  <dimension ref="A5:T102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="14" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="19" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="15" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="20" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:20" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45777</v>
+      </c>
+      <c r="E7" s="2">
         <v>45688</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45596</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45504</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45412</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45322</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45230</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45138</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45046</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44957</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44865</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44592</v>
       </c>
-      <c r="O7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="P7" s="2" t="s">
         <v>3</v>
       </c>
@@ -729,8 +732,11 @@
       <c r="S7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
@@ -758,18 +764,18 @@
       <c r="K8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L8" s="3">
+      <c r="L8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M8" s="3">
         <v>5671200</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>4507100</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>5019700</v>
       </c>
-      <c r="O8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P8" s="3" t="s">
         <v>3</v>
       </c>
@@ -782,8 +788,11 @@
       <c r="S8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -811,18 +820,18 @@
       <c r="K9" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L9" s="3">
+      <c r="L9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M9" s="3">
         <v>4633900</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>3635800</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>4041200</v>
       </c>
-      <c r="O9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P9" s="3" t="s">
         <v>3</v>
       </c>
@@ -835,8 +844,11 @@
       <c r="S9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -864,18 +876,18 @@
       <c r="K10" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L10" s="3">
+      <c r="L10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M10" s="3">
         <v>1037300</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>871300</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>978500</v>
       </c>
-      <c r="O10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P10" s="3" t="s">
         <v>3</v>
       </c>
@@ -888,8 +900,11 @@
       <c r="S10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -909,8 +924,9 @@
       <c r="Q11" s="3"/>
       <c r="R11" s="3"/>
       <c r="S11" s="3"/>
-    </row>
-    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T11" s="3"/>
+    </row>
+    <row r="12" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -962,8 +978,11 @@
       <c r="S12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1015,8 +1034,11 @@
       <c r="S13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1044,18 +1066,18 @@
       <c r="K14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L14" s="3">
+      <c r="L14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M14" s="3">
         <v>19500</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>-54000</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>3000</v>
       </c>
-      <c r="O14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1068,8 +1090,11 @@
       <c r="S14" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T14" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1097,8 +1122,8 @@
       <c r="K15" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L15" s="3">
-        <v>0</v>
+      <c r="L15" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M15" s="3">
         <v>0</v>
@@ -1121,8 +1146,11 @@
       <c r="S15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:20" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1139,8 +1167,9 @@
       <c r="Q16" s="3"/>
       <c r="R16" s="3"/>
       <c r="S16" s="3"/>
-    </row>
-    <row r="17" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T16" s="3"/>
+    </row>
+    <row r="17" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -1168,18 +1197,18 @@
       <c r="K17" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L17" s="3">
+      <c r="L17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M17" s="3">
         <v>5271800</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>4095300</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>4605300</v>
       </c>
-      <c r="O17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P17" s="3" t="s">
         <v>3</v>
       </c>
@@ -1192,8 +1221,11 @@
       <c r="S17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1221,18 +1253,18 @@
       <c r="K18" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L18" s="3">
+      <c r="L18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M18" s="3">
         <v>399300</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>411700</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>414400</v>
       </c>
-      <c r="O18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1245,8 +1277,11 @@
       <c r="S18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1266,8 +1301,9 @@
       <c r="Q19" s="3"/>
       <c r="R19" s="3"/>
       <c r="S19" s="3"/>
-    </row>
-    <row r="20" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T19" s="3"/>
+    </row>
+    <row r="20" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1295,18 +1331,18 @@
       <c r="K20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L20" s="3">
+      <c r="L20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M20" s="3">
         <v>-21300</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>1900</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>5800</v>
       </c>
-      <c r="O20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P20" s="3" t="s">
         <v>3</v>
       </c>
@@ -1319,8 +1355,11 @@
       <c r="S20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1372,8 +1411,11 @@
       <c r="S21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1401,18 +1443,18 @@
       <c r="K22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L22" s="3">
+      <c r="L22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M22" s="3">
         <v>13600</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>10600</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>10700</v>
       </c>
-      <c r="O22" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P22" s="3" t="s">
         <v>3</v>
       </c>
@@ -1425,8 +1467,11 @@
       <c r="S22" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
@@ -1454,18 +1499,18 @@
       <c r="K23" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L23" s="3">
+      <c r="L23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M23" s="3">
         <v>364400</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>403100</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>409500</v>
       </c>
-      <c r="O23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P23" s="3" t="s">
         <v>3</v>
       </c>
@@ -1478,8 +1523,11 @@
       <c r="S23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1507,18 +1555,18 @@
       <c r="K24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L24" s="3">
+      <c r="L24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M24" s="3">
         <v>113500</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>106400</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>134300</v>
       </c>
-      <c r="O24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P24" s="3" t="s">
         <v>3</v>
       </c>
@@ -1531,8 +1579,11 @@
       <c r="S24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1584,8 +1635,11 @@
       <c r="S25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -1613,18 +1667,18 @@
       <c r="K26" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L26" s="3">
+      <c r="L26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M26" s="3">
         <v>250900</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>296700</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>275100</v>
       </c>
-      <c r="O26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P26" s="3" t="s">
         <v>3</v>
       </c>
@@ -1637,8 +1691,11 @@
       <c r="S26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -1666,18 +1723,18 @@
       <c r="K27" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L27" s="3">
+      <c r="L27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M27" s="3">
         <v>246400</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>291900</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>256200</v>
       </c>
-      <c r="O27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P27" s="3" t="s">
         <v>3</v>
       </c>
@@ -1690,8 +1747,11 @@
       <c r="S27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1743,8 +1803,11 @@
       <c r="S28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1772,8 +1835,8 @@
       <c r="K29" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L29" s="3">
-        <v>0</v>
+      <c r="L29" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M29" s="3">
         <v>0</v>
@@ -1796,8 +1859,11 @@
       <c r="S29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1849,8 +1915,11 @@
       <c r="S30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1902,8 +1971,11 @@
       <c r="S31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -1931,18 +2003,18 @@
       <c r="K32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L32" s="3">
+      <c r="L32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M32" s="3">
         <v>21300</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-1900</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-5800</v>
       </c>
-      <c r="O32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P32" s="3" t="s">
         <v>3</v>
       </c>
@@ -1955,8 +2027,11 @@
       <c r="S32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -1984,18 +2059,18 @@
       <c r="K33" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L33" s="3">
+      <c r="L33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M33" s="3">
         <v>246400</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>291900</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>256200</v>
       </c>
-      <c r="O33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P33" s="3" t="s">
         <v>3</v>
       </c>
@@ -2008,8 +2083,11 @@
       <c r="S33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2061,8 +2139,11 @@
       <c r="S34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -2090,18 +2171,18 @@
       <c r="K35" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L35" s="3">
+      <c r="L35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M35" s="3">
         <v>246400</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>291900</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>256200</v>
       </c>
-      <c r="O35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P35" s="3" t="s">
         <v>3</v>
       </c>
@@ -2114,52 +2195,55 @@
       <c r="S35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:20" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45777</v>
+      </c>
+      <c r="E38" s="2">
         <v>45688</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45596</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45504</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45412</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45322</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45230</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45138</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45046</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44957</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44865</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44592</v>
       </c>
-      <c r="O38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="P38" s="2" t="s">
         <v>3</v>
       </c>
@@ -2172,8 +2256,11 @@
       <c r="S38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2193,8 +2280,9 @@
       <c r="Q39" s="3"/>
       <c r="R39" s="3"/>
       <c r="S39" s="3"/>
-    </row>
-    <row r="40" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T39" s="3"/>
+    </row>
+    <row r="40" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2214,47 +2302,48 @@
       <c r="Q40" s="3"/>
       <c r="R40" s="3"/>
       <c r="S40" s="3"/>
-    </row>
-    <row r="41" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T40" s="3"/>
+    </row>
+    <row r="41" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="D41" s="3">
+      <c r="D41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E41" s="3">
         <v>2521100</v>
       </c>
-      <c r="E41" s="3">
-        <v>2305500</v>
-      </c>
-      <c r="F41" s="3">
+      <c r="F41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G41" s="3">
         <v>2869900</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>2464100</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>2003800</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>2073100</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>2143900</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>2227900</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>2363600</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>2165300</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>3473000</v>
       </c>
-      <c r="O41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2267,8 +2356,11 @@
       <c r="S41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2276,17 +2368,17 @@
         <v>0</v>
       </c>
       <c r="E42" s="3">
-        <v>83900</v>
+        <v>0</v>
       </c>
       <c r="F42" s="3">
+        <v>0</v>
+      </c>
+      <c r="G42" s="3">
         <v>190300</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>78100</v>
       </c>
-      <c r="H42" s="3">
-        <v>0</v>
-      </c>
       <c r="I42" s="3">
         <v>0</v>
       </c>
@@ -2296,14 +2388,14 @@
       <c r="K42" s="3">
         <v>0</v>
       </c>
-      <c r="L42" s="3" t="s">
-        <v>3</v>
+      <c r="L42" s="3">
+        <v>0</v>
       </c>
       <c r="M42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N42" s="3">
-        <v>0</v>
+      <c r="N42" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="O42" s="3">
         <v>0</v>
@@ -2320,47 +2412,50 @@
       <c r="S42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="D43" s="3">
+      <c r="D43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E43" s="3">
         <v>1356200</v>
       </c>
-      <c r="E43" s="3">
-        <v>1270300</v>
-      </c>
-      <c r="F43" s="3">
+      <c r="F43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G43" s="3">
         <v>1172400</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>1093000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>1199200</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>1008200</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>1004600</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>1134600</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>1107500</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>959500</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>884900</v>
       </c>
-      <c r="O43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P43" s="3" t="s">
         <v>3</v>
       </c>
@@ -2373,47 +2468,50 @@
       <c r="S43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D44" s="3">
+      <c r="D44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E44" s="3">
         <v>18497600</v>
       </c>
-      <c r="E44" s="3">
-        <v>17004400</v>
-      </c>
-      <c r="F44" s="3">
+      <c r="F44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G44" s="3">
         <v>18166300</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>16747900</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>12944000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>12885100</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>12606200</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>11310400</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>10400000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>9720300</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>8118200</v>
       </c>
-      <c r="O44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P44" s="3" t="s">
         <v>3</v>
       </c>
@@ -2426,47 +2524,50 @@
       <c r="S44" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="45" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T44" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3">
+      <c r="D45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E45" s="3">
         <v>1587100</v>
       </c>
-      <c r="E45" s="3">
-        <v>1468000</v>
-      </c>
-      <c r="F45" s="3">
+      <c r="F45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G45" s="3">
         <v>1517300</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>1168100</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>920200</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>921400</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>936400</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>999000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>995400</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>880000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>685300</v>
       </c>
-      <c r="O45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P45" s="3" t="s">
         <v>3</v>
       </c>
@@ -2479,47 +2580,50 @@
       <c r="S45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="D46" s="3">
+      <c r="D46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E46" s="3">
         <v>23962100</v>
       </c>
-      <c r="E46" s="3">
-        <v>22132200</v>
-      </c>
-      <c r="F46" s="3">
+      <c r="F46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G46" s="3">
         <v>23916200</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>21551200</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>17067200</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>16887700</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>16691100</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>15671900</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>14866600</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>13725100</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>13161400</v>
       </c>
-      <c r="O46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P46" s="3" t="s">
         <v>3</v>
       </c>
@@ -2532,47 +2636,50 @@
       <c r="S46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3">
+      <c r="D47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E47" s="3">
         <v>2041900</v>
       </c>
-      <c r="E47" s="3">
-        <v>1390000</v>
-      </c>
-      <c r="F47" s="3">
+      <c r="F47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G47" s="3">
         <v>2145600</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>1968900</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>2016400</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>1965700</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>2132000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>2117000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>1384000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>1265200</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>1319900</v>
       </c>
-      <c r="O47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P47" s="3" t="s">
         <v>3</v>
       </c>
@@ -2585,47 +2692,50 @@
       <c r="S47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="D48" s="3">
+      <c r="D48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E48" s="3">
         <v>3448600</v>
       </c>
-      <c r="E48" s="3">
-        <v>3439800</v>
-      </c>
-      <c r="F48" s="3">
+      <c r="F48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G48" s="3">
         <v>3538100</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>3352100</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>3392000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>3346600</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>3773100</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>4126800</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>3937400</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>3684500</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>3644400</v>
       </c>
-      <c r="O48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P48" s="3" t="s">
         <v>3</v>
       </c>
@@ -2638,47 +2748,50 @@
       <c r="S48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="D49" s="3">
+      <c r="D49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E49" s="3">
         <v>1432200</v>
       </c>
-      <c r="E49" s="3">
-        <v>1434100</v>
-      </c>
-      <c r="F49" s="3">
+      <c r="F49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G49" s="3">
         <v>1632200</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>1392500</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>276100</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>273600</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>298900</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>308200</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>362900</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>351500</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>121200</v>
       </c>
-      <c r="O49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P49" s="3" t="s">
         <v>3</v>
       </c>
@@ -2691,8 +2804,11 @@
       <c r="S49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2744,8 +2860,11 @@
       <c r="S50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2797,19 +2916,22 @@
       <c r="S51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="D52" s="3">
-        <v>0</v>
+      <c r="D52" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="E52" s="3">
-        <v>655400</v>
-      </c>
-      <c r="F52" s="3">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="F52" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="G52" s="3">
         <v>0</v>
@@ -2827,17 +2949,17 @@
         <v>0</v>
       </c>
       <c r="L52" s="3">
+        <v>0</v>
+      </c>
+      <c r="M52" s="3">
         <v>802600</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>617000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>633100</v>
       </c>
-      <c r="O52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P52" s="3" t="s">
         <v>3</v>
       </c>
@@ -2850,8 +2972,11 @@
       <c r="S52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2903,47 +3028,50 @@
       <c r="S53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="D54" s="3">
+      <c r="D54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E54" s="3">
         <v>31041600</v>
       </c>
-      <c r="E54" s="3">
-        <v>29223600</v>
-      </c>
-      <c r="F54" s="3">
+      <c r="F54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G54" s="3">
         <v>31369800</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>28347500</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>22917100</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>22632200</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>23052900</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>22381500</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>21353500</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>19643300</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>18880000</v>
       </c>
-      <c r="O54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P54" s="3" t="s">
         <v>3</v>
       </c>
@@ -2956,8 +3084,11 @@
       <c r="S54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2977,8 +3108,9 @@
       <c r="Q55" s="3"/>
       <c r="R55" s="3"/>
       <c r="S55" s="3"/>
-    </row>
-    <row r="56" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T55" s="3"/>
+    </row>
+    <row r="56" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2998,47 +3130,48 @@
       <c r="Q56" s="3"/>
       <c r="R56" s="3"/>
       <c r="S56" s="3"/>
-    </row>
-    <row r="57" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T56" s="3"/>
+    </row>
+    <row r="57" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="D57" s="3">
+      <c r="D57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E57" s="3">
         <v>1771200</v>
       </c>
-      <c r="E57" s="3">
-        <v>985700</v>
-      </c>
-      <c r="F57" s="3">
+      <c r="F57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G57" s="3">
         <v>1481200</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>1438400</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>1621900</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>1468400</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>1589400</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>1568900</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>1610500</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>1425200</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>1399600</v>
       </c>
-      <c r="O57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P57" s="3" t="s">
         <v>3</v>
       </c>
@@ -3051,47 +3184,50 @@
       <c r="S57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="D58" s="3">
+      <c r="D58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E58" s="3">
         <v>4974600</v>
       </c>
-      <c r="E58" s="3">
-        <v>5930100</v>
-      </c>
-      <c r="F58" s="3">
+      <c r="F58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G58" s="3">
         <v>7148900</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>8001100</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>3155800</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>3932500</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>3250400</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>3560800</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>2906500</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>3104000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>1593600</v>
       </c>
-      <c r="O58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P58" s="3" t="s">
         <v>3</v>
       </c>
@@ -3104,47 +3240,50 @@
       <c r="S58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="D59" s="3">
+      <c r="D59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E59" s="3">
         <v>2996700</v>
       </c>
-      <c r="E59" s="3">
-        <v>3514300</v>
-      </c>
-      <c r="F59" s="3">
+      <c r="F59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G59" s="3">
         <v>3554900</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>2799700</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>2732700</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>2558700</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>2693400</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>2599600</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>2899900</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>2496000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>2856500</v>
       </c>
-      <c r="O59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P59" s="3" t="s">
         <v>3</v>
       </c>
@@ -3157,47 +3296,50 @@
       <c r="S59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="D60" s="3">
+      <c r="D60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E60" s="3">
         <v>10041900</v>
       </c>
-      <c r="E60" s="3">
-        <v>10752000</v>
-      </c>
-      <c r="F60" s="3">
+      <c r="F60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G60" s="3">
         <v>12393300</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>12420200</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>7778700</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>8252300</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>7732200</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>7926500</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>7417000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>7025200</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>5849700</v>
       </c>
-      <c r="O60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P60" s="3" t="s">
         <v>3</v>
       </c>
@@ -3210,47 +3352,50 @@
       <c r="S60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>0</v>
+      </c>
+      <c r="E61" s="3">
         <v>6948600</v>
       </c>
-      <c r="E61" s="3">
-        <v>5493200</v>
-      </c>
       <c r="F61" s="3">
+        <v>0</v>
+      </c>
+      <c r="G61" s="3">
         <v>4722500</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>3132700</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>1976000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>1892300</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>2060400</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>1246900</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>1404600</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>1143800</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>2112500</v>
       </c>
-      <c r="O61" s="3">
-        <v>0</v>
-      </c>
       <c r="P61" s="3">
         <v>0</v>
       </c>
@@ -3263,47 +3408,50 @@
       <c r="S61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D62" s="3">
+      <c r="D62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E62" s="3">
         <v>724400</v>
       </c>
-      <c r="E62" s="3">
-        <v>708500</v>
-      </c>
-      <c r="F62" s="3">
+      <c r="F62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G62" s="3">
         <v>618100</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>733100</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>643000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>591300</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>616700</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>637900</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>692400</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>747600</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>666600</v>
       </c>
-      <c r="O62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P62" s="3" t="s">
         <v>3</v>
       </c>
@@ -3316,8 +3464,11 @@
       <c r="S62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3369,8 +3520,11 @@
       <c r="S63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3422,8 +3576,11 @@
       <c r="S64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3475,47 +3632,50 @@
       <c r="S65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="D66" s="3">
+      <c r="D66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E66" s="3">
         <v>18011400</v>
       </c>
-      <c r="E66" s="3">
-        <v>17290100</v>
-      </c>
-      <c r="F66" s="3">
+      <c r="F66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G66" s="3">
         <v>18094400</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>16641600</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>10654400</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>10958600</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>10667000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>10061400</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>9759500</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>9257000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>8944400</v>
       </c>
-      <c r="O66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P66" s="3" t="s">
         <v>3</v>
       </c>
@@ -3528,8 +3688,11 @@
       <c r="S66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3549,8 +3712,9 @@
       <c r="Q67" s="3"/>
       <c r="R67" s="3"/>
       <c r="S67" s="3"/>
-    </row>
-    <row r="68" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T67" s="3"/>
+    </row>
+    <row r="68" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3602,8 +3766,11 @@
       <c r="S68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3655,8 +3822,11 @@
       <c r="S69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3708,8 +3878,11 @@
       <c r="S70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3761,47 +3934,50 @@
       <c r="S71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="D72" s="3">
+      <c r="D72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E72" s="3">
         <v>8178500</v>
       </c>
-      <c r="E72" s="3">
-        <v>7966000</v>
-      </c>
-      <c r="F72" s="3">
+      <c r="F72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G72" s="3">
         <v>8066400</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>7248000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>7739400</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>7073200</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>7464200</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>7422400</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>7501900</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>6520100</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>6337800</v>
       </c>
-      <c r="O72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P72" s="3" t="s">
         <v>3</v>
       </c>
@@ -3814,8 +3990,11 @@
       <c r="S72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3867,8 +4046,11 @@
       <c r="S73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3920,8 +4102,11 @@
       <c r="S74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3973,47 +4158,50 @@
       <c r="S75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="D76" s="3">
+      <c r="D76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E76" s="3">
         <v>12666800</v>
       </c>
-      <c r="E76" s="3">
-        <v>11642700</v>
-      </c>
-      <c r="F76" s="3">
+      <c r="F76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G76" s="3">
         <v>12969200</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>11428300</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>11993700</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>11415000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>12117200</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>12058200</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>11594100</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>10386300</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>9935600</v>
       </c>
-      <c r="O76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P76" s="3" t="s">
         <v>3</v>
       </c>
@@ -4026,8 +4214,11 @@
       <c r="S76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4079,52 +4270,55 @@
       <c r="S77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:20" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45777</v>
+      </c>
+      <c r="E80" s="2">
         <v>45688</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45596</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45504</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45412</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45322</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45230</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45138</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45046</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44957</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44865</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44592</v>
       </c>
-      <c r="O80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="P80" s="2" t="s">
         <v>3</v>
       </c>
@@ -4137,8 +4331,11 @@
       <c r="S80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -4166,18 +4363,18 @@
       <c r="K81" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L81" s="3">
+      <c r="L81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M81" s="3">
         <v>246400</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>291900</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>256200</v>
       </c>
-      <c r="O81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P81" s="3" t="s">
         <v>3</v>
       </c>
@@ -4190,8 +4387,11 @@
       <c r="S81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4211,8 +4411,9 @@
       <c r="Q82" s="3"/>
       <c r="R82" s="3"/>
       <c r="S82" s="3"/>
-    </row>
-    <row r="83" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T82" s="3"/>
+    </row>
+    <row r="83" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -4258,14 +4459,17 @@
       <c r="Q83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R83" s="3">
-        <v>0</v>
+      <c r="R83" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="S83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4317,8 +4521,11 @@
       <c r="S84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4370,8 +4577,11 @@
       <c r="S85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4423,8 +4633,11 @@
       <c r="S86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4476,8 +4689,11 @@
       <c r="S87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4529,8 +4745,11 @@
       <c r="S88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
@@ -4558,14 +4777,14 @@
       <c r="K89" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L89" s="3">
-        <v>0</v>
-      </c>
-      <c r="M89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N89" s="3">
-        <v>0</v>
+      <c r="L89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M89" s="3">
+        <v>0</v>
+      </c>
+      <c r="N89" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="O89" s="3">
         <v>0</v>
@@ -4582,8 +4801,11 @@
       <c r="S89" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="90" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T89" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4603,8 +4825,9 @@
       <c r="Q90" s="3"/>
       <c r="R90" s="3"/>
       <c r="S90" s="3"/>
-    </row>
-    <row r="91" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T90" s="3"/>
+    </row>
+    <row r="91" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -4632,8 +4855,8 @@
       <c r="K91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L91" s="3">
-        <v>0</v>
+      <c r="L91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M91" s="3">
         <v>0</v>
@@ -4656,8 +4879,11 @@
       <c r="S91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4709,8 +4935,11 @@
       <c r="S92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4762,8 +4991,11 @@
       <c r="S93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -4791,14 +5023,14 @@
       <c r="K94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L94" s="3">
-        <v>0</v>
-      </c>
-      <c r="M94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N94" s="3">
-        <v>0</v>
+      <c r="L94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M94" s="3">
+        <v>0</v>
+      </c>
+      <c r="N94" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="O94" s="3">
         <v>0</v>
@@ -4815,8 +5047,11 @@
       <c r="S94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4836,8 +5071,9 @@
       <c r="Q95" s="3"/>
       <c r="R95" s="3"/>
       <c r="S95" s="3"/>
-    </row>
-    <row r="96" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T95" s="3"/>
+    </row>
+    <row r="96" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -4865,8 +5101,8 @@
       <c r="K96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L96" s="3">
-        <v>0</v>
+      <c r="L96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M96" s="3">
         <v>0</v>
@@ -4889,8 +5125,11 @@
       <c r="S96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4942,8 +5181,11 @@
       <c r="S97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4995,8 +5237,11 @@
       <c r="S98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5048,8 +5293,11 @@
       <c r="S99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -5077,14 +5325,14 @@
       <c r="K100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L100" s="3">
-        <v>0</v>
-      </c>
-      <c r="M100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N100" s="3">
-        <v>0</v>
+      <c r="L100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M100" s="3">
+        <v>0</v>
+      </c>
+      <c r="N100" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="O100" s="3">
         <v>0</v>
@@ -5101,8 +5349,11 @@
       <c r="S100" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="101" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -5130,14 +5381,14 @@
       <c r="K101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L101" s="3">
-        <v>0</v>
-      </c>
-      <c r="M101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N101" s="3">
-        <v>0</v>
+      <c r="L101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M101" s="3">
+        <v>0</v>
+      </c>
+      <c r="N101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="O101" s="3">
         <v>0</v>
@@ -5154,8 +5405,11 @@
       <c r="S101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
@@ -5183,14 +5437,14 @@
       <c r="K102" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L102" s="3">
-        <v>0</v>
-      </c>
-      <c r="M102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N102" s="3">
-        <v>0</v>
+      <c r="L102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M102" s="3">
+        <v>0</v>
+      </c>
+      <c r="N102" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="O102" s="3">
         <v>0</v>
@@ -5205,6 +5459,9 @@
         <v>0</v>
       </c>
       <c r="S102" s="3">
+        <v>0</v>
+      </c>
+      <c r="T102" s="3">
         <v>0</v>
       </c>
     </row>
